--- a/input_data/two_stage_dh_model.xlsx
+++ b/input_data/two_stage_dh_model.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dsdennis\HOPE\Predicer\input_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E911949-E6B2-45CD-8E01-B08C63E36AE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5709A8F4-2E0D-42D8-8C3F-A0C399672118}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17640" tabRatio="796" activeTab="1" xr2:uid="{788BFBD1-D930-4535-8A91-D85C56924796}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="796" firstSheet="4" activeTab="14" xr2:uid="{788BFBD1-D930-4535-8A91-D85C56924796}"/>
   </bookViews>
   <sheets>
     <sheet name="timeseries" sheetId="18" r:id="rId1"/>
@@ -27,20 +27,21 @@
     <sheet name="cf" sheetId="7" r:id="rId12"/>
     <sheet name="inflow" sheetId="3" r:id="rId13"/>
     <sheet name="inflow_blocks" sheetId="22" r:id="rId14"/>
-    <sheet name="price" sheetId="4" r:id="rId15"/>
-    <sheet name="markets" sheetId="5" r:id="rId16"/>
-    <sheet name="reserve_realisation" sheetId="23" r:id="rId17"/>
-    <sheet name="market_prices" sheetId="8" r:id="rId18"/>
-    <sheet name="balance_prices" sheetId="20" r:id="rId19"/>
-    <sheet name="reserve_activation_price" sheetId="28" r:id="rId20"/>
-    <sheet name="bid_slots" sheetId="29" r:id="rId21"/>
-    <sheet name="risk" sheetId="17" r:id="rId22"/>
-    <sheet name="scenarios" sheetId="9" r:id="rId23"/>
-    <sheet name="fixed_ts" sheetId="11" r:id="rId24"/>
-    <sheet name="eff_ts" sheetId="12" r:id="rId25"/>
-    <sheet name="cap_ts" sheetId="16" r:id="rId26"/>
-    <sheet name="constraints" sheetId="14" r:id="rId27"/>
-    <sheet name="gen_constraint" sheetId="15" r:id="rId28"/>
+    <sheet name="flex_inflow" sheetId="30" r:id="rId15"/>
+    <sheet name="price" sheetId="4" r:id="rId16"/>
+    <sheet name="markets" sheetId="5" r:id="rId17"/>
+    <sheet name="reserve_realisation" sheetId="23" r:id="rId18"/>
+    <sheet name="market_prices" sheetId="8" r:id="rId19"/>
+    <sheet name="balance_prices" sheetId="20" r:id="rId20"/>
+    <sheet name="reserve_activation_price" sheetId="28" r:id="rId21"/>
+    <sheet name="bid_slots" sheetId="29" r:id="rId22"/>
+    <sheet name="risk" sheetId="17" r:id="rId23"/>
+    <sheet name="scenarios" sheetId="9" r:id="rId24"/>
+    <sheet name="fixed_ts" sheetId="11" r:id="rId25"/>
+    <sheet name="eff_ts" sheetId="12" r:id="rId26"/>
+    <sheet name="cap_ts" sheetId="16" r:id="rId27"/>
+    <sheet name="constraints" sheetId="14" r:id="rId28"/>
+    <sheet name="gen_constraint" sheetId="15" r:id="rId29"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -60,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="241" uniqueCount="151">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="247" uniqueCount="156">
   <si>
     <t>node</t>
   </si>
@@ -514,6 +515,21 @@
   <si>
     <t>common_end_timesteps</t>
   </si>
+  <si>
+    <t>period_name</t>
+  </si>
+  <si>
+    <t>scenario</t>
+  </si>
+  <si>
+    <t>t_start</t>
+  </si>
+  <si>
+    <t>t_end</t>
+  </si>
+  <si>
+    <t>inflow</t>
+  </si>
 </sst>
 </file>
 
@@ -565,13 +581,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -579,7 +592,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -6653,9 +6665,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -6693,7 +6705,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -6799,7 +6811,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -6941,7 +6953,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -6950,207 +6962,207 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{39053E69-3A75-490E-847C-66A9CF6C1FC5}">
   <dimension ref="A1:A49"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="14.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A2" s="8">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A2" s="5">
         <v>45398</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A3" s="8">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A3" s="5">
         <v>45398.041666666664</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A4" s="8">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A4" s="5">
         <v>45398.083333333336</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A5" s="8">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A5" s="5">
         <v>45398.125</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A6" s="8">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6" s="5">
         <v>45398.166666666664</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A7" s="8">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A7" s="5">
         <v>45398.208333333336</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A8" s="8">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A8" s="5">
         <v>45398.25</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A9" s="8">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A9" s="5">
         <v>45398.291666666664</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A10" s="8">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A10" s="5">
         <v>45398.333333333336</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A11" s="8">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A11" s="5">
         <v>45398.375</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A12" s="8">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A12" s="5">
         <v>45398.416666666664</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A13" s="8">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A13" s="5">
         <v>45398.458333333336</v>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A14" s="8">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A14" s="5">
         <v>45398.5</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A15" s="8">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A15" s="5">
         <v>45398.541666666664</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A16" s="8">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A16" s="5">
         <v>45398.583333333336</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A17" s="8">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A17" s="5">
         <v>45398.625</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A18" s="8">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A18" s="5">
         <v>45398.666666666664</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A19" s="8">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A19" s="5">
         <v>45398.708333333336</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A20" s="8">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A20" s="5">
         <v>45398.75</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A21" s="8">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A21" s="5">
         <v>45398.791666666664</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A22" s="8">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A22" s="5">
         <v>45398.833333333336</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A23" s="8">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A23" s="5">
         <v>45398.875</v>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A24" s="8">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A24" s="5">
         <v>45398.916666666664</v>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A25" s="8">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A25" s="5">
         <v>45398.958333333336</v>
       </c>
     </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A26" s="8"/>
-    </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A27" s="8"/>
-    </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A28" s="8"/>
-    </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A29" s="8"/>
-    </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A30" s="8"/>
-    </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A31" s="8"/>
-    </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A32" s="8"/>
-    </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A33" s="8"/>
-    </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A34" s="8"/>
-    </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A35" s="8"/>
-    </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A36" s="8"/>
-    </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A37" s="8"/>
-    </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A38" s="8"/>
-    </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A39" s="8"/>
-    </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A40" s="8"/>
-    </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A41" s="8"/>
-    </row>
-    <row r="42" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A42" s="8"/>
-    </row>
-    <row r="43" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A43" s="8"/>
-    </row>
-    <row r="44" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A44" s="8"/>
-    </row>
-    <row r="45" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A45" s="8"/>
-    </row>
-    <row r="46" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A46" s="8"/>
-    </row>
-    <row r="47" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A47" s="8"/>
-    </row>
-    <row r="48" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A48" s="8"/>
-    </row>
-    <row r="49" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A49" s="8"/>
+    <row r="26" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A26" s="5"/>
+    </row>
+    <row r="27" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A27" s="5"/>
+    </row>
+    <row r="28" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A28" s="5"/>
+    </row>
+    <row r="29" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A29" s="5"/>
+    </row>
+    <row r="30" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A30" s="5"/>
+    </row>
+    <row r="31" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A31" s="5"/>
+    </row>
+    <row r="32" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A32" s="5"/>
+    </row>
+    <row r="33" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A33" s="5"/>
+    </row>
+    <row r="34" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A34" s="5"/>
+    </row>
+    <row r="35" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A35" s="5"/>
+    </row>
+    <row r="36" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A36" s="5"/>
+    </row>
+    <row r="37" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A37" s="5"/>
+    </row>
+    <row r="38" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A38" s="5"/>
+    </row>
+    <row r="39" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A39" s="5"/>
+    </row>
+    <row r="40" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A40" s="5"/>
+    </row>
+    <row r="41" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A41" s="5"/>
+    </row>
+    <row r="42" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A42" s="5"/>
+    </row>
+    <row r="43" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A43" s="5"/>
+    </row>
+    <row r="44" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A44" s="5"/>
+    </row>
+    <row r="45" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A45" s="5"/>
+    </row>
+    <row r="46" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A46" s="5"/>
+    </row>
+    <row r="47" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A47" s="5"/>
+    </row>
+    <row r="48" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A48" s="5"/>
+    </row>
+    <row r="49" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A49" s="5"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -7161,194 +7173,194 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8E3CA5E7-5C31-4336-93EE-0293D708EE58}">
   <dimension ref="A1:C31"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="19.28515625" style="8" customWidth="1"/>
+    <col min="1" max="1" width="19.33203125" style="5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="B1" s="3"/>
-      <c r="C1" s="3"/>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="8">
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" s="5">
         <f>IF(timeseries!A2&lt;&gt;"",timeseries!A2,"")</f>
         <v>45398</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" s="8">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" s="5">
         <f>IF(timeseries!A3&lt;&gt;"",timeseries!A3,"")</f>
         <v>45398.041666666664</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" s="8">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" s="5">
         <f>IF(timeseries!A4&lt;&gt;"",timeseries!A4,"")</f>
         <v>45398.083333333336</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" s="8">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" s="5">
         <f>IF(timeseries!A5&lt;&gt;"",timeseries!A5,"")</f>
         <v>45398.125</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" s="8">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6" s="5">
         <f>IF(timeseries!A6&lt;&gt;"",timeseries!A6,"")</f>
         <v>45398.166666666664</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" s="8">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A7" s="5">
         <f>IF(timeseries!A7&lt;&gt;"",timeseries!A7,"")</f>
         <v>45398.208333333336</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" s="8">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A8" s="5">
         <f>IF(timeseries!A8&lt;&gt;"",timeseries!A8,"")</f>
         <v>45398.25</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" s="8">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A9" s="5">
         <f>IF(timeseries!A9&lt;&gt;"",timeseries!A9,"")</f>
         <v>45398.291666666664</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" s="8">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A10" s="5">
         <f>IF(timeseries!A10&lt;&gt;"",timeseries!A10,"")</f>
         <v>45398.333333333336</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A11" s="8">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A11" s="5">
         <f>IF(timeseries!A11&lt;&gt;"",timeseries!A11,"")</f>
         <v>45398.375</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12" s="8">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A12" s="5">
         <f>IF(timeseries!A12&lt;&gt;"",timeseries!A12,"")</f>
         <v>45398.416666666664</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A13" s="8">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A13" s="5">
         <f>IF(timeseries!A13&lt;&gt;"",timeseries!A13,"")</f>
         <v>45398.458333333336</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A14" s="8">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A14" s="5">
         <f>IF(timeseries!A14&lt;&gt;"",timeseries!A14,"")</f>
         <v>45398.5</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A15" s="8">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A15" s="5">
         <f>IF(timeseries!A15&lt;&gt;"",timeseries!A15,"")</f>
         <v>45398.541666666664</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A16" s="8">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A16" s="5">
         <f>IF(timeseries!A16&lt;&gt;"",timeseries!A16,"")</f>
         <v>45398.583333333336</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A17" s="8">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A17" s="5">
         <f>IF(timeseries!A17&lt;&gt;"",timeseries!A17,"")</f>
         <v>45398.625</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A18" s="8">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A18" s="5">
         <f>IF(timeseries!A18&lt;&gt;"",timeseries!A18,"")</f>
         <v>45398.666666666664</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A19" s="8">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A19" s="5">
         <f>IF(timeseries!A19&lt;&gt;"",timeseries!A19,"")</f>
         <v>45398.708333333336</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A20" s="8">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A20" s="5">
         <f>IF(timeseries!A20&lt;&gt;"",timeseries!A20,"")</f>
         <v>45398.75</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A21" s="8">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A21" s="5">
         <f>IF(timeseries!A21&lt;&gt;"",timeseries!A21,"")</f>
         <v>45398.791666666664</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A22" s="8">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A22" s="5">
         <f>IF(timeseries!A22&lt;&gt;"",timeseries!A22,"")</f>
         <v>45398.833333333336</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A23" s="8">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A23" s="5">
         <f>IF(timeseries!A23&lt;&gt;"",timeseries!A23,"")</f>
         <v>45398.875</v>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A24" s="8">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A24" s="5">
         <f>IF(timeseries!A24&lt;&gt;"",timeseries!A24,"")</f>
         <v>45398.916666666664</v>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A25" s="8">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A25" s="5">
         <f>IF(timeseries!A25&lt;&gt;"",timeseries!A25,"")</f>
         <v>45398.958333333336</v>
       </c>
     </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A26" s="8" t="str">
+    <row r="26" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A26" s="5" t="str">
         <f>IF(timeseries!A26&lt;&gt;"",timeseries!A26,"")</f>
         <v/>
       </c>
     </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A27" s="8" t="str">
+    <row r="27" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A27" s="5" t="str">
         <f>IF(timeseries!A27&lt;&gt;"",timeseries!A27,"")</f>
         <v/>
       </c>
     </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A28" s="8" t="str">
+    <row r="28" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A28" s="5" t="str">
         <f>IF(timeseries!A28&lt;&gt;"",timeseries!A28,"")</f>
         <v/>
       </c>
     </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A29" s="8" t="str">
+    <row r="29" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A29" s="5" t="str">
         <f>IF(timeseries!A29&lt;&gt;"",timeseries!A29,"")</f>
         <v/>
       </c>
     </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A30" s="8" t="str">
+    <row r="30" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A30" s="5" t="str">
         <f>IF(timeseries!A30&lt;&gt;"",timeseries!A30,"")</f>
         <v/>
       </c>
     </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A31" s="8" t="str">
+    <row r="31" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A31" s="5" t="str">
         <f>IF(timeseries!A31&lt;&gt;"",timeseries!A31,"")</f>
         <v/>
       </c>
@@ -7362,13 +7374,13 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F0532F8A-0FB4-47AD-98A1-4065D3376432}">
   <dimension ref="A1:B1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:2" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="2" t="s">
         <v>39</v>
       </c>
     </row>
@@ -7380,30 +7392,30 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{77A4637A-7829-48D6-AE54-2E654AB1A427}">
   <dimension ref="A1:L25"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="19.28515625" style="8" customWidth="1"/>
-    <col min="2" max="5" width="12.5703125" bestFit="1" customWidth="1"/>
-    <col min="6" max="8" width="5.5703125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.33203125" style="5" customWidth="1"/>
+    <col min="2" max="5" width="12.5546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="8" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="12.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="2" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A2" s="8">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A2" s="5">
         <f>IF(timeseries!A2&lt;&gt;"",timeseries!A2,"")</f>
         <v>45398</v>
       </c>
@@ -7418,11 +7430,11 @@
         <f>C2</f>
         <v>0.63</v>
       </c>
-      <c r="F2" s="8"/>
-      <c r="L2" s="8"/>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A3" s="8">
+      <c r="F2" s="5"/>
+      <c r="L2" s="5"/>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A3" s="5">
         <f>IF(timeseries!A3&lt;&gt;"",timeseries!A3,"")</f>
         <v>45398.041666666664</v>
       </c>
@@ -7438,8 +7450,8 @@
         <v>0.56000000000000005</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A4" s="8">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A4" s="5">
         <f>IF(timeseries!A4&lt;&gt;"",timeseries!A4,"")</f>
         <v>45398.083333333336</v>
       </c>
@@ -7455,8 +7467,8 @@
         <v>0.55000000000000004</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A5" s="8">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A5" s="5">
         <f>IF(timeseries!A5&lt;&gt;"",timeseries!A5,"")</f>
         <v>45398.125</v>
       </c>
@@ -7472,8 +7484,8 @@
         <v>0.46000000000000008</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A6" s="8">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A6" s="5">
         <f>IF(timeseries!A6&lt;&gt;"",timeseries!A6,"")</f>
         <v>45398.166666666664</v>
       </c>
@@ -7489,8 +7501,8 @@
         <v>0.3600000000000001</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A7" s="8">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A7" s="5">
         <f>IF(timeseries!A7&lt;&gt;"",timeseries!A7,"")</f>
         <v>45398.208333333336</v>
       </c>
@@ -7506,8 +7518,8 @@
         <v>0.28000000000000008</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A8" s="8">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A8" s="5">
         <f>IF(timeseries!A8&lt;&gt;"",timeseries!A8,"")</f>
         <v>45398.25</v>
       </c>
@@ -7523,8 +7535,8 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A9" s="8">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A9" s="5">
         <f>IF(timeseries!A9&lt;&gt;"",timeseries!A9,"")</f>
         <v>45398.291666666664</v>
       </c>
@@ -7540,8 +7552,8 @@
         <v>0.28000000000000003</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A10" s="8">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A10" s="5">
         <f>IF(timeseries!A10&lt;&gt;"",timeseries!A10,"")</f>
         <v>45398.333333333336</v>
       </c>
@@ -7557,8 +7569,8 @@
         <v>0.23000000000000004</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A11" s="8">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A11" s="5">
         <f>IF(timeseries!A11&lt;&gt;"",timeseries!A11,"")</f>
         <v>45398.375</v>
       </c>
@@ -7574,8 +7586,8 @@
         <v>0.23000000000000004</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A12" s="8">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A12" s="5">
         <f>IF(timeseries!A12&lt;&gt;"",timeseries!A12,"")</f>
         <v>45398.416666666664</v>
       </c>
@@ -7591,8 +7603,8 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A13" s="8">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A13" s="5">
         <f>IF(timeseries!A13&lt;&gt;"",timeseries!A13,"")</f>
         <v>45398.458333333336</v>
       </c>
@@ -7608,8 +7620,8 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A14" s="8">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A14" s="5">
         <f>IF(timeseries!A14&lt;&gt;"",timeseries!A14,"")</f>
         <v>45398.5</v>
       </c>
@@ -7623,8 +7635,8 @@
         <v>0.06</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A15" s="8">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A15" s="5">
         <f>IF(timeseries!A15&lt;&gt;"",timeseries!A15,"")</f>
         <v>45398.541666666664</v>
       </c>
@@ -7638,8 +7650,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A16" s="8">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A16" s="5">
         <f>IF(timeseries!A16&lt;&gt;"",timeseries!A16,"")</f>
         <v>45398.583333333336</v>
       </c>
@@ -7653,8 +7665,8 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A17" s="8">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A17" s="5">
         <f>IF(timeseries!A17&lt;&gt;"",timeseries!A17,"")</f>
         <v>45398.625</v>
       </c>
@@ -7668,8 +7680,8 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A18" s="8">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A18" s="5">
         <f>IF(timeseries!A18&lt;&gt;"",timeseries!A18,"")</f>
         <v>45398.666666666664</v>
       </c>
@@ -7683,8 +7695,8 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A19" s="8">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A19" s="5">
         <f>IF(timeseries!A19&lt;&gt;"",timeseries!A19,"")</f>
         <v>45398.708333333336</v>
       </c>
@@ -7698,8 +7710,8 @@
         <v>2.0000000000000004E-2</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A20" s="8">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A20" s="5">
         <f>IF(timeseries!A20&lt;&gt;"",timeseries!A20,"")</f>
         <v>45398.75</v>
       </c>
@@ -7713,8 +7725,8 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A21" s="8">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A21" s="5">
         <f>IF(timeseries!A21&lt;&gt;"",timeseries!A21,"")</f>
         <v>45398.791666666664</v>
       </c>
@@ -7728,8 +7740,8 @@
         <v>0.14000000000000001</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A22" s="8">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A22" s="5">
         <f>IF(timeseries!A22&lt;&gt;"",timeseries!A22,"")</f>
         <v>45398.833333333336</v>
       </c>
@@ -7743,8 +7755,8 @@
         <v>0.13</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A23" s="8">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A23" s="5">
         <f>IF(timeseries!A23&lt;&gt;"",timeseries!A23,"")</f>
         <v>45398.875</v>
       </c>
@@ -7758,8 +7770,8 @@
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A24" s="8">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A24" s="5">
         <f>IF(timeseries!A24&lt;&gt;"",timeseries!A24,"")</f>
         <v>45398.916666666664</v>
       </c>
@@ -7773,8 +7785,8 @@
         <v>0.11000000000000001</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A25" s="8">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A25" s="5">
         <f>IF(timeseries!A25&lt;&gt;"",timeseries!A25,"")</f>
         <v>45398.958333333336</v>
       </c>
@@ -7799,29 +7811,29 @@
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1F87DD44-A1AD-4241-AED7-C48CC9DEE2E2}">
   <dimension ref="A1:G25"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="19.28515625" style="8" customWidth="1"/>
-    <col min="4" max="6" width="10.42578125" customWidth="1"/>
-    <col min="7" max="7" width="10.42578125" style="1" customWidth="1"/>
+    <col min="1" max="1" width="19.33203125" style="5" customWidth="1"/>
+    <col min="4" max="6" width="10.44140625" customWidth="1"/>
+    <col min="7" max="7" width="10.44140625" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="2" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2" s="8">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A2" s="5">
         <f>IF(timeseries!A2&lt;&gt;"",timeseries!A2,"")</f>
         <v>45398</v>
       </c>
@@ -7838,8 +7850,8 @@
       </c>
       <c r="G2"/>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="8">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A3" s="5">
         <f>IF(timeseries!A3&lt;&gt;"",timeseries!A3,"")</f>
         <v>45398.041666666664</v>
       </c>
@@ -7856,8 +7868,8 @@
       </c>
       <c r="G3"/>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" s="8">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A4" s="5">
         <f>IF(timeseries!A4&lt;&gt;"",timeseries!A4,"")</f>
         <v>45398.083333333336</v>
       </c>
@@ -7874,8 +7886,8 @@
       </c>
       <c r="G4"/>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="8">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A5" s="5">
         <f>IF(timeseries!A5&lt;&gt;"",timeseries!A5,"")</f>
         <v>45398.125</v>
       </c>
@@ -7892,8 +7904,8 @@
       </c>
       <c r="G5"/>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="8">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A6" s="5">
         <f>IF(timeseries!A6&lt;&gt;"",timeseries!A6,"")</f>
         <v>45398.166666666664</v>
       </c>
@@ -7910,8 +7922,8 @@
       </c>
       <c r="G6"/>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="8">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A7" s="5">
         <f>IF(timeseries!A7&lt;&gt;"",timeseries!A7,"")</f>
         <v>45398.208333333336</v>
       </c>
@@ -7928,8 +7940,8 @@
       </c>
       <c r="G7"/>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="8">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A8" s="5">
         <f>IF(timeseries!A8&lt;&gt;"",timeseries!A8,"")</f>
         <v>45398.25</v>
       </c>
@@ -7946,8 +7958,8 @@
       </c>
       <c r="G8"/>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="8">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A9" s="5">
         <f>IF(timeseries!A9&lt;&gt;"",timeseries!A9,"")</f>
         <v>45398.291666666664</v>
       </c>
@@ -7964,8 +7976,8 @@
       </c>
       <c r="G9"/>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="8">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A10" s="5">
         <f>IF(timeseries!A10&lt;&gt;"",timeseries!A10,"")</f>
         <v>45398.333333333336</v>
       </c>
@@ -7982,8 +7994,8 @@
       </c>
       <c r="G10"/>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" s="8">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A11" s="5">
         <f>IF(timeseries!A11&lt;&gt;"",timeseries!A11,"")</f>
         <v>45398.375</v>
       </c>
@@ -8000,8 +8012,8 @@
       </c>
       <c r="G11"/>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A12" s="8">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A12" s="5">
         <f>IF(timeseries!A12&lt;&gt;"",timeseries!A12,"")</f>
         <v>45398.416666666664</v>
       </c>
@@ -8018,8 +8030,8 @@
       </c>
       <c r="G12"/>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" s="8">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A13" s="5">
         <f>IF(timeseries!A13&lt;&gt;"",timeseries!A13,"")</f>
         <v>45398.458333333336</v>
       </c>
@@ -8036,8 +8048,8 @@
       </c>
       <c r="G13"/>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A14" s="8">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A14" s="5">
         <f>IF(timeseries!A14&lt;&gt;"",timeseries!A14,"")</f>
         <v>45398.5</v>
       </c>
@@ -8052,8 +8064,8 @@
       </c>
       <c r="G14"/>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A15" s="8">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A15" s="5">
         <f>IF(timeseries!A15&lt;&gt;"",timeseries!A15,"")</f>
         <v>45398.541666666664</v>
       </c>
@@ -8068,8 +8080,8 @@
       </c>
       <c r="G15"/>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A16" s="8">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A16" s="5">
         <f>IF(timeseries!A16&lt;&gt;"",timeseries!A16,"")</f>
         <v>45398.583333333336</v>
       </c>
@@ -8084,8 +8096,8 @@
       </c>
       <c r="G16"/>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A17" s="8">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A17" s="5">
         <f>IF(timeseries!A17&lt;&gt;"",timeseries!A17,"")</f>
         <v>45398.625</v>
       </c>
@@ -8100,8 +8112,8 @@
       </c>
       <c r="G17"/>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A18" s="8">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A18" s="5">
         <f>IF(timeseries!A18&lt;&gt;"",timeseries!A18,"")</f>
         <v>45398.666666666664</v>
       </c>
@@ -8116,8 +8128,8 @@
       </c>
       <c r="G18"/>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A19" s="8">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A19" s="5">
         <f>IF(timeseries!A19&lt;&gt;"",timeseries!A19,"")</f>
         <v>45398.708333333336</v>
       </c>
@@ -8132,8 +8144,8 @@
       </c>
       <c r="G19"/>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A20" s="8">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A20" s="5">
         <f>IF(timeseries!A20&lt;&gt;"",timeseries!A20,"")</f>
         <v>45398.75</v>
       </c>
@@ -8148,8 +8160,8 @@
       </c>
       <c r="G20"/>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A21" s="8">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A21" s="5">
         <f>IF(timeseries!A21&lt;&gt;"",timeseries!A21,"")</f>
         <v>45398.791666666664</v>
       </c>
@@ -8164,8 +8176,8 @@
       </c>
       <c r="G21"/>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A22" s="8">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A22" s="5">
         <f>IF(timeseries!A22&lt;&gt;"",timeseries!A22,"")</f>
         <v>45398.833333333336</v>
       </c>
@@ -8180,8 +8192,8 @@
       </c>
       <c r="G22"/>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A23" s="8">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A23" s="5">
         <f>IF(timeseries!A23&lt;&gt;"",timeseries!A23,"")</f>
         <v>45398.875</v>
       </c>
@@ -8196,8 +8208,8 @@
       </c>
       <c r="G23"/>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A24" s="8">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A24" s="5">
         <f>IF(timeseries!A24&lt;&gt;"",timeseries!A24,"")</f>
         <v>45398.916666666664</v>
       </c>
@@ -8212,8 +8224,8 @@
       </c>
       <c r="G24"/>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A25" s="8">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A25" s="5">
         <f>IF(timeseries!A25&lt;&gt;"",timeseries!A25,"")</f>
         <v>45398.958333333336</v>
       </c>
@@ -8239,86 +8251,86 @@
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E44A96C9-CA4B-4735-AF1E-65BD86DB3657}">
   <dimension ref="A1:F17"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="3" max="6" width="13.28515625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.7109375" customWidth="1"/>
+    <col min="3" max="6" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
-      <c r="C2" s="8"/>
-      <c r="E2" s="8"/>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="C2" s="5"/>
+      <c r="E2" s="5"/>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2</v>
       </c>
-      <c r="C3" s="8"/>
-      <c r="E3" s="8"/>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="C3" s="5"/>
+      <c r="E3" s="5"/>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>3</v>
       </c>
-      <c r="C4" s="8"/>
-      <c r="E4" s="8"/>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="C4" s="5"/>
+      <c r="E4" s="5"/>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>4</v>
       </c>
-      <c r="C5" s="8"/>
-      <c r="E5" s="8"/>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="C5" s="5"/>
+      <c r="E5" s="5"/>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>10</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="C15" s="8"/>
-      <c r="D15" s="8"/>
-      <c r="E15" s="8"/>
-      <c r="F15" s="8"/>
-    </row>
-    <row r="17" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="C17" s="8"/>
-      <c r="D17" s="8"/>
-      <c r="E17" s="8"/>
-      <c r="F17" s="8"/>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="C15" s="5"/>
+      <c r="D15" s="5"/>
+      <c r="E15" s="5"/>
+      <c r="F15" s="5"/>
+    </row>
+    <row r="17" spans="3:6" x14ac:dyDescent="0.3">
+      <c r="C17" s="5"/>
+      <c r="D17" s="5"/>
+      <c r="E17" s="5"/>
+      <c r="F17" s="5"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -8326,38 +8338,72 @@
 </file>
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0B25A1A0-0B9E-4920-9C7F-E13769DD6437}">
+  <dimension ref="A1:F1"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="12.44140625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>151</v>
+      </c>
+      <c r="B1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" t="s">
+        <v>152</v>
+      </c>
+      <c r="D1" t="s">
+        <v>153</v>
+      </c>
+      <c r="E1" t="s">
+        <v>154</v>
+      </c>
+      <c r="F1" t="s">
+        <v>155</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{02307C1F-427B-487D-B703-EBF512D7AC27}">
   <dimension ref="A1:G25"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="19.28515625" style="8" customWidth="1"/>
+    <col min="1" max="1" width="19.33203125" style="5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="2" t="s">
         <v>139</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="2" t="s">
         <v>141</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="2" t="s">
         <v>140</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="2" t="s">
         <v>143</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" s="2" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2" s="8">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A2" s="5">
         <f>IF(timeseries!A2&lt;&gt;"",timeseries!A2,"")</f>
         <v>45398</v>
       </c>
@@ -8380,8 +8426,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="8">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A3" s="5">
         <f>IF(timeseries!A3&lt;&gt;"",timeseries!A3,"")</f>
         <v>45398.041666666664</v>
       </c>
@@ -8404,8 +8450,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" s="8">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A4" s="5">
         <f>IF(timeseries!A4&lt;&gt;"",timeseries!A4,"")</f>
         <v>45398.083333333336</v>
       </c>
@@ -8428,8 +8474,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="8">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A5" s="5">
         <f>IF(timeseries!A5&lt;&gt;"",timeseries!A5,"")</f>
         <v>45398.125</v>
       </c>
@@ -8452,8 +8498,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="8">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A6" s="5">
         <f>IF(timeseries!A6&lt;&gt;"",timeseries!A6,"")</f>
         <v>45398.166666666664</v>
       </c>
@@ -8476,8 +8522,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="8">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A7" s="5">
         <f>IF(timeseries!A7&lt;&gt;"",timeseries!A7,"")</f>
         <v>45398.208333333336</v>
       </c>
@@ -8500,8 +8546,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="8">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A8" s="5">
         <f>IF(timeseries!A8&lt;&gt;"",timeseries!A8,"")</f>
         <v>45398.25</v>
       </c>
@@ -8524,8 +8570,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="8">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A9" s="5">
         <f>IF(timeseries!A9&lt;&gt;"",timeseries!A9,"")</f>
         <v>45398.291666666664</v>
       </c>
@@ -8548,8 +8594,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="8">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A10" s="5">
         <f>IF(timeseries!A10&lt;&gt;"",timeseries!A10,"")</f>
         <v>45398.333333333336</v>
       </c>
@@ -8572,8 +8618,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" s="8">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A11" s="5">
         <f>IF(timeseries!A11&lt;&gt;"",timeseries!A11,"")</f>
         <v>45398.375</v>
       </c>
@@ -8596,8 +8642,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A12" s="8">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A12" s="5">
         <f>IF(timeseries!A12&lt;&gt;"",timeseries!A12,"")</f>
         <v>45398.416666666664</v>
       </c>
@@ -8620,8 +8666,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" s="8">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A13" s="5">
         <f>IF(timeseries!A13&lt;&gt;"",timeseries!A13,"")</f>
         <v>45398.458333333336</v>
       </c>
@@ -8644,8 +8690,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A14" s="8">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A14" s="5">
         <f>IF(timeseries!A14&lt;&gt;"",timeseries!A14,"")</f>
         <v>45398.5</v>
       </c>
@@ -8668,8 +8714,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A15" s="8">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A15" s="5">
         <f>IF(timeseries!A15&lt;&gt;"",timeseries!A15,"")</f>
         <v>45398.541666666664</v>
       </c>
@@ -8692,8 +8738,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A16" s="8">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A16" s="5">
         <f>IF(timeseries!A16&lt;&gt;"",timeseries!A16,"")</f>
         <v>45398.583333333336</v>
       </c>
@@ -8716,8 +8762,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A17" s="8">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A17" s="5">
         <f>IF(timeseries!A17&lt;&gt;"",timeseries!A17,"")</f>
         <v>45398.625</v>
       </c>
@@ -8740,8 +8786,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A18" s="8">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A18" s="5">
         <f>IF(timeseries!A18&lt;&gt;"",timeseries!A18,"")</f>
         <v>45398.666666666664</v>
       </c>
@@ -8764,8 +8810,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A19" s="8">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A19" s="5">
         <f>IF(timeseries!A19&lt;&gt;"",timeseries!A19,"")</f>
         <v>45398.708333333336</v>
       </c>
@@ -8788,8 +8834,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A20" s="8">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A20" s="5">
         <f>IF(timeseries!A20&lt;&gt;"",timeseries!A20,"")</f>
         <v>45398.75</v>
       </c>
@@ -8812,8 +8858,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A21" s="8">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A21" s="5">
         <f>IF(timeseries!A21&lt;&gt;"",timeseries!A21,"")</f>
         <v>45398.791666666664</v>
       </c>
@@ -8836,8 +8882,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A22" s="8">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A22" s="5">
         <f>IF(timeseries!A22&lt;&gt;"",timeseries!A22,"")</f>
         <v>45398.833333333336</v>
       </c>
@@ -8860,8 +8906,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A23" s="8">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A23" s="5">
         <f>IF(timeseries!A23&lt;&gt;"",timeseries!A23,"")</f>
         <v>45398.875</v>
       </c>
@@ -8884,8 +8930,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A24" s="8">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A24" s="5">
         <f>IF(timeseries!A24&lt;&gt;"",timeseries!A24,"")</f>
         <v>45398.916666666664</v>
       </c>
@@ -8908,8 +8954,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A25" s="8">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A25" s="5">
         <f>IF(timeseries!A25&lt;&gt;"",timeseries!A25,"")</f>
         <v>45398.958333333336</v>
       </c>
@@ -8938,104 +8984,104 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B3788A93-7501-4F5D-9E8F-38D329CC85EC}">
   <dimension ref="A1:L5"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="11" style="7" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="7.7109375" style="7" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="5.5703125" style="7" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.85546875" style="7" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.28515625" style="7" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.42578125" style="7" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.7109375" style="7" bestFit="1" customWidth="1"/>
-    <col min="8" max="16384" width="9.140625" style="7"/>
+    <col min="1" max="1" width="11" style="4" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="7.6640625" style="4" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="5.5546875" style="4" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.88671875" style="4" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.33203125" style="4" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.44140625" style="4" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.6640625" style="4" bestFit="1" customWidth="1"/>
+    <col min="8" max="16384" width="9.109375" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="2" t="s">
         <v>147</v>
       </c>
-      <c r="C1" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="D1" s="3" t="s">
+      <c r="C1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="F1" s="6" t="s">
+      <c r="F1" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="I1" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="J1" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="K1" s="3" t="s">
+      <c r="K1" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="L1" s="3" t="s">
+      <c r="L1" s="2" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A2" s="7" t="s">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A2" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="B2" s="7" t="s">
+      <c r="B2" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="C2" s="7" t="s">
+      <c r="C2" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="7" t="s">
+      <c r="D2" s="4" t="s">
         <v>82</v>
       </c>
-      <c r="E2" s="7" t="s">
+      <c r="E2" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="F2" s="7">
-        <v>0</v>
-      </c>
-      <c r="G2" s="7" t="s">
+      <c r="F2" s="4">
+        <v>0</v>
+      </c>
+      <c r="G2" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="H2" s="7">
+      <c r="H2" s="4">
         <v>1</v>
       </c>
       <c r="I2">
         <v>0</v>
       </c>
-      <c r="J2" s="7">
-        <v>0</v>
-      </c>
-      <c r="K2" s="7">
-        <v>0</v>
-      </c>
-      <c r="L2" s="7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="J2" s="4">
+        <v>0</v>
+      </c>
+      <c r="K2" s="4">
+        <v>0</v>
+      </c>
+      <c r="L2" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
       <c r="I3"/>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
       <c r="I4"/>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
       <c r="I5"/>
     </row>
   </sheetData>
@@ -9044,196 +9090,196 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A3E266E0-7523-413E-8B0C-F3E2413808A5}">
   <dimension ref="A1:A31"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="19.28515625" style="8" customWidth="1"/>
-    <col min="2" max="3" width="6.5703125" customWidth="1"/>
+    <col min="1" max="1" width="19.33203125" style="5" customWidth="1"/>
+    <col min="2" max="3" width="6.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1" s="2" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A2" s="8">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A2" s="5">
         <f>IF(timeseries!A2&lt;&gt;"",timeseries!A2,"")</f>
         <v>45398</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A3" s="8">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A3" s="5">
         <f>IF(timeseries!A3&lt;&gt;"",timeseries!A3,"")</f>
         <v>45398.041666666664</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A4" s="8">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A4" s="5">
         <f>IF(timeseries!A4&lt;&gt;"",timeseries!A4,"")</f>
         <v>45398.083333333336</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A5" s="8">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A5" s="5">
         <f>IF(timeseries!A5&lt;&gt;"",timeseries!A5,"")</f>
         <v>45398.125</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A6" s="8">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6" s="5">
         <f>IF(timeseries!A6&lt;&gt;"",timeseries!A6,"")</f>
         <v>45398.166666666664</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A7" s="8">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A7" s="5">
         <f>IF(timeseries!A7&lt;&gt;"",timeseries!A7,"")</f>
         <v>45398.208333333336</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A8" s="8">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A8" s="5">
         <f>IF(timeseries!A8&lt;&gt;"",timeseries!A8,"")</f>
         <v>45398.25</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A9" s="8">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A9" s="5">
         <f>IF(timeseries!A9&lt;&gt;"",timeseries!A9,"")</f>
         <v>45398.291666666664</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A10" s="8">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A10" s="5">
         <f>IF(timeseries!A10&lt;&gt;"",timeseries!A10,"")</f>
         <v>45398.333333333336</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A11" s="8">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A11" s="5">
         <f>IF(timeseries!A11&lt;&gt;"",timeseries!A11,"")</f>
         <v>45398.375</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A12" s="8">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A12" s="5">
         <f>IF(timeseries!A12&lt;&gt;"",timeseries!A12,"")</f>
         <v>45398.416666666664</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A13" s="8">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A13" s="5">
         <f>IF(timeseries!A13&lt;&gt;"",timeseries!A13,"")</f>
         <v>45398.458333333336</v>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A14" s="8">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A14" s="5">
         <f>IF(timeseries!A14&lt;&gt;"",timeseries!A14,"")</f>
         <v>45398.5</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A15" s="8">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A15" s="5">
         <f>IF(timeseries!A15&lt;&gt;"",timeseries!A15,"")</f>
         <v>45398.541666666664</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A16" s="8">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A16" s="5">
         <f>IF(timeseries!A16&lt;&gt;"",timeseries!A16,"")</f>
         <v>45398.583333333336</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A17" s="8">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A17" s="5">
         <f>IF(timeseries!A17&lt;&gt;"",timeseries!A17,"")</f>
         <v>45398.625</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A18" s="8">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A18" s="5">
         <f>IF(timeseries!A18&lt;&gt;"",timeseries!A18,"")</f>
         <v>45398.666666666664</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A19" s="8">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A19" s="5">
         <f>IF(timeseries!A19&lt;&gt;"",timeseries!A19,"")</f>
         <v>45398.708333333336</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A20" s="8">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A20" s="5">
         <f>IF(timeseries!A20&lt;&gt;"",timeseries!A20,"")</f>
         <v>45398.75</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A21" s="8">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A21" s="5">
         <f>IF(timeseries!A21&lt;&gt;"",timeseries!A21,"")</f>
         <v>45398.791666666664</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A22" s="8">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A22" s="5">
         <f>IF(timeseries!A22&lt;&gt;"",timeseries!A22,"")</f>
         <v>45398.833333333336</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A23" s="8">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A23" s="5">
         <f>IF(timeseries!A23&lt;&gt;"",timeseries!A23,"")</f>
         <v>45398.875</v>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A24" s="8">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A24" s="5">
         <f>IF(timeseries!A24&lt;&gt;"",timeseries!A24,"")</f>
         <v>45398.916666666664</v>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A25" s="8">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A25" s="5">
         <f>IF(timeseries!A25&lt;&gt;"",timeseries!A25,"")</f>
         <v>45398.958333333336</v>
       </c>
     </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A26" s="8" t="str">
+    <row r="26" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A26" s="5" t="str">
         <f>IF(timeseries!A26&lt;&gt;"",timeseries!A26,"")</f>
         <v/>
       </c>
     </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A27" s="8" t="str">
+    <row r="27" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A27" s="5" t="str">
         <f>IF(timeseries!A27&lt;&gt;"",timeseries!A27,"")</f>
         <v/>
       </c>
     </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A28" s="8" t="str">
+    <row r="28" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A28" s="5" t="str">
         <f>IF(timeseries!A28&lt;&gt;"",timeseries!A28,"")</f>
         <v/>
       </c>
     </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A29" s="8" t="str">
+    <row r="29" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A29" s="5" t="str">
         <f>IF(timeseries!A29&lt;&gt;"",timeseries!A29,"")</f>
         <v/>
       </c>
     </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A30" s="8" t="str">
+    <row r="30" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A30" s="5" t="str">
         <f>IF(timeseries!A30&lt;&gt;"",timeseries!A30,"")</f>
         <v/>
       </c>
     </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A31" s="8" t="str">
+    <row r="31" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A31" s="5" t="str">
         <f>IF(timeseries!A31&lt;&gt;"",timeseries!A31,"")</f>
         <v/>
       </c>
@@ -9243,33 +9289,33 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EF6DDD9A-EF34-4108-8532-230729E9C708}">
   <dimension ref="A1:D31"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="19.28515625" style="8" customWidth="1"/>
-    <col min="2" max="4" width="11.42578125" customWidth="1"/>
-    <col min="5" max="6" width="11.140625" customWidth="1"/>
-    <col min="8" max="10" width="11.140625" customWidth="1"/>
+    <col min="1" max="1" width="19.33203125" style="5" customWidth="1"/>
+    <col min="2" max="4" width="11.44140625" customWidth="1"/>
+    <col min="5" max="6" width="11.109375" customWidth="1"/>
+    <col min="8" max="10" width="11.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="2" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" s="8">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A2" s="5">
         <f>IF(timeseries!A2&lt;&gt;"",timeseries!A2,"")</f>
         <v>45398</v>
       </c>
@@ -9284,8 +9330,8 @@
         <v>59.25</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3" s="8">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A3" s="5">
         <f>IF(timeseries!A3&lt;&gt;"",timeseries!A3,"")</f>
         <v>45398.041666666664</v>
       </c>
@@ -9300,8 +9346,8 @@
         <v>47.58</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" s="8">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A4" s="5">
         <f>IF(timeseries!A4&lt;&gt;"",timeseries!A4,"")</f>
         <v>45398.083333333336</v>
       </c>
@@ -9316,8 +9362,8 @@
         <v>52.53</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" s="8">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A5" s="5">
         <f>IF(timeseries!A5&lt;&gt;"",timeseries!A5,"")</f>
         <v>45398.125</v>
       </c>
@@ -9332,8 +9378,8 @@
         <v>55.879999999999995</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" s="8">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A6" s="5">
         <f>IF(timeseries!A6&lt;&gt;"",timeseries!A6,"")</f>
         <v>45398.166666666664</v>
       </c>
@@ -9348,8 +9394,8 @@
         <v>53.54</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A7" s="8">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A7" s="5">
         <f>IF(timeseries!A7&lt;&gt;"",timeseries!A7,"")</f>
         <v>45398.208333333336</v>
       </c>
@@ -9364,8 +9410,8 @@
         <v>62.91</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A8" s="8">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A8" s="5">
         <f>IF(timeseries!A8&lt;&gt;"",timeseries!A8,"")</f>
         <v>45398.25</v>
       </c>
@@ -9380,8 +9426,8 @@
         <v>89.56</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A9" s="8">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A9" s="5">
         <f>IF(timeseries!A9&lt;&gt;"",timeseries!A9,"")</f>
         <v>45398.291666666664</v>
       </c>
@@ -9396,8 +9442,8 @@
         <v>89.22</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A10" s="8">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A10" s="5">
         <f>IF(timeseries!A10&lt;&gt;"",timeseries!A10,"")</f>
         <v>45398.333333333336</v>
       </c>
@@ -9412,8 +9458,8 @@
         <v>77.22</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A11" s="8">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A11" s="5">
         <f>IF(timeseries!A11&lt;&gt;"",timeseries!A11,"")</f>
         <v>45398.375</v>
       </c>
@@ -9428,8 +9474,8 @@
         <v>80.3</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A12" s="8">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A12" s="5">
         <f>IF(timeseries!A12&lt;&gt;"",timeseries!A12,"")</f>
         <v>45398.416666666664</v>
       </c>
@@ -9444,8 +9490,8 @@
         <v>85.23</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A13" s="8">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A13" s="5">
         <f>IF(timeseries!A13&lt;&gt;"",timeseries!A13,"")</f>
         <v>45398.458333333336</v>
       </c>
@@ -9460,8 +9506,8 @@
         <v>80.87</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A14" s="8">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A14" s="5">
         <f>IF(timeseries!A14&lt;&gt;"",timeseries!A14,"")</f>
         <v>45398.5</v>
       </c>
@@ -9475,8 +9521,8 @@
         <v>81.430000000000007</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A15" s="8">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A15" s="5">
         <f>IF(timeseries!A15&lt;&gt;"",timeseries!A15,"")</f>
         <v>45398.541666666664</v>
       </c>
@@ -9490,8 +9536,8 @@
         <v>99.39</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A16" s="8">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A16" s="5">
         <f>IF(timeseries!A16&lt;&gt;"",timeseries!A16,"")</f>
         <v>45398.583333333336</v>
       </c>
@@ -9505,8 +9551,8 @@
         <v>96.43</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A17" s="8">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A17" s="5">
         <f>IF(timeseries!A17&lt;&gt;"",timeseries!A17,"")</f>
         <v>45398.625</v>
       </c>
@@ -9520,8 +9566,8 @@
         <v>101.3</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A18" s="8">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A18" s="5">
         <f>IF(timeseries!A18&lt;&gt;"",timeseries!A18,"")</f>
         <v>45398.666666666664</v>
       </c>
@@ -9535,8 +9581,8 @@
         <v>103.32</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A19" s="8">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A19" s="5">
         <f>IF(timeseries!A19&lt;&gt;"",timeseries!A19,"")</f>
         <v>45398.708333333336</v>
       </c>
@@ -9550,8 +9596,8 @@
         <v>100.25</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A20" s="8">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A20" s="5">
         <f>IF(timeseries!A20&lt;&gt;"",timeseries!A20,"")</f>
         <v>45398.75</v>
       </c>
@@ -9565,8 +9611,8 @@
         <v>101.93</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A21" s="8">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A21" s="5">
         <f>IF(timeseries!A21&lt;&gt;"",timeseries!A21,"")</f>
         <v>45398.791666666664</v>
       </c>
@@ -9580,8 +9626,8 @@
         <v>97.08</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A22" s="8">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A22" s="5">
         <f>IF(timeseries!A22&lt;&gt;"",timeseries!A22,"")</f>
         <v>45398.833333333336</v>
       </c>
@@ -9595,8 +9641,8 @@
         <v>96.789999999999992</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A23" s="8">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A23" s="5">
         <f>IF(timeseries!A23&lt;&gt;"",timeseries!A23,"")</f>
         <v>45398.875</v>
       </c>
@@ -9610,8 +9656,8 @@
         <v>91.75</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A24" s="8">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A24" s="5">
         <f>IF(timeseries!A24&lt;&gt;"",timeseries!A24,"")</f>
         <v>45398.916666666664</v>
       </c>
@@ -9625,8 +9671,8 @@
         <v>89.15</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A25" s="8">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A25" s="5">
         <f>IF(timeseries!A25&lt;&gt;"",timeseries!A25,"")</f>
         <v>45398.958333333336</v>
       </c>
@@ -9640,38 +9686,38 @@
         <v>88.71</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A26" s="8" t="str">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A26" s="5" t="str">
         <f>IF(timeseries!A26&lt;&gt;"",timeseries!A26,"")</f>
         <v/>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A27" s="8" t="str">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A27" s="5" t="str">
         <f>IF(timeseries!A27&lt;&gt;"",timeseries!A27,"")</f>
         <v/>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A28" s="8" t="str">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A28" s="5" t="str">
         <f>IF(timeseries!A28&lt;&gt;"",timeseries!A28,"")</f>
         <v/>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A29" s="8" t="str">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A29" s="5" t="str">
         <f>IF(timeseries!A29&lt;&gt;"",timeseries!A29,"")</f>
         <v/>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A30" s="8" t="str">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A30" s="5" t="str">
         <f>IF(timeseries!A30&lt;&gt;"",timeseries!A30,"")</f>
         <v/>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A31" s="8" t="str">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A31" s="5" t="str">
         <f>IF(timeseries!A31&lt;&gt;"",timeseries!A31,"")</f>
         <v/>
       </c>
@@ -9684,43 +9730,146 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AB98B755-8BE1-4837-9877-4DDB59C80C3F}">
+  <dimension ref="A1:B11"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="27" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>97</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>98</v>
+      </c>
+      <c r="B3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>99</v>
+      </c>
+      <c r="B4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>100</v>
+      </c>
+      <c r="B5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>126</v>
+      </c>
+      <c r="B6">
+        <v>10000000</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>101</v>
+      </c>
+      <c r="B7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>127</v>
+      </c>
+      <c r="B8">
+        <v>10000000</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>149</v>
+      </c>
+      <c r="B9">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>150</v>
+      </c>
+      <c r="B10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>102</v>
+      </c>
+      <c r="B11" t="s">
+        <v>138</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{817FDE8F-BC70-48D0-8376-FB52E6946AF1}">
   <dimension ref="A1:H33"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="14.28515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="9.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.7109375" customWidth="1"/>
-    <col min="5" max="6" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="9.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.6640625" customWidth="1"/>
+    <col min="5" max="6" width="10.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A1" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="H1" s="3"/>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A2" s="8">
+      <c r="H1" s="2"/>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2" s="5">
         <f>IF(timeseries!A2&lt;&gt;"",timeseries!A2,"")</f>
         <v>45398</v>
       </c>
@@ -9749,8 +9898,8 @@
         <v>59.24</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A3" s="8">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3" s="5">
         <f>IF(timeseries!A3&lt;&gt;"",timeseries!A3,"")</f>
         <v>45398.041666666664</v>
       </c>
@@ -9779,8 +9928,8 @@
         <v>47.57</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A4" s="8">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A4" s="5">
         <f>IF(timeseries!A4&lt;&gt;"",timeseries!A4,"")</f>
         <v>45398.083333333336</v>
       </c>
@@ -9809,8 +9958,8 @@
         <v>52.52</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A5" s="8">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A5" s="5">
         <f>IF(timeseries!A5&lt;&gt;"",timeseries!A5,"")</f>
         <v>45398.125</v>
       </c>
@@ -9839,8 +9988,8 @@
         <v>55.87</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A6" s="8">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A6" s="5">
         <f>IF(timeseries!A6&lt;&gt;"",timeseries!A6,"")</f>
         <v>45398.166666666664</v>
       </c>
@@ -9869,8 +10018,8 @@
         <v>53.53</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A7" s="8">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A7" s="5">
         <f>IF(timeseries!A7&lt;&gt;"",timeseries!A7,"")</f>
         <v>45398.208333333336</v>
       </c>
@@ -9899,8 +10048,8 @@
         <v>62.9</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A8" s="8">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A8" s="5">
         <f>IF(timeseries!A8&lt;&gt;"",timeseries!A8,"")</f>
         <v>45398.25</v>
       </c>
@@ -9929,8 +10078,8 @@
         <v>89.55</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A9" s="8">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A9" s="5">
         <f>IF(timeseries!A9&lt;&gt;"",timeseries!A9,"")</f>
         <v>45398.291666666664</v>
       </c>
@@ -9959,8 +10108,8 @@
         <v>89.21</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A10" s="8">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A10" s="5">
         <f>IF(timeseries!A10&lt;&gt;"",timeseries!A10,"")</f>
         <v>45398.333333333336</v>
       </c>
@@ -9989,8 +10138,8 @@
         <v>77.209999999999994</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A11" s="8">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A11" s="5">
         <f>IF(timeseries!A11&lt;&gt;"",timeseries!A11,"")</f>
         <v>45398.375</v>
       </c>
@@ -10019,8 +10168,8 @@
         <v>80.289999999999992</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A12" s="8">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A12" s="5">
         <f>IF(timeseries!A12&lt;&gt;"",timeseries!A12,"")</f>
         <v>45398.416666666664</v>
       </c>
@@ -10049,8 +10198,8 @@
         <v>85.22</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A13" s="8">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A13" s="5">
         <f>IF(timeseries!A13&lt;&gt;"",timeseries!A13,"")</f>
         <v>45398.458333333336</v>
       </c>
@@ -10079,8 +10228,8 @@
         <v>80.86</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A14" s="8">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A14" s="5">
         <f>IF(timeseries!A14&lt;&gt;"",timeseries!A14,"")</f>
         <v>45398.5</v>
       </c>
@@ -10109,8 +10258,8 @@
         <v>81.42</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A15" s="8">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A15" s="5">
         <f>IF(timeseries!A15&lt;&gt;"",timeseries!A15,"")</f>
         <v>45398.541666666664</v>
       </c>
@@ -10139,8 +10288,8 @@
         <v>99.38</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A16" s="8">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A16" s="5">
         <f>IF(timeseries!A16&lt;&gt;"",timeseries!A16,"")</f>
         <v>45398.583333333336</v>
       </c>
@@ -10169,8 +10318,8 @@
         <v>96.42</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A17" s="8">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A17" s="5">
         <f>IF(timeseries!A17&lt;&gt;"",timeseries!A17,"")</f>
         <v>45398.625</v>
       </c>
@@ -10199,8 +10348,8 @@
         <v>101.28999999999999</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A18" s="8">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A18" s="5">
         <f>IF(timeseries!A18&lt;&gt;"",timeseries!A18,"")</f>
         <v>45398.666666666664</v>
       </c>
@@ -10229,8 +10378,8 @@
         <v>103.30999999999999</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A19" s="8">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A19" s="5">
         <f>IF(timeseries!A19&lt;&gt;"",timeseries!A19,"")</f>
         <v>45398.708333333336</v>
       </c>
@@ -10259,8 +10408,8 @@
         <v>100.24</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A20" s="8">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A20" s="5">
         <f>IF(timeseries!A20&lt;&gt;"",timeseries!A20,"")</f>
         <v>45398.75</v>
       </c>
@@ -10289,8 +10438,8 @@
         <v>101.92</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A21" s="8">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A21" s="5">
         <f>IF(timeseries!A21&lt;&gt;"",timeseries!A21,"")</f>
         <v>45398.791666666664</v>
       </c>
@@ -10319,8 +10468,8 @@
         <v>97.07</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A22" s="8">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A22" s="5">
         <f>IF(timeseries!A22&lt;&gt;"",timeseries!A22,"")</f>
         <v>45398.833333333336</v>
       </c>
@@ -10349,8 +10498,8 @@
         <v>96.779999999999987</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A23" s="8">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A23" s="5">
         <f>IF(timeseries!A23&lt;&gt;"",timeseries!A23,"")</f>
         <v>45398.875</v>
       </c>
@@ -10379,8 +10528,8 @@
         <v>91.74</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A24" s="8">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A24" s="5">
         <f>IF(timeseries!A24&lt;&gt;"",timeseries!A24,"")</f>
         <v>45398.916666666664</v>
       </c>
@@ -10409,8 +10558,8 @@
         <v>89.14</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A25" s="8">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A25" s="5">
         <f>IF(timeseries!A25&lt;&gt;"",timeseries!A25,"")</f>
         <v>45398.958333333336</v>
       </c>
@@ -10439,50 +10588,50 @@
         <v>88.699999999999989</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A26" s="8" t="str">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A26" s="5" t="str">
         <f>IF(timeseries!A26&lt;&gt;"",timeseries!A26,"")</f>
         <v/>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A27" s="8" t="str">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A27" s="5" t="str">
         <f>IF(timeseries!A27&lt;&gt;"",timeseries!A27,"")</f>
         <v/>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A28" s="8" t="str">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A28" s="5" t="str">
         <f>IF(timeseries!A28&lt;&gt;"",timeseries!A28,"")</f>
         <v/>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A29" s="8" t="str">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A29" s="5" t="str">
         <f>IF(timeseries!A29&lt;&gt;"",timeseries!A29,"")</f>
         <v/>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A30" s="8" t="str">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A30" s="5" t="str">
         <f>IF(timeseries!A30&lt;&gt;"",timeseries!A30,"")</f>
         <v/>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A31" s="8" t="str">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A31" s="5" t="str">
         <f>IF(timeseries!A31&lt;&gt;"",timeseries!A31,"")</f>
         <v/>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A32" s="8" t="str">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A32" s="5" t="str">
         <f>IF(timeseries!A32&lt;&gt;"",timeseries!A32,"")</f>
         <v/>
       </c>
     </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A33" s="8" t="str">
+    <row r="33" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A33" s="5" t="str">
         <f>IF(timeseries!A33&lt;&gt;"",timeseries!A33,"")</f>
         <v/>
       </c>
@@ -10494,119 +10643,16 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AB98B755-8BE1-4837-9877-4DDB59C80C3F}">
-  <dimension ref="A1:B11"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{50AC839B-83EF-4125-B3A8-4A12BECA18D1}">
+  <dimension ref="A1:BA31"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="27" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.33203125" style="5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="B1" s="3" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>97</v>
-      </c>
-      <c r="B2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>98</v>
-      </c>
-      <c r="B3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>99</v>
-      </c>
-      <c r="B4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>100</v>
-      </c>
-      <c r="B5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>126</v>
-      </c>
-      <c r="B6">
-        <v>10000000</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>101</v>
-      </c>
-      <c r="B7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>127</v>
-      </c>
-      <c r="B8">
-        <v>10000000</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>149</v>
-      </c>
-      <c r="B9">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>150</v>
-      </c>
-      <c r="B10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>102</v>
-      </c>
-      <c r="B11" t="s">
-        <v>138</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{50AC839B-83EF-4125-B3A8-4A12BECA18D1}">
-  <dimension ref="A1:BA31"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="19.28515625" style="8" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:53" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:53" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="2" t="s">
         <v>24</v>
       </c>
       <c r="B1"/>
@@ -10662,380 +10708,182 @@
       <c r="AZ1"/>
       <c r="BA1"/>
     </row>
-    <row r="2" spans="1:53" x14ac:dyDescent="0.25">
-      <c r="A2" s="8">
+    <row r="2" spans="1:53" x14ac:dyDescent="0.3">
+      <c r="A2" s="5">
         <f>IF(timeseries!A2&lt;&gt;"",timeseries!A2,"")</f>
         <v>45398</v>
       </c>
     </row>
-    <row r="3" spans="1:53" x14ac:dyDescent="0.25">
-      <c r="A3" s="8">
+    <row r="3" spans="1:53" x14ac:dyDescent="0.3">
+      <c r="A3" s="5">
         <f>IF(timeseries!A3&lt;&gt;"",timeseries!A3,"")</f>
         <v>45398.041666666664</v>
       </c>
     </row>
-    <row r="4" spans="1:53" x14ac:dyDescent="0.25">
-      <c r="A4" s="8">
+    <row r="4" spans="1:53" x14ac:dyDescent="0.3">
+      <c r="A4" s="5">
         <f>IF(timeseries!A4&lt;&gt;"",timeseries!A4,"")</f>
         <v>45398.083333333336</v>
       </c>
     </row>
-    <row r="5" spans="1:53" x14ac:dyDescent="0.25">
-      <c r="A5" s="8">
+    <row r="5" spans="1:53" x14ac:dyDescent="0.3">
+      <c r="A5" s="5">
         <f>IF(timeseries!A5&lt;&gt;"",timeseries!A5,"")</f>
         <v>45398.125</v>
       </c>
     </row>
-    <row r="6" spans="1:53" x14ac:dyDescent="0.25">
-      <c r="A6" s="8">
+    <row r="6" spans="1:53" x14ac:dyDescent="0.3">
+      <c r="A6" s="5">
         <f>IF(timeseries!A6&lt;&gt;"",timeseries!A6,"")</f>
         <v>45398.166666666664</v>
       </c>
     </row>
-    <row r="7" spans="1:53" x14ac:dyDescent="0.25">
-      <c r="A7" s="8">
+    <row r="7" spans="1:53" x14ac:dyDescent="0.3">
+      <c r="A7" s="5">
         <f>IF(timeseries!A7&lt;&gt;"",timeseries!A7,"")</f>
         <v>45398.208333333336</v>
       </c>
     </row>
-    <row r="8" spans="1:53" x14ac:dyDescent="0.25">
-      <c r="A8" s="8">
+    <row r="8" spans="1:53" x14ac:dyDescent="0.3">
+      <c r="A8" s="5">
         <f>IF(timeseries!A8&lt;&gt;"",timeseries!A8,"")</f>
         <v>45398.25</v>
       </c>
     </row>
-    <row r="9" spans="1:53" x14ac:dyDescent="0.25">
-      <c r="A9" s="8">
+    <row r="9" spans="1:53" x14ac:dyDescent="0.3">
+      <c r="A9" s="5">
         <f>IF(timeseries!A9&lt;&gt;"",timeseries!A9,"")</f>
         <v>45398.291666666664</v>
       </c>
     </row>
-    <row r="10" spans="1:53" x14ac:dyDescent="0.25">
-      <c r="A10" s="8">
+    <row r="10" spans="1:53" x14ac:dyDescent="0.3">
+      <c r="A10" s="5">
         <f>IF(timeseries!A10&lt;&gt;"",timeseries!A10,"")</f>
         <v>45398.333333333336</v>
       </c>
     </row>
-    <row r="11" spans="1:53" x14ac:dyDescent="0.25">
-      <c r="A11" s="8">
+    <row r="11" spans="1:53" x14ac:dyDescent="0.3">
+      <c r="A11" s="5">
         <f>IF(timeseries!A11&lt;&gt;"",timeseries!A11,"")</f>
         <v>45398.375</v>
       </c>
     </row>
-    <row r="12" spans="1:53" x14ac:dyDescent="0.25">
-      <c r="A12" s="8">
+    <row r="12" spans="1:53" x14ac:dyDescent="0.3">
+      <c r="A12" s="5">
         <f>IF(timeseries!A12&lt;&gt;"",timeseries!A12,"")</f>
         <v>45398.416666666664</v>
       </c>
     </row>
-    <row r="13" spans="1:53" x14ac:dyDescent="0.25">
-      <c r="A13" s="8">
+    <row r="13" spans="1:53" x14ac:dyDescent="0.3">
+      <c r="A13" s="5">
         <f>IF(timeseries!A13&lt;&gt;"",timeseries!A13,"")</f>
         <v>45398.458333333336</v>
       </c>
     </row>
-    <row r="14" spans="1:53" x14ac:dyDescent="0.25">
-      <c r="A14" s="8">
+    <row r="14" spans="1:53" x14ac:dyDescent="0.3">
+      <c r="A14" s="5">
         <f>IF(timeseries!A14&lt;&gt;"",timeseries!A14,"")</f>
         <v>45398.5</v>
       </c>
     </row>
-    <row r="15" spans="1:53" x14ac:dyDescent="0.25">
-      <c r="A15" s="8">
+    <row r="15" spans="1:53" x14ac:dyDescent="0.3">
+      <c r="A15" s="5">
         <f>IF(timeseries!A15&lt;&gt;"",timeseries!A15,"")</f>
         <v>45398.541666666664</v>
       </c>
     </row>
-    <row r="16" spans="1:53" x14ac:dyDescent="0.25">
-      <c r="A16" s="8">
+    <row r="16" spans="1:53" x14ac:dyDescent="0.3">
+      <c r="A16" s="5">
         <f>IF(timeseries!A16&lt;&gt;"",timeseries!A16,"")</f>
         <v>45398.583333333336</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A17" s="8">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A17" s="5">
         <f>IF(timeseries!A17&lt;&gt;"",timeseries!A17,"")</f>
         <v>45398.625</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A18" s="8">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A18" s="5">
         <f>IF(timeseries!A18&lt;&gt;"",timeseries!A18,"")</f>
         <v>45398.666666666664</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A19" s="8">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A19" s="5">
         <f>IF(timeseries!A19&lt;&gt;"",timeseries!A19,"")</f>
         <v>45398.708333333336</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A20" s="8">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A20" s="5">
         <f>IF(timeseries!A20&lt;&gt;"",timeseries!A20,"")</f>
         <v>45398.75</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A21" s="8">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A21" s="5">
         <f>IF(timeseries!A21&lt;&gt;"",timeseries!A21,"")</f>
         <v>45398.791666666664</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A22" s="8">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A22" s="5">
         <f>IF(timeseries!A22&lt;&gt;"",timeseries!A22,"")</f>
         <v>45398.833333333336</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A23" s="8">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A23" s="5">
         <f>IF(timeseries!A23&lt;&gt;"",timeseries!A23,"")</f>
         <v>45398.875</v>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A24" s="8">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A24" s="5">
         <f>IF(timeseries!A24&lt;&gt;"",timeseries!A24,"")</f>
         <v>45398.916666666664</v>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A25" s="8">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A25" s="5">
         <f>IF(timeseries!A25&lt;&gt;"",timeseries!A25,"")</f>
         <v>45398.958333333336</v>
       </c>
     </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A26" s="8" t="str">
+    <row r="26" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A26" s="5" t="str">
         <f>IF(timeseries!A26&lt;&gt;"",timeseries!A26,"")</f>
         <v/>
       </c>
     </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A27" s="8" t="str">
+    <row r="27" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A27" s="5" t="str">
         <f>IF(timeseries!A27&lt;&gt;"",timeseries!A27,"")</f>
         <v/>
       </c>
     </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A28" s="8" t="str">
+    <row r="28" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A28" s="5" t="str">
         <f>IF(timeseries!A28&lt;&gt;"",timeseries!A28,"")</f>
         <v/>
       </c>
     </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A29" s="8" t="str">
+    <row r="29" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A29" s="5" t="str">
         <f>IF(timeseries!A29&lt;&gt;"",timeseries!A29,"")</f>
         <v/>
       </c>
     </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A30" s="8" t="str">
+    <row r="30" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A30" s="5" t="str">
         <f>IF(timeseries!A30&lt;&gt;"",timeseries!A30,"")</f>
         <v/>
       </c>
     </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A31" s="8" t="str">
-        <f>IF(timeseries!A31&lt;&gt;"",timeseries!A31,"")</f>
-        <v/>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F4EEEFDD-AB06-48CB-8034-A9C0C38E7F82}">
-  <dimension ref="A1:A31"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="19.28515625" style="8" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A1" s="3" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A2" s="8">
-        <f>IF(timeseries!A2&lt;&gt;"",timeseries!A2,"")</f>
-        <v>45398</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A3" s="8">
-        <f>IF(timeseries!A3&lt;&gt;"",timeseries!A3,"")</f>
-        <v>45398.041666666664</v>
-      </c>
-    </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A4" s="8">
-        <f>IF(timeseries!A4&lt;&gt;"",timeseries!A4,"")</f>
-        <v>45398.083333333336</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A5" s="8">
-        <f>IF(timeseries!A5&lt;&gt;"",timeseries!A5,"")</f>
-        <v>45398.125</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A6" s="8">
-        <f>IF(timeseries!A6&lt;&gt;"",timeseries!A6,"")</f>
-        <v>45398.166666666664</v>
-      </c>
-    </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A7" s="8">
-        <f>IF(timeseries!A7&lt;&gt;"",timeseries!A7,"")</f>
-        <v>45398.208333333336</v>
-      </c>
-    </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A8" s="8">
-        <f>IF(timeseries!A8&lt;&gt;"",timeseries!A8,"")</f>
-        <v>45398.25</v>
-      </c>
-    </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A9" s="8">
-        <f>IF(timeseries!A9&lt;&gt;"",timeseries!A9,"")</f>
-        <v>45398.291666666664</v>
-      </c>
-    </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A10" s="8">
-        <f>IF(timeseries!A10&lt;&gt;"",timeseries!A10,"")</f>
-        <v>45398.333333333336</v>
-      </c>
-    </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A11" s="8">
-        <f>IF(timeseries!A11&lt;&gt;"",timeseries!A11,"")</f>
-        <v>45398.375</v>
-      </c>
-    </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A12" s="8">
-        <f>IF(timeseries!A12&lt;&gt;"",timeseries!A12,"")</f>
-        <v>45398.416666666664</v>
-      </c>
-    </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A13" s="8">
-        <f>IF(timeseries!A13&lt;&gt;"",timeseries!A13,"")</f>
-        <v>45398.458333333336</v>
-      </c>
-    </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A14" s="8">
-        <f>IF(timeseries!A14&lt;&gt;"",timeseries!A14,"")</f>
-        <v>45398.5</v>
-      </c>
-    </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A15" s="8">
-        <f>IF(timeseries!A15&lt;&gt;"",timeseries!A15,"")</f>
-        <v>45398.541666666664</v>
-      </c>
-    </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A16" s="8">
-        <f>IF(timeseries!A16&lt;&gt;"",timeseries!A16,"")</f>
-        <v>45398.583333333336</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A17" s="8">
-        <f>IF(timeseries!A17&lt;&gt;"",timeseries!A17,"")</f>
-        <v>45398.625</v>
-      </c>
-    </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A18" s="8">
-        <f>IF(timeseries!A18&lt;&gt;"",timeseries!A18,"")</f>
-        <v>45398.666666666664</v>
-      </c>
-    </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A19" s="8">
-        <f>IF(timeseries!A19&lt;&gt;"",timeseries!A19,"")</f>
-        <v>45398.708333333336</v>
-      </c>
-    </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A20" s="8">
-        <f>IF(timeseries!A20&lt;&gt;"",timeseries!A20,"")</f>
-        <v>45398.75</v>
-      </c>
-    </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A21" s="8">
-        <f>IF(timeseries!A21&lt;&gt;"",timeseries!A21,"")</f>
-        <v>45398.791666666664</v>
-      </c>
-    </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A22" s="8">
-        <f>IF(timeseries!A22&lt;&gt;"",timeseries!A22,"")</f>
-        <v>45398.833333333336</v>
-      </c>
-    </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A23" s="8">
-        <f>IF(timeseries!A23&lt;&gt;"",timeseries!A23,"")</f>
-        <v>45398.875</v>
-      </c>
-    </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A24" s="8">
-        <f>IF(timeseries!A24&lt;&gt;"",timeseries!A24,"")</f>
-        <v>45398.916666666664</v>
-      </c>
-    </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A25" s="8">
-        <f>IF(timeseries!A25&lt;&gt;"",timeseries!A25,"")</f>
-        <v>45398.958333333336</v>
-      </c>
-    </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A26" s="8" t="str">
-        <f>IF(timeseries!A26&lt;&gt;"",timeseries!A26,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A27" s="8" t="str">
-        <f>IF(timeseries!A27&lt;&gt;"",timeseries!A27,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A28" s="8" t="str">
-        <f>IF(timeseries!A28&lt;&gt;"",timeseries!A28,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A29" s="8" t="str">
-        <f>IF(timeseries!A29&lt;&gt;"",timeseries!A29,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A30" s="8" t="str">
-        <f>IF(timeseries!A30&lt;&gt;"",timeseries!A30,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A31" s="8" t="str">
+    <row r="31" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A31" s="5" t="str">
         <f>IF(timeseries!A31&lt;&gt;"",timeseries!A31,"")</f>
         <v/>
       </c>
@@ -11046,35 +10894,196 @@
 </file>
 
 <file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9314D326-256A-435C-AAE3-3517FA836EAE}">
-  <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F4EEEFDD-AB06-48CB-8034-A9C0C38E7F82}">
+  <dimension ref="A1:A31"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="10.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.33203125" style="5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="B1" s="3" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>46</v>
-      </c>
-      <c r="B2">
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>47</v>
-      </c>
-      <c r="B3">
-        <v>0</v>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A2" s="5">
+        <f>IF(timeseries!A2&lt;&gt;"",timeseries!A2,"")</f>
+        <v>45398</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A3" s="5">
+        <f>IF(timeseries!A3&lt;&gt;"",timeseries!A3,"")</f>
+        <v>45398.041666666664</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A4" s="5">
+        <f>IF(timeseries!A4&lt;&gt;"",timeseries!A4,"")</f>
+        <v>45398.083333333336</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A5" s="5">
+        <f>IF(timeseries!A5&lt;&gt;"",timeseries!A5,"")</f>
+        <v>45398.125</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6" s="5">
+        <f>IF(timeseries!A6&lt;&gt;"",timeseries!A6,"")</f>
+        <v>45398.166666666664</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A7" s="5">
+        <f>IF(timeseries!A7&lt;&gt;"",timeseries!A7,"")</f>
+        <v>45398.208333333336</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A8" s="5">
+        <f>IF(timeseries!A8&lt;&gt;"",timeseries!A8,"")</f>
+        <v>45398.25</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A9" s="5">
+        <f>IF(timeseries!A9&lt;&gt;"",timeseries!A9,"")</f>
+        <v>45398.291666666664</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A10" s="5">
+        <f>IF(timeseries!A10&lt;&gt;"",timeseries!A10,"")</f>
+        <v>45398.333333333336</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A11" s="5">
+        <f>IF(timeseries!A11&lt;&gt;"",timeseries!A11,"")</f>
+        <v>45398.375</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A12" s="5">
+        <f>IF(timeseries!A12&lt;&gt;"",timeseries!A12,"")</f>
+        <v>45398.416666666664</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A13" s="5">
+        <f>IF(timeseries!A13&lt;&gt;"",timeseries!A13,"")</f>
+        <v>45398.458333333336</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A14" s="5">
+        <f>IF(timeseries!A14&lt;&gt;"",timeseries!A14,"")</f>
+        <v>45398.5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A15" s="5">
+        <f>IF(timeseries!A15&lt;&gt;"",timeseries!A15,"")</f>
+        <v>45398.541666666664</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A16" s="5">
+        <f>IF(timeseries!A16&lt;&gt;"",timeseries!A16,"")</f>
+        <v>45398.583333333336</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A17" s="5">
+        <f>IF(timeseries!A17&lt;&gt;"",timeseries!A17,"")</f>
+        <v>45398.625</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A18" s="5">
+        <f>IF(timeseries!A18&lt;&gt;"",timeseries!A18,"")</f>
+        <v>45398.666666666664</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A19" s="5">
+        <f>IF(timeseries!A19&lt;&gt;"",timeseries!A19,"")</f>
+        <v>45398.708333333336</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A20" s="5">
+        <f>IF(timeseries!A20&lt;&gt;"",timeseries!A20,"")</f>
+        <v>45398.75</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A21" s="5">
+        <f>IF(timeseries!A21&lt;&gt;"",timeseries!A21,"")</f>
+        <v>45398.791666666664</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A22" s="5">
+        <f>IF(timeseries!A22&lt;&gt;"",timeseries!A22,"")</f>
+        <v>45398.833333333336</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A23" s="5">
+        <f>IF(timeseries!A23&lt;&gt;"",timeseries!A23,"")</f>
+        <v>45398.875</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A24" s="5">
+        <f>IF(timeseries!A24&lt;&gt;"",timeseries!A24,"")</f>
+        <v>45398.916666666664</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A25" s="5">
+        <f>IF(timeseries!A25&lt;&gt;"",timeseries!A25,"")</f>
+        <v>45398.958333333336</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A26" s="5" t="str">
+        <f>IF(timeseries!A26&lt;&gt;"",timeseries!A26,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A27" s="5" t="str">
+        <f>IF(timeseries!A27&lt;&gt;"",timeseries!A27,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A28" s="5" t="str">
+        <f>IF(timeseries!A28&lt;&gt;"",timeseries!A28,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A29" s="5" t="str">
+        <f>IF(timeseries!A29&lt;&gt;"",timeseries!A29,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A30" s="5" t="str">
+        <f>IF(timeseries!A30&lt;&gt;"",timeseries!A30,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A31" s="5" t="str">
+        <f>IF(timeseries!A31&lt;&gt;"",timeseries!A31,"")</f>
+        <v/>
       </c>
     </row>
   </sheetData>
@@ -11083,40 +11092,35 @@
 </file>
 
 <file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A87AD413-E614-48C1-80E1-F1E8236FCBC6}">
-  <dimension ref="A1:B4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9314D326-256A-435C-AAE3-3517FA836EAE}">
+  <dimension ref="A1:B3"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="10.33203125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:2" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="B1" s="3" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>33</v>
+        <v>46</v>
       </c>
       <c r="B2">
-        <v>0.3</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="B3">
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>86</v>
-      </c>
-      <c r="B4">
-        <v>0.3</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -11125,167 +11129,40 @@
 </file>
 
 <file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{31679CA5-0AA2-4F6F-8223-14BF74917F04}">
-  <dimension ref="A1:B25"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="19.28515625" style="8" customWidth="1"/>
-  </cols>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A87AD413-E614-48C1-80E1-F1E8236FCBC6}">
+  <dimension ref="A1:B4"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:2" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="3" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" s="8">
-        <f>IF(timeseries!A2&lt;&gt;"",timeseries!A2,"")</f>
-        <v>45398</v>
-      </c>
-      <c r="B2" s="2"/>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" s="8">
-        <f>IF(timeseries!A3&lt;&gt;"",timeseries!A3,"")</f>
-        <v>45398.041666666664</v>
-      </c>
-      <c r="B3" s="2"/>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" s="8">
-        <f>IF(timeseries!A4&lt;&gt;"",timeseries!A4,"")</f>
-        <v>45398.083333333336</v>
-      </c>
-      <c r="B4" s="2"/>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" s="8">
-        <f>IF(timeseries!A5&lt;&gt;"",timeseries!A5,"")</f>
-        <v>45398.125</v>
-      </c>
-      <c r="B5" s="2"/>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" s="8">
-        <f>IF(timeseries!A6&lt;&gt;"",timeseries!A6,"")</f>
-        <v>45398.166666666664</v>
-      </c>
-      <c r="B6" s="2"/>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" s="8">
-        <f>IF(timeseries!A7&lt;&gt;"",timeseries!A7,"")</f>
-        <v>45398.208333333336</v>
-      </c>
-      <c r="B7" s="2"/>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" s="8">
-        <f>IF(timeseries!A8&lt;&gt;"",timeseries!A8,"")</f>
-        <v>45398.25</v>
-      </c>
-      <c r="B8" s="2"/>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" s="8">
-        <f>IF(timeseries!A9&lt;&gt;"",timeseries!A9,"")</f>
-        <v>45398.291666666664</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" s="8">
-        <f>IF(timeseries!A10&lt;&gt;"",timeseries!A10,"")</f>
-        <v>45398.333333333336</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" s="8">
-        <f>IF(timeseries!A11&lt;&gt;"",timeseries!A11,"")</f>
-        <v>45398.375</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" s="8">
-        <f>IF(timeseries!A12&lt;&gt;"",timeseries!A12,"")</f>
-        <v>45398.416666666664</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" s="8">
-        <f>IF(timeseries!A13&lt;&gt;"",timeseries!A13,"")</f>
-        <v>45398.458333333336</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A14" s="8">
-        <f>IF(timeseries!A14&lt;&gt;"",timeseries!A14,"")</f>
-        <v>45398.5</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A15" s="8">
-        <f>IF(timeseries!A15&lt;&gt;"",timeseries!A15,"")</f>
-        <v>45398.541666666664</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A16" s="8">
-        <f>IF(timeseries!A16&lt;&gt;"",timeseries!A16,"")</f>
-        <v>45398.583333333336</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A17" s="8">
-        <f>IF(timeseries!A17&lt;&gt;"",timeseries!A17,"")</f>
-        <v>45398.625</v>
-      </c>
-    </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A18" s="8">
-        <f>IF(timeseries!A18&lt;&gt;"",timeseries!A18,"")</f>
-        <v>45398.666666666664</v>
-      </c>
-    </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A19" s="8">
-        <f>IF(timeseries!A19&lt;&gt;"",timeseries!A19,"")</f>
-        <v>45398.708333333336</v>
-      </c>
-    </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A20" s="8">
-        <f>IF(timeseries!A20&lt;&gt;"",timeseries!A20,"")</f>
-        <v>45398.75</v>
-      </c>
-    </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A21" s="8">
-        <f>IF(timeseries!A21&lt;&gt;"",timeseries!A21,"")</f>
-        <v>45398.791666666664</v>
-      </c>
-    </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A22" s="8">
-        <f>IF(timeseries!A22&lt;&gt;"",timeseries!A22,"")</f>
-        <v>45398.833333333336</v>
-      </c>
-    </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A23" s="8">
-        <f>IF(timeseries!A23&lt;&gt;"",timeseries!A23,"")</f>
-        <v>45398.875</v>
-      </c>
-    </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A24" s="8">
-        <f>IF(timeseries!A24&lt;&gt;"",timeseries!A24,"")</f>
-        <v>45398.916666666664</v>
-      </c>
-    </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A25" s="8">
-        <f>IF(timeseries!A25&lt;&gt;"",timeseries!A25,"")</f>
-        <v>45398.958333333336</v>
+    <row r="1" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B2">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>34</v>
+      </c>
+      <c r="B3">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>86</v>
+      </c>
+      <c r="B4">
+        <v>0.3</v>
       </c>
     </row>
   </sheetData>
@@ -11294,824 +11171,572 @@
 </file>
 
 <file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FD670E02-665B-45B8-BC4E-9596D2C1BC55}">
-  <dimension ref="A1:D25"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{31679CA5-0AA2-4F6F-8223-14BF74917F04}">
+  <dimension ref="A1:A25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="19.28515625" style="8" customWidth="1"/>
-    <col min="2" max="4" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.33203125" style="5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:1" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="B1" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" s="8">
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A2" s="5">
         <f>IF(timeseries!A2&lt;&gt;"",timeseries!A2,"")</f>
         <v>45398</v>
       </c>
-      <c r="B2">
-        <v>1.9500000000000002</v>
-      </c>
-      <c r="C2">
-        <f>B2</f>
-        <v>1.9500000000000002</v>
-      </c>
-      <c r="D2">
-        <f>B2</f>
-        <v>1.9500000000000002</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3" s="8">
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A3" s="5">
         <f>IF(timeseries!A3&lt;&gt;"",timeseries!A3,"")</f>
         <v>45398.041666666664</v>
       </c>
-      <c r="B3">
-        <v>1.83</v>
-      </c>
-      <c r="C3">
-        <f t="shared" ref="C3:C13" si="0">B3</f>
-        <v>1.83</v>
-      </c>
-      <c r="D3">
-        <f t="shared" ref="D3:D13" si="1">B3</f>
-        <v>1.83</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" s="8">
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A4" s="5">
         <f>IF(timeseries!A4&lt;&gt;"",timeseries!A4,"")</f>
         <v>45398.083333333336</v>
       </c>
-      <c r="B4">
-        <v>1.9300000000000002</v>
-      </c>
-      <c r="C4">
-        <f t="shared" si="0"/>
-        <v>1.9300000000000002</v>
-      </c>
-      <c r="D4">
-        <f t="shared" si="1"/>
-        <v>1.9300000000000002</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" s="8">
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A5" s="5">
         <f>IF(timeseries!A5&lt;&gt;"",timeseries!A5,"")</f>
         <v>45398.125</v>
       </c>
-      <c r="B5">
-        <v>1.7800000000000002</v>
-      </c>
-      <c r="C5">
-        <f t="shared" si="0"/>
-        <v>1.7800000000000002</v>
-      </c>
-      <c r="D5">
-        <f t="shared" si="1"/>
-        <v>1.7800000000000002</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" s="8">
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6" s="5">
         <f>IF(timeseries!A6&lt;&gt;"",timeseries!A6,"")</f>
         <v>45398.166666666664</v>
       </c>
-      <c r="B6">
-        <v>1.9200000000000004</v>
-      </c>
-      <c r="C6">
-        <f t="shared" si="0"/>
-        <v>1.9200000000000004</v>
-      </c>
-      <c r="D6">
-        <f t="shared" si="1"/>
-        <v>1.9200000000000004</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A7" s="8">
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A7" s="5">
         <f>IF(timeseries!A7&lt;&gt;"",timeseries!A7,"")</f>
         <v>45398.208333333336</v>
       </c>
-      <c r="B7">
-        <v>1.8200000000000003</v>
-      </c>
-      <c r="C7">
-        <f t="shared" si="0"/>
-        <v>1.8200000000000003</v>
-      </c>
-      <c r="D7">
-        <f t="shared" si="1"/>
-        <v>1.8200000000000003</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A8" s="8">
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A8" s="5">
         <f>IF(timeseries!A8&lt;&gt;"",timeseries!A8,"")</f>
         <v>45398.25</v>
       </c>
-      <c r="B8">
-        <v>1.7700000000000005</v>
-      </c>
-      <c r="C8">
-        <f t="shared" si="0"/>
-        <v>1.7700000000000005</v>
-      </c>
-      <c r="D8">
-        <f t="shared" si="1"/>
-        <v>1.7700000000000005</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A9" s="8">
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A9" s="5">
         <f>IF(timeseries!A9&lt;&gt;"",timeseries!A9,"")</f>
         <v>45398.291666666664</v>
       </c>
-      <c r="B9">
-        <v>1.9400000000000004</v>
-      </c>
-      <c r="C9">
-        <f t="shared" si="0"/>
-        <v>1.9400000000000004</v>
-      </c>
-      <c r="D9">
-        <f t="shared" si="1"/>
-        <v>1.9400000000000004</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A10" s="8">
+    </row>
+    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A10" s="5">
         <f>IF(timeseries!A10&lt;&gt;"",timeseries!A10,"")</f>
         <v>45398.333333333336</v>
       </c>
-      <c r="B10">
-        <v>1.8200000000000003</v>
-      </c>
-      <c r="C10">
-        <f t="shared" si="0"/>
-        <v>1.8200000000000003</v>
-      </c>
-      <c r="D10">
-        <f t="shared" si="1"/>
-        <v>1.8200000000000003</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A11" s="8">
+    </row>
+    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A11" s="5">
         <f>IF(timeseries!A11&lt;&gt;"",timeseries!A11,"")</f>
         <v>45398.375</v>
       </c>
-      <c r="B11">
-        <v>1.8000000000000003</v>
-      </c>
-      <c r="C11">
-        <f t="shared" si="0"/>
-        <v>1.8000000000000003</v>
-      </c>
-      <c r="D11">
-        <f t="shared" si="1"/>
-        <v>1.8000000000000003</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A12" s="8">
+    </row>
+    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A12" s="5">
         <f>IF(timeseries!A12&lt;&gt;"",timeseries!A12,"")</f>
         <v>45398.416666666664</v>
       </c>
-      <c r="B12">
-        <v>1.7800000000000002</v>
-      </c>
-      <c r="C12">
-        <f t="shared" si="0"/>
-        <v>1.7800000000000002</v>
-      </c>
-      <c r="D12">
-        <f t="shared" si="1"/>
-        <v>1.7800000000000002</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A13" s="8">
+    </row>
+    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A13" s="5">
         <f>IF(timeseries!A13&lt;&gt;"",timeseries!A13,"")</f>
         <v>45398.458333333336</v>
       </c>
-      <c r="B13">
-        <v>1.9000000000000004</v>
-      </c>
-      <c r="C13">
-        <f t="shared" si="0"/>
-        <v>1.9000000000000004</v>
-      </c>
-      <c r="D13">
-        <f t="shared" si="1"/>
-        <v>1.9000000000000004</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A14" s="8">
+    </row>
+    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A14" s="5">
         <f>IF(timeseries!A14&lt;&gt;"",timeseries!A14,"")</f>
         <v>45398.5</v>
       </c>
-      <c r="B14">
-        <v>2.0300000000000002</v>
-      </c>
-      <c r="C14">
-        <v>2.8400000000000003</v>
-      </c>
-      <c r="D14">
-        <v>1.25</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A15" s="8">
+    </row>
+    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A15" s="5">
         <f>IF(timeseries!A15&lt;&gt;"",timeseries!A15,"")</f>
         <v>45398.541666666664</v>
       </c>
-      <c r="B15">
-        <v>2.1100000000000003</v>
-      </c>
-      <c r="C15">
-        <v>2.8000000000000003</v>
-      </c>
-      <c r="D15">
-        <v>1.44</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A16" s="8">
+    </row>
+    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A16" s="5">
         <f>IF(timeseries!A16&lt;&gt;"",timeseries!A16,"")</f>
         <v>45398.583333333336</v>
       </c>
-      <c r="B16">
-        <v>2.2100000000000004</v>
-      </c>
-      <c r="C16">
-        <v>2.83</v>
-      </c>
-      <c r="D16">
-        <v>1.4499999999999997</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A17" s="8">
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A17" s="5">
         <f>IF(timeseries!A17&lt;&gt;"",timeseries!A17,"")</f>
         <v>45398.625</v>
       </c>
-      <c r="B17">
-        <v>2.2400000000000002</v>
-      </c>
-      <c r="C17">
-        <v>2.9</v>
-      </c>
-      <c r="D17">
-        <v>1.2899999999999996</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A18" s="8">
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A18" s="5">
         <f>IF(timeseries!A18&lt;&gt;"",timeseries!A18,"")</f>
         <v>45398.666666666664</v>
       </c>
-      <c r="B18">
-        <v>2.3400000000000003</v>
-      </c>
-      <c r="C18">
-        <v>2.78</v>
-      </c>
-      <c r="D18">
-        <v>1.1699999999999995</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A19" s="8">
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A19" s="5">
         <f>IF(timeseries!A19&lt;&gt;"",timeseries!A19,"")</f>
         <v>45398.708333333336</v>
       </c>
-      <c r="B19">
-        <v>2.3100000000000005</v>
-      </c>
-      <c r="C19">
-        <v>2.6599999999999997</v>
-      </c>
-      <c r="D19">
-        <v>1.1299999999999994</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A20" s="8">
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A20" s="5">
         <f>IF(timeseries!A20&lt;&gt;"",timeseries!A20,"")</f>
         <v>45398.75</v>
       </c>
-      <c r="B20">
-        <v>2.3500000000000005</v>
-      </c>
-      <c r="C20">
-        <v>2.7099999999999995</v>
-      </c>
-      <c r="D20">
-        <v>1.3099999999999996</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A21" s="8">
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A21" s="5">
         <f>IF(timeseries!A21&lt;&gt;"",timeseries!A21,"")</f>
         <v>45398.791666666664</v>
       </c>
-      <c r="B21">
-        <v>2.5200000000000005</v>
-      </c>
-      <c r="C21">
-        <v>2.8799999999999994</v>
-      </c>
-      <c r="D21">
-        <v>1.1099999999999994</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A22" s="8">
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A22" s="5">
         <f>IF(timeseries!A22&lt;&gt;"",timeseries!A22,"")</f>
         <v>45398.833333333336</v>
       </c>
-      <c r="B22">
-        <v>2.5100000000000007</v>
-      </c>
-      <c r="C22">
-        <v>2.8499999999999996</v>
-      </c>
-      <c r="D22">
-        <v>1.0699999999999994</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A23" s="8">
+    </row>
+    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A23" s="5">
         <f>IF(timeseries!A23&lt;&gt;"",timeseries!A23,"")</f>
         <v>45398.875</v>
       </c>
-      <c r="B23">
-        <v>2.4600000000000009</v>
-      </c>
-      <c r="C23">
-        <v>2.9199999999999995</v>
-      </c>
-      <c r="D23">
-        <v>1.2399999999999993</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A24" s="8">
+    </row>
+    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A24" s="5">
         <f>IF(timeseries!A24&lt;&gt;"",timeseries!A24,"")</f>
         <v>45398.916666666664</v>
       </c>
-      <c r="B24">
-        <v>2.5100000000000007</v>
-      </c>
-      <c r="C24">
-        <v>2.7299999999999995</v>
-      </c>
-      <c r="D24">
-        <v>1.4099999999999993</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A25" s="8">
+    </row>
+    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A25" s="5">
         <f>IF(timeseries!A25&lt;&gt;"",timeseries!A25,"")</f>
         <v>45398.958333333336</v>
       </c>
-      <c r="B25">
-        <v>2.6400000000000006</v>
-      </c>
-      <c r="C25">
-        <v>2.8099999999999996</v>
-      </c>
-      <c r="D25">
-        <v>1.4099999999999993</v>
-      </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
-  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A7FEDBA5-B0F3-4E9D-9367-08D5F5FA8AEA}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FD670E02-665B-45B8-BC4E-9596D2C1BC55}">
   <dimension ref="A1:D25"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="19.28515625" style="8" customWidth="1"/>
+    <col min="1" max="1" width="19.33203125" style="5" customWidth="1"/>
+    <col min="2" max="4" width="13.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="B1" t="s">
-        <v>118</v>
-      </c>
-      <c r="C1" t="s">
-        <v>119</v>
-      </c>
-      <c r="D1" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" s="8">
+      <c r="B1" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A2" s="5">
         <f>IF(timeseries!A2&lt;&gt;"",timeseries!A2,"")</f>
         <v>45398</v>
       </c>
-      <c r="B2" s="1">
-        <f>D2</f>
-        <v>2.4950000000000001</v>
-      </c>
-      <c r="C2" s="1">
-        <f>D2</f>
-        <v>2.4950000000000001</v>
-      </c>
-      <c r="D2" s="1">
-        <v>2.4950000000000001</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3" s="8">
+      <c r="B2">
+        <v>1.9500000000000002</v>
+      </c>
+      <c r="C2">
+        <f>B2</f>
+        <v>1.9500000000000002</v>
+      </c>
+      <c r="D2">
+        <f>B2</f>
+        <v>1.9500000000000002</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A3" s="5">
         <f>IF(timeseries!A3&lt;&gt;"",timeseries!A3,"")</f>
         <v>45398.041666666664</v>
       </c>
-      <c r="B3" s="1">
-        <f t="shared" ref="B3:B13" si="0">D3</f>
-        <v>2.5449999999999999</v>
-      </c>
-      <c r="C3" s="1">
-        <f t="shared" ref="C3:C13" si="1">D3</f>
-        <v>2.5449999999999999</v>
-      </c>
-      <c r="D3" s="1">
-        <v>2.5449999999999999</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" s="8">
+      <c r="B3">
+        <v>1.83</v>
+      </c>
+      <c r="C3">
+        <f t="shared" ref="C3:C13" si="0">B3</f>
+        <v>1.83</v>
+      </c>
+      <c r="D3">
+        <f t="shared" ref="D3:D13" si="1">B3</f>
+        <v>1.83</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A4" s="5">
         <f>IF(timeseries!A4&lt;&gt;"",timeseries!A4,"")</f>
         <v>45398.083333333336</v>
       </c>
-      <c r="B4" s="1">
+      <c r="B4">
+        <v>1.9300000000000002</v>
+      </c>
+      <c r="C4">
         <f t="shared" si="0"/>
-        <v>2.4449999999999998</v>
-      </c>
-      <c r="C4" s="1">
+        <v>1.9300000000000002</v>
+      </c>
+      <c r="D4">
         <f t="shared" si="1"/>
-        <v>2.4449999999999998</v>
-      </c>
-      <c r="D4" s="1">
-        <v>2.4449999999999998</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" s="8">
+        <v>1.9300000000000002</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A5" s="5">
         <f>IF(timeseries!A5&lt;&gt;"",timeseries!A5,"")</f>
         <v>45398.125</v>
       </c>
-      <c r="B5" s="1">
+      <c r="B5">
+        <v>1.7800000000000002</v>
+      </c>
+      <c r="C5">
         <f t="shared" si="0"/>
-        <v>2.4949999999999997</v>
-      </c>
-      <c r="C5" s="1">
+        <v>1.7800000000000002</v>
+      </c>
+      <c r="D5">
         <f t="shared" si="1"/>
-        <v>2.4949999999999997</v>
-      </c>
-      <c r="D5" s="1">
-        <v>2.4949999999999997</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" s="8">
+        <v>1.7800000000000002</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A6" s="5">
         <f>IF(timeseries!A6&lt;&gt;"",timeseries!A6,"")</f>
         <v>45398.166666666664</v>
       </c>
-      <c r="B6" s="1">
+      <c r="B6">
+        <v>1.9200000000000004</v>
+      </c>
+      <c r="C6">
         <f t="shared" si="0"/>
-        <v>2.6449999999999996</v>
-      </c>
-      <c r="C6" s="1">
+        <v>1.9200000000000004</v>
+      </c>
+      <c r="D6">
         <f t="shared" si="1"/>
-        <v>2.6449999999999996</v>
-      </c>
-      <c r="D6" s="1">
-        <v>2.6449999999999996</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A7" s="8">
+        <v>1.9200000000000004</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A7" s="5">
         <f>IF(timeseries!A7&lt;&gt;"",timeseries!A7,"")</f>
         <v>45398.208333333336</v>
       </c>
-      <c r="B7" s="1">
+      <c r="B7">
+        <v>1.8200000000000003</v>
+      </c>
+      <c r="C7">
         <f t="shared" si="0"/>
-        <v>2.5449999999999995</v>
-      </c>
-      <c r="C7" s="1">
+        <v>1.8200000000000003</v>
+      </c>
+      <c r="D7">
         <f t="shared" si="1"/>
-        <v>2.5449999999999995</v>
-      </c>
-      <c r="D7" s="1">
-        <v>2.5449999999999995</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A8" s="8">
+        <v>1.8200000000000003</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A8" s="5">
         <f>IF(timeseries!A8&lt;&gt;"",timeseries!A8,"")</f>
         <v>45398.25</v>
       </c>
-      <c r="B8" s="1">
+      <c r="B8">
+        <v>1.7700000000000005</v>
+      </c>
+      <c r="C8">
         <f t="shared" si="0"/>
-        <v>2.5949999999999993</v>
-      </c>
-      <c r="C8" s="1">
+        <v>1.7700000000000005</v>
+      </c>
+      <c r="D8">
         <f t="shared" si="1"/>
-        <v>2.5949999999999993</v>
-      </c>
-      <c r="D8" s="1">
-        <v>2.5949999999999993</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A9" s="8">
+        <v>1.7700000000000005</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A9" s="5">
         <f>IF(timeseries!A9&lt;&gt;"",timeseries!A9,"")</f>
         <v>45398.291666666664</v>
       </c>
-      <c r="B9" s="1">
+      <c r="B9">
+        <v>1.9400000000000004</v>
+      </c>
+      <c r="C9">
         <f t="shared" si="0"/>
-        <v>2.4949999999999992</v>
-      </c>
-      <c r="C9" s="1">
+        <v>1.9400000000000004</v>
+      </c>
+      <c r="D9">
         <f t="shared" si="1"/>
-        <v>2.4949999999999992</v>
-      </c>
-      <c r="D9" s="1">
-        <v>2.4949999999999992</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A10" s="8">
+        <v>1.9400000000000004</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A10" s="5">
         <f>IF(timeseries!A10&lt;&gt;"",timeseries!A10,"")</f>
         <v>45398.333333333336</v>
       </c>
-      <c r="B10" s="1">
+      <c r="B10">
+        <v>1.8200000000000003</v>
+      </c>
+      <c r="C10">
         <f t="shared" si="0"/>
-        <v>2.4949999999999992</v>
-      </c>
-      <c r="C10" s="1">
+        <v>1.8200000000000003</v>
+      </c>
+      <c r="D10">
         <f t="shared" si="1"/>
-        <v>2.4949999999999992</v>
-      </c>
-      <c r="D10" s="1">
-        <v>2.4949999999999992</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A11" s="8">
+        <v>1.8200000000000003</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A11" s="5">
         <f>IF(timeseries!A11&lt;&gt;"",timeseries!A11,"")</f>
         <v>45398.375</v>
       </c>
-      <c r="B11" s="1">
+      <c r="B11">
+        <v>1.8000000000000003</v>
+      </c>
+      <c r="C11">
         <f t="shared" si="0"/>
-        <v>2.4449999999999994</v>
-      </c>
-      <c r="C11" s="1">
+        <v>1.8000000000000003</v>
+      </c>
+      <c r="D11">
         <f t="shared" si="1"/>
-        <v>2.4449999999999994</v>
-      </c>
-      <c r="D11" s="1">
-        <v>2.4449999999999994</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A12" s="8">
+        <v>1.8000000000000003</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A12" s="5">
         <f>IF(timeseries!A12&lt;&gt;"",timeseries!A12,"")</f>
         <v>45398.416666666664</v>
       </c>
-      <c r="B12" s="1">
+      <c r="B12">
+        <v>1.7800000000000002</v>
+      </c>
+      <c r="C12">
         <f t="shared" si="0"/>
-        <v>2.5449999999999995</v>
-      </c>
-      <c r="C12" s="1">
+        <v>1.7800000000000002</v>
+      </c>
+      <c r="D12">
         <f t="shared" si="1"/>
-        <v>2.5449999999999995</v>
-      </c>
-      <c r="D12" s="1">
-        <v>2.5449999999999995</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A13" s="8">
+        <v>1.7800000000000002</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A13" s="5">
         <f>IF(timeseries!A13&lt;&gt;"",timeseries!A13,"")</f>
         <v>45398.458333333336</v>
       </c>
-      <c r="B13" s="1">
+      <c r="B13">
+        <v>1.9000000000000004</v>
+      </c>
+      <c r="C13">
         <f t="shared" si="0"/>
-        <v>2.3949999999999996</v>
-      </c>
-      <c r="C13" s="1">
+        <v>1.9000000000000004</v>
+      </c>
+      <c r="D13">
         <f t="shared" si="1"/>
-        <v>2.3949999999999996</v>
-      </c>
-      <c r="D13" s="1">
-        <v>2.3949999999999996</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A14" s="8">
+        <v>1.9000000000000004</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A14" s="5">
         <f>IF(timeseries!A14&lt;&gt;"",timeseries!A14,"")</f>
         <v>45398.5</v>
       </c>
-      <c r="B14" s="1">
-        <v>2.0149999999999997</v>
-      </c>
-      <c r="C14" s="1">
-        <v>2.6950000000000003</v>
-      </c>
-      <c r="D14" s="1">
-        <v>2.4949999999999997</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A15" s="8">
+      <c r="B14">
+        <v>2.0300000000000002</v>
+      </c>
+      <c r="C14">
+        <v>2.8400000000000003</v>
+      </c>
+      <c r="D14">
+        <v>1.25</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A15" s="5">
         <f>IF(timeseries!A15&lt;&gt;"",timeseries!A15,"")</f>
         <v>45398.541666666664</v>
       </c>
-      <c r="B15" s="1">
-        <v>1.9649999999999996</v>
-      </c>
-      <c r="C15" s="1">
-        <v>2.7950000000000004</v>
-      </c>
-      <c r="D15" s="1">
-        <v>2.6449999999999996</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A16" s="8">
+      <c r="B15">
+        <v>2.1100000000000003</v>
+      </c>
+      <c r="C15">
+        <v>2.8000000000000003</v>
+      </c>
+      <c r="D15">
+        <v>1.44</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A16" s="5">
         <f>IF(timeseries!A16&lt;&gt;"",timeseries!A16,"")</f>
         <v>45398.583333333336</v>
       </c>
-      <c r="B16" s="1">
-        <v>2.0649999999999995</v>
-      </c>
-      <c r="C16" s="1">
-        <v>2.9450000000000003</v>
-      </c>
-      <c r="D16" s="1">
-        <v>2.7449999999999997</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A17" s="8">
+      <c r="B16">
+        <v>2.2100000000000004</v>
+      </c>
+      <c r="C16">
+        <v>2.83</v>
+      </c>
+      <c r="D16">
+        <v>1.4499999999999997</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A17" s="5">
         <f>IF(timeseries!A17&lt;&gt;"",timeseries!A17,"")</f>
         <v>45398.625</v>
       </c>
-      <c r="B17" s="1">
-        <v>2.0649999999999995</v>
-      </c>
-      <c r="C17" s="1">
-        <v>2.8950000000000005</v>
-      </c>
-      <c r="D17" s="1">
-        <v>2.7949999999999995</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A18" s="8">
+      <c r="B17">
+        <v>2.2400000000000002</v>
+      </c>
+      <c r="C17">
+        <v>2.9</v>
+      </c>
+      <c r="D17">
+        <v>1.2899999999999996</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A18" s="5">
         <f>IF(timeseries!A18&lt;&gt;"",timeseries!A18,"")</f>
         <v>45398.666666666664</v>
       </c>
-      <c r="B18" s="1">
-        <v>2.2149999999999994</v>
-      </c>
-      <c r="C18" s="1">
-        <v>3.0450000000000004</v>
-      </c>
-      <c r="D18" s="1">
-        <v>2.8949999999999996</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A19" s="8">
+      <c r="B18">
+        <v>2.3400000000000003</v>
+      </c>
+      <c r="C18">
+        <v>2.78</v>
+      </c>
+      <c r="D18">
+        <v>1.1699999999999995</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A19" s="5">
         <f>IF(timeseries!A19&lt;&gt;"",timeseries!A19,"")</f>
         <v>45398.708333333336</v>
       </c>
-      <c r="B19" s="1">
-        <v>2.3149999999999995</v>
-      </c>
-      <c r="C19" s="1">
-        <v>3.1950000000000003</v>
-      </c>
-      <c r="D19" s="1">
-        <v>2.9449999999999994</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A20" s="8">
+      <c r="B19">
+        <v>2.3100000000000005</v>
+      </c>
+      <c r="C19">
+        <v>2.6599999999999997</v>
+      </c>
+      <c r="D19">
+        <v>1.1299999999999994</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A20" s="5">
         <f>IF(timeseries!A20&lt;&gt;"",timeseries!A20,"")</f>
         <v>45398.75</v>
       </c>
-      <c r="B20" s="1">
-        <v>2.3149999999999995</v>
-      </c>
-      <c r="C20" s="1">
-        <v>3.0950000000000002</v>
-      </c>
-      <c r="D20" s="1">
-        <v>2.9449999999999994</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A21" s="8">
+      <c r="B20">
+        <v>2.3500000000000005</v>
+      </c>
+      <c r="C20">
+        <v>2.7099999999999995</v>
+      </c>
+      <c r="D20">
+        <v>1.3099999999999996</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A21" s="5">
         <f>IF(timeseries!A21&lt;&gt;"",timeseries!A21,"")</f>
         <v>45398.791666666664</v>
       </c>
-      <c r="B21" s="1">
-        <v>2.3649999999999993</v>
-      </c>
-      <c r="C21" s="1">
-        <v>3.0450000000000004</v>
-      </c>
-      <c r="D21" s="1">
-        <v>3.0449999999999995</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A22" s="8">
+      <c r="B21">
+        <v>2.5200000000000005</v>
+      </c>
+      <c r="C21">
+        <v>2.8799999999999994</v>
+      </c>
+      <c r="D21">
+        <v>1.1099999999999994</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A22" s="5">
         <f>IF(timeseries!A22&lt;&gt;"",timeseries!A22,"")</f>
         <v>45398.833333333336</v>
       </c>
-      <c r="B22" s="1">
-        <v>2.2649999999999992</v>
-      </c>
-      <c r="C22" s="1">
-        <v>3.0950000000000002</v>
-      </c>
-      <c r="D22" s="1">
-        <v>2.9949999999999997</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A23" s="8">
+      <c r="B22">
+        <v>2.5100000000000007</v>
+      </c>
+      <c r="C22">
+        <v>2.8499999999999996</v>
+      </c>
+      <c r="D22">
+        <v>1.0699999999999994</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A23" s="5">
         <f>IF(timeseries!A23&lt;&gt;"",timeseries!A23,"")</f>
         <v>45398.875</v>
       </c>
-      <c r="B23" s="1">
-        <v>2.3649999999999993</v>
-      </c>
-      <c r="C23" s="1">
-        <v>2.9450000000000003</v>
-      </c>
-      <c r="D23" s="1">
-        <v>2.8949999999999996</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A24" s="8">
+      <c r="B23">
+        <v>2.4600000000000009</v>
+      </c>
+      <c r="C23">
+        <v>2.9199999999999995</v>
+      </c>
+      <c r="D23">
+        <v>1.2399999999999993</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A24" s="5">
         <f>IF(timeseries!A24&lt;&gt;"",timeseries!A24,"")</f>
         <v>45398.916666666664</v>
       </c>
-      <c r="B24" s="1">
-        <v>2.3649999999999993</v>
-      </c>
-      <c r="C24" s="1">
-        <v>2.8950000000000005</v>
-      </c>
-      <c r="D24" s="1">
-        <v>2.8949999999999996</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A25" s="8">
+      <c r="B24">
+        <v>2.5100000000000007</v>
+      </c>
+      <c r="C24">
+        <v>2.7299999999999995</v>
+      </c>
+      <c r="D24">
+        <v>1.4099999999999993</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A25" s="5">
         <f>IF(timeseries!A25&lt;&gt;"",timeseries!A25,"")</f>
         <v>45398.958333333336</v>
       </c>
-      <c r="B25" s="1">
-        <v>2.5149999999999992</v>
-      </c>
-      <c r="C25" s="1">
-        <v>2.9450000000000003</v>
-      </c>
-      <c r="D25" s="1">
-        <v>2.7949999999999995</v>
+      <c r="B25">
+        <v>2.6400000000000006</v>
+      </c>
+      <c r="C25">
+        <v>2.8099999999999996</v>
+      </c>
+      <c r="D25">
+        <v>1.4099999999999993</v>
       </c>
     </row>
   </sheetData>
@@ -12123,16 +11748,430 @@
 </file>
 
 <file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A7FEDBA5-B0F3-4E9D-9367-08D5F5FA8AEA}">
+  <dimension ref="A1:D25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="19.33203125" style="5" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B1" t="s">
+        <v>118</v>
+      </c>
+      <c r="C1" t="s">
+        <v>119</v>
+      </c>
+      <c r="D1" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A2" s="5">
+        <f>IF(timeseries!A2&lt;&gt;"",timeseries!A2,"")</f>
+        <v>45398</v>
+      </c>
+      <c r="B2" s="1">
+        <f>D2</f>
+        <v>2.4950000000000001</v>
+      </c>
+      <c r="C2" s="1">
+        <f>D2</f>
+        <v>2.4950000000000001</v>
+      </c>
+      <c r="D2" s="1">
+        <v>2.4950000000000001</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A3" s="5">
+        <f>IF(timeseries!A3&lt;&gt;"",timeseries!A3,"")</f>
+        <v>45398.041666666664</v>
+      </c>
+      <c r="B3" s="1">
+        <f t="shared" ref="B3:B13" si="0">D3</f>
+        <v>2.5449999999999999</v>
+      </c>
+      <c r="C3" s="1">
+        <f t="shared" ref="C3:C13" si="1">D3</f>
+        <v>2.5449999999999999</v>
+      </c>
+      <c r="D3" s="1">
+        <v>2.5449999999999999</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A4" s="5">
+        <f>IF(timeseries!A4&lt;&gt;"",timeseries!A4,"")</f>
+        <v>45398.083333333336</v>
+      </c>
+      <c r="B4" s="1">
+        <f t="shared" si="0"/>
+        <v>2.4449999999999998</v>
+      </c>
+      <c r="C4" s="1">
+        <f t="shared" si="1"/>
+        <v>2.4449999999999998</v>
+      </c>
+      <c r="D4" s="1">
+        <v>2.4449999999999998</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A5" s="5">
+        <f>IF(timeseries!A5&lt;&gt;"",timeseries!A5,"")</f>
+        <v>45398.125</v>
+      </c>
+      <c r="B5" s="1">
+        <f t="shared" si="0"/>
+        <v>2.4949999999999997</v>
+      </c>
+      <c r="C5" s="1">
+        <f t="shared" si="1"/>
+        <v>2.4949999999999997</v>
+      </c>
+      <c r="D5" s="1">
+        <v>2.4949999999999997</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A6" s="5">
+        <f>IF(timeseries!A6&lt;&gt;"",timeseries!A6,"")</f>
+        <v>45398.166666666664</v>
+      </c>
+      <c r="B6" s="1">
+        <f t="shared" si="0"/>
+        <v>2.6449999999999996</v>
+      </c>
+      <c r="C6" s="1">
+        <f t="shared" si="1"/>
+        <v>2.6449999999999996</v>
+      </c>
+      <c r="D6" s="1">
+        <v>2.6449999999999996</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A7" s="5">
+        <f>IF(timeseries!A7&lt;&gt;"",timeseries!A7,"")</f>
+        <v>45398.208333333336</v>
+      </c>
+      <c r="B7" s="1">
+        <f t="shared" si="0"/>
+        <v>2.5449999999999995</v>
+      </c>
+      <c r="C7" s="1">
+        <f t="shared" si="1"/>
+        <v>2.5449999999999995</v>
+      </c>
+      <c r="D7" s="1">
+        <v>2.5449999999999995</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A8" s="5">
+        <f>IF(timeseries!A8&lt;&gt;"",timeseries!A8,"")</f>
+        <v>45398.25</v>
+      </c>
+      <c r="B8" s="1">
+        <f t="shared" si="0"/>
+        <v>2.5949999999999993</v>
+      </c>
+      <c r="C8" s="1">
+        <f t="shared" si="1"/>
+        <v>2.5949999999999993</v>
+      </c>
+      <c r="D8" s="1">
+        <v>2.5949999999999993</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A9" s="5">
+        <f>IF(timeseries!A9&lt;&gt;"",timeseries!A9,"")</f>
+        <v>45398.291666666664</v>
+      </c>
+      <c r="B9" s="1">
+        <f t="shared" si="0"/>
+        <v>2.4949999999999992</v>
+      </c>
+      <c r="C9" s="1">
+        <f t="shared" si="1"/>
+        <v>2.4949999999999992</v>
+      </c>
+      <c r="D9" s="1">
+        <v>2.4949999999999992</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A10" s="5">
+        <f>IF(timeseries!A10&lt;&gt;"",timeseries!A10,"")</f>
+        <v>45398.333333333336</v>
+      </c>
+      <c r="B10" s="1">
+        <f t="shared" si="0"/>
+        <v>2.4949999999999992</v>
+      </c>
+      <c r="C10" s="1">
+        <f t="shared" si="1"/>
+        <v>2.4949999999999992</v>
+      </c>
+      <c r="D10" s="1">
+        <v>2.4949999999999992</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A11" s="5">
+        <f>IF(timeseries!A11&lt;&gt;"",timeseries!A11,"")</f>
+        <v>45398.375</v>
+      </c>
+      <c r="B11" s="1">
+        <f t="shared" si="0"/>
+        <v>2.4449999999999994</v>
+      </c>
+      <c r="C11" s="1">
+        <f t="shared" si="1"/>
+        <v>2.4449999999999994</v>
+      </c>
+      <c r="D11" s="1">
+        <v>2.4449999999999994</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A12" s="5">
+        <f>IF(timeseries!A12&lt;&gt;"",timeseries!A12,"")</f>
+        <v>45398.416666666664</v>
+      </c>
+      <c r="B12" s="1">
+        <f t="shared" si="0"/>
+        <v>2.5449999999999995</v>
+      </c>
+      <c r="C12" s="1">
+        <f t="shared" si="1"/>
+        <v>2.5449999999999995</v>
+      </c>
+      <c r="D12" s="1">
+        <v>2.5449999999999995</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A13" s="5">
+        <f>IF(timeseries!A13&lt;&gt;"",timeseries!A13,"")</f>
+        <v>45398.458333333336</v>
+      </c>
+      <c r="B13" s="1">
+        <f t="shared" si="0"/>
+        <v>2.3949999999999996</v>
+      </c>
+      <c r="C13" s="1">
+        <f t="shared" si="1"/>
+        <v>2.3949999999999996</v>
+      </c>
+      <c r="D13" s="1">
+        <v>2.3949999999999996</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A14" s="5">
+        <f>IF(timeseries!A14&lt;&gt;"",timeseries!A14,"")</f>
+        <v>45398.5</v>
+      </c>
+      <c r="B14" s="1">
+        <v>2.0149999999999997</v>
+      </c>
+      <c r="C14" s="1">
+        <v>2.6950000000000003</v>
+      </c>
+      <c r="D14" s="1">
+        <v>2.4949999999999997</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A15" s="5">
+        <f>IF(timeseries!A15&lt;&gt;"",timeseries!A15,"")</f>
+        <v>45398.541666666664</v>
+      </c>
+      <c r="B15" s="1">
+        <v>1.9649999999999996</v>
+      </c>
+      <c r="C15" s="1">
+        <v>2.7950000000000004</v>
+      </c>
+      <c r="D15" s="1">
+        <v>2.6449999999999996</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A16" s="5">
+        <f>IF(timeseries!A16&lt;&gt;"",timeseries!A16,"")</f>
+        <v>45398.583333333336</v>
+      </c>
+      <c r="B16" s="1">
+        <v>2.0649999999999995</v>
+      </c>
+      <c r="C16" s="1">
+        <v>2.9450000000000003</v>
+      </c>
+      <c r="D16" s="1">
+        <v>2.7449999999999997</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A17" s="5">
+        <f>IF(timeseries!A17&lt;&gt;"",timeseries!A17,"")</f>
+        <v>45398.625</v>
+      </c>
+      <c r="B17" s="1">
+        <v>2.0649999999999995</v>
+      </c>
+      <c r="C17" s="1">
+        <v>2.8950000000000005</v>
+      </c>
+      <c r="D17" s="1">
+        <v>2.7949999999999995</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A18" s="5">
+        <f>IF(timeseries!A18&lt;&gt;"",timeseries!A18,"")</f>
+        <v>45398.666666666664</v>
+      </c>
+      <c r="B18" s="1">
+        <v>2.2149999999999994</v>
+      </c>
+      <c r="C18" s="1">
+        <v>3.0450000000000004</v>
+      </c>
+      <c r="D18" s="1">
+        <v>2.8949999999999996</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A19" s="5">
+        <f>IF(timeseries!A19&lt;&gt;"",timeseries!A19,"")</f>
+        <v>45398.708333333336</v>
+      </c>
+      <c r="B19" s="1">
+        <v>2.3149999999999995</v>
+      </c>
+      <c r="C19" s="1">
+        <v>3.1950000000000003</v>
+      </c>
+      <c r="D19" s="1">
+        <v>2.9449999999999994</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A20" s="5">
+        <f>IF(timeseries!A20&lt;&gt;"",timeseries!A20,"")</f>
+        <v>45398.75</v>
+      </c>
+      <c r="B20" s="1">
+        <v>2.3149999999999995</v>
+      </c>
+      <c r="C20" s="1">
+        <v>3.0950000000000002</v>
+      </c>
+      <c r="D20" s="1">
+        <v>2.9449999999999994</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A21" s="5">
+        <f>IF(timeseries!A21&lt;&gt;"",timeseries!A21,"")</f>
+        <v>45398.791666666664</v>
+      </c>
+      <c r="B21" s="1">
+        <v>2.3649999999999993</v>
+      </c>
+      <c r="C21" s="1">
+        <v>3.0450000000000004</v>
+      </c>
+      <c r="D21" s="1">
+        <v>3.0449999999999995</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A22" s="5">
+        <f>IF(timeseries!A22&lt;&gt;"",timeseries!A22,"")</f>
+        <v>45398.833333333336</v>
+      </c>
+      <c r="B22" s="1">
+        <v>2.2649999999999992</v>
+      </c>
+      <c r="C22" s="1">
+        <v>3.0950000000000002</v>
+      </c>
+      <c r="D22" s="1">
+        <v>2.9949999999999997</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A23" s="5">
+        <f>IF(timeseries!A23&lt;&gt;"",timeseries!A23,"")</f>
+        <v>45398.875</v>
+      </c>
+      <c r="B23" s="1">
+        <v>2.3649999999999993</v>
+      </c>
+      <c r="C23" s="1">
+        <v>2.9450000000000003</v>
+      </c>
+      <c r="D23" s="1">
+        <v>2.8949999999999996</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A24" s="5">
+        <f>IF(timeseries!A24&lt;&gt;"",timeseries!A24,"")</f>
+        <v>45398.916666666664</v>
+      </c>
+      <c r="B24" s="1">
+        <v>2.3649999999999993</v>
+      </c>
+      <c r="C24" s="1">
+        <v>2.8950000000000005</v>
+      </c>
+      <c r="D24" s="1">
+        <v>2.8949999999999996</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A25" s="5">
+        <f>IF(timeseries!A25&lt;&gt;"",timeseries!A25,"")</f>
+        <v>45398.958333333336</v>
+      </c>
+      <c r="B25" s="1">
+        <v>2.5149999999999992</v>
+      </c>
+      <c r="C25" s="1">
+        <v>2.9450000000000003</v>
+      </c>
+      <c r="D25" s="1">
+        <v>2.7949999999999995</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5704FC51-737E-45F9-9A9E-85A96AFE5439}">
   <dimension ref="A1:M9"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="17.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="22.5703125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="25.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="17.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22.5546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="25.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>31</v>
       </c>
@@ -12146,7 +12185,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>66</v>
       </c>
@@ -12160,7 +12199,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>128</v>
       </c>
@@ -12174,10 +12213,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="K9" s="3"/>
-      <c r="L9" s="3"/>
-      <c r="M9" s="3"/>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="K9" s="2"/>
+      <c r="L9" s="2"/>
+      <c r="M9" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -12185,21 +12224,21 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BE12AB76-2BDA-4ACA-A128-8CFB9FB6C8F8}">
   <dimension ref="A1:S25"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="19.28515625" style="8" customWidth="1"/>
-    <col min="2" max="4" width="14.42578125" bestFit="1" customWidth="1"/>
-    <col min="5" max="7" width="14.140625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="19.140625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="20.42578125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.33203125" style="5" customWidth="1"/>
+    <col min="2" max="4" width="14.44140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="7" width="14.109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="19.109375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="20.44140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1" s="2" t="s">
         <v>24</v>
       </c>
       <c r="B1" t="s">
@@ -12257,8 +12296,8 @@
         <v>131</v>
       </c>
     </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A2" s="8">
+    <row r="2" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A2" s="5">
         <f>IF(timeseries!A2&lt;&gt;"",timeseries!A2,"")</f>
         <v>45398</v>
       </c>
@@ -12317,8 +12356,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A3" s="8">
+    <row r="3" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A3" s="5">
         <f>IF(timeseries!A3&lt;&gt;"",timeseries!A3,"")</f>
         <v>45398.041666666664</v>
       </c>
@@ -12377,8 +12416,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A4" s="8">
+    <row r="4" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A4" s="5">
         <f>IF(timeseries!A4&lt;&gt;"",timeseries!A4,"")</f>
         <v>45398.083333333336</v>
       </c>
@@ -12437,8 +12476,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A5" s="8">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A5" s="5">
         <f>IF(timeseries!A5&lt;&gt;"",timeseries!A5,"")</f>
         <v>45398.125</v>
       </c>
@@ -12497,8 +12536,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A6" s="8">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A6" s="5">
         <f>IF(timeseries!A6&lt;&gt;"",timeseries!A6,"")</f>
         <v>45398.166666666664</v>
       </c>
@@ -12557,8 +12596,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A7" s="8">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A7" s="5">
         <f>IF(timeseries!A7&lt;&gt;"",timeseries!A7,"")</f>
         <v>45398.208333333336</v>
       </c>
@@ -12617,8 +12656,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A8" s="8">
+    <row r="8" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A8" s="5">
         <f>IF(timeseries!A8&lt;&gt;"",timeseries!A8,"")</f>
         <v>45398.25</v>
       </c>
@@ -12677,8 +12716,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A9" s="8">
+    <row r="9" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A9" s="5">
         <f>IF(timeseries!A9&lt;&gt;"",timeseries!A9,"")</f>
         <v>45398.291666666664</v>
       </c>
@@ -12737,8 +12776,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A10" s="8">
+    <row r="10" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A10" s="5">
         <f>IF(timeseries!A10&lt;&gt;"",timeseries!A10,"")</f>
         <v>45398.333333333336</v>
       </c>
@@ -12797,8 +12836,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A11" s="8">
+    <row r="11" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A11" s="5">
         <f>IF(timeseries!A11&lt;&gt;"",timeseries!A11,"")</f>
         <v>45398.375</v>
       </c>
@@ -12857,8 +12896,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A12" s="8">
+    <row r="12" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A12" s="5">
         <f>IF(timeseries!A12&lt;&gt;"",timeseries!A12,"")</f>
         <v>45398.416666666664</v>
       </c>
@@ -12917,8 +12956,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A13" s="8">
+    <row r="13" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A13" s="5">
         <f>IF(timeseries!A13&lt;&gt;"",timeseries!A13,"")</f>
         <v>45398.458333333336</v>
       </c>
@@ -12977,8 +13016,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A14" s="8">
+    <row r="14" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A14" s="5">
         <f>IF(timeseries!A14&lt;&gt;"",timeseries!A14,"")</f>
         <v>45398.5</v>
       </c>
@@ -13037,8 +13076,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A15" s="8">
+    <row r="15" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A15" s="5">
         <f>IF(timeseries!A15&lt;&gt;"",timeseries!A15,"")</f>
         <v>45398.541666666664</v>
       </c>
@@ -13097,8 +13136,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A16" s="8">
+    <row r="16" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A16" s="5">
         <f>IF(timeseries!A16&lt;&gt;"",timeseries!A16,"")</f>
         <v>45398.583333333336</v>
       </c>
@@ -13157,8 +13196,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A17" s="8">
+    <row r="17" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A17" s="5">
         <f>IF(timeseries!A17&lt;&gt;"",timeseries!A17,"")</f>
         <v>45398.625</v>
       </c>
@@ -13217,8 +13256,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A18" s="8">
+    <row r="18" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A18" s="5">
         <f>IF(timeseries!A18&lt;&gt;"",timeseries!A18,"")</f>
         <v>45398.666666666664</v>
       </c>
@@ -13277,8 +13316,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A19" s="8">
+    <row r="19" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A19" s="5">
         <f>IF(timeseries!A19&lt;&gt;"",timeseries!A19,"")</f>
         <v>45398.708333333336</v>
       </c>
@@ -13337,8 +13376,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A20" s="8">
+    <row r="20" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A20" s="5">
         <f>IF(timeseries!A20&lt;&gt;"",timeseries!A20,"")</f>
         <v>45398.75</v>
       </c>
@@ -13397,8 +13436,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A21" s="8">
+    <row r="21" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A21" s="5">
         <f>IF(timeseries!A21&lt;&gt;"",timeseries!A21,"")</f>
         <v>45398.791666666664</v>
       </c>
@@ -13457,8 +13496,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A22" s="8">
+    <row r="22" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A22" s="5">
         <f>IF(timeseries!A22&lt;&gt;"",timeseries!A22,"")</f>
         <v>45398.833333333336</v>
       </c>
@@ -13517,8 +13556,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A23" s="8">
+    <row r="23" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A23" s="5">
         <f>IF(timeseries!A23&lt;&gt;"",timeseries!A23,"")</f>
         <v>45398.875</v>
       </c>
@@ -13577,8 +13616,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A24" s="8">
+    <row r="24" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A24" s="5">
         <f>IF(timeseries!A24&lt;&gt;"",timeseries!A24,"")</f>
         <v>45398.916666666664</v>
       </c>
@@ -13637,8 +13676,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A25" s="8">
+    <row r="25" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A25" s="5">
         <f>IF(timeseries!A25&lt;&gt;"",timeseries!A25,"")</f>
         <v>45398.958333333336</v>
       </c>
@@ -13707,319 +13746,319 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{04A1B16B-CDA9-46BD-BA51-731AA9327652}">
   <dimension ref="A1:Q6"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="7.28515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.85546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="6.140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.7109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="10.140625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="7.42578125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="8.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.5546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.88671875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="6.109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.6640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="7.44140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="3" t="s">
+    <row r="1" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="I1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="J1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="K1" s="3" t="s">
+      <c r="K1" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="L1" s="3" t="s">
+      <c r="L1" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="M1" s="3" t="s">
+      <c r="M1" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="N1" s="3" t="s">
+      <c r="N1" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="O1" s="3" t="s">
+      <c r="O1" s="2" t="s">
         <v>146</v>
       </c>
-      <c r="P1" s="3" t="s">
+      <c r="P1" s="2" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="7">
-        <v>1</v>
-      </c>
-      <c r="C2" s="7">
-        <v>0</v>
-      </c>
-      <c r="D2" s="7">
-        <v>0</v>
-      </c>
-      <c r="E2" s="7">
-        <v>0</v>
-      </c>
-      <c r="F2" s="7">
-        <v>0</v>
-      </c>
-      <c r="G2" s="7">
-        <v>0</v>
-      </c>
-      <c r="H2" s="7">
-        <v>0</v>
-      </c>
-      <c r="I2" s="7">
-        <v>0</v>
-      </c>
-      <c r="J2" s="7">
-        <v>0</v>
-      </c>
-      <c r="K2" s="7">
-        <v>0</v>
-      </c>
-      <c r="L2" s="7">
-        <v>0</v>
-      </c>
-      <c r="M2" s="7">
-        <v>0</v>
-      </c>
-      <c r="N2" s="7">
-        <v>0</v>
-      </c>
-      <c r="O2" s="7">
-        <v>1</v>
-      </c>
-      <c r="P2" s="7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="B2" s="4">
+        <v>1</v>
+      </c>
+      <c r="C2" s="4">
+        <v>0</v>
+      </c>
+      <c r="D2" s="4">
+        <v>0</v>
+      </c>
+      <c r="E2" s="4">
+        <v>0</v>
+      </c>
+      <c r="F2" s="4">
+        <v>0</v>
+      </c>
+      <c r="G2" s="4">
+        <v>0</v>
+      </c>
+      <c r="H2" s="4">
+        <v>0</v>
+      </c>
+      <c r="I2" s="4">
+        <v>0</v>
+      </c>
+      <c r="J2" s="4">
+        <v>0</v>
+      </c>
+      <c r="K2" s="4">
+        <v>0</v>
+      </c>
+      <c r="L2" s="4">
+        <v>0</v>
+      </c>
+      <c r="M2" s="4">
+        <v>0</v>
+      </c>
+      <c r="N2" s="4">
+        <v>0</v>
+      </c>
+      <c r="O2" s="4">
+        <v>1</v>
+      </c>
+      <c r="P2" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="7">
-        <v>0</v>
-      </c>
-      <c r="C3" s="7">
-        <v>0</v>
-      </c>
-      <c r="D3" s="7">
-        <v>0</v>
-      </c>
-      <c r="E3" s="7">
-        <v>0</v>
-      </c>
-      <c r="F3" s="7">
-        <v>0</v>
-      </c>
-      <c r="G3" s="7">
-        <v>0</v>
-      </c>
-      <c r="H3" s="7">
-        <v>0</v>
-      </c>
-      <c r="I3" s="7">
-        <v>0</v>
-      </c>
-      <c r="J3" s="7">
-        <v>0</v>
-      </c>
-      <c r="K3" s="7">
-        <v>0</v>
-      </c>
-      <c r="L3" s="7">
-        <v>0</v>
-      </c>
-      <c r="M3" s="7">
-        <v>0</v>
-      </c>
-      <c r="N3" s="7">
-        <v>0</v>
-      </c>
-      <c r="O3" s="7">
-        <v>1</v>
-      </c>
-      <c r="P3" s="7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="B3" s="4">
+        <v>0</v>
+      </c>
+      <c r="C3" s="4">
+        <v>0</v>
+      </c>
+      <c r="D3" s="4">
+        <v>0</v>
+      </c>
+      <c r="E3" s="4">
+        <v>0</v>
+      </c>
+      <c r="F3" s="4">
+        <v>0</v>
+      </c>
+      <c r="G3" s="4">
+        <v>0</v>
+      </c>
+      <c r="H3" s="4">
+        <v>0</v>
+      </c>
+      <c r="I3" s="4">
+        <v>0</v>
+      </c>
+      <c r="J3" s="4">
+        <v>0</v>
+      </c>
+      <c r="K3" s="4">
+        <v>0</v>
+      </c>
+      <c r="L3" s="4">
+        <v>0</v>
+      </c>
+      <c r="M3" s="4">
+        <v>0</v>
+      </c>
+      <c r="N3" s="4">
+        <v>0</v>
+      </c>
+      <c r="O3" s="4">
+        <v>1</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>107</v>
       </c>
-      <c r="B4" s="7">
-        <v>0</v>
-      </c>
-      <c r="C4" s="7">
-        <v>1</v>
-      </c>
-      <c r="D4" s="7">
-        <v>0</v>
-      </c>
-      <c r="E4" s="7">
-        <v>0</v>
-      </c>
-      <c r="F4" s="7">
-        <v>0</v>
-      </c>
-      <c r="G4" s="7">
+      <c r="B4" s="4">
+        <v>0</v>
+      </c>
+      <c r="C4" s="4">
+        <v>1</v>
+      </c>
+      <c r="D4" s="4">
+        <v>0</v>
+      </c>
+      <c r="E4" s="4">
+        <v>0</v>
+      </c>
+      <c r="F4" s="4">
+        <v>0</v>
+      </c>
+      <c r="G4" s="4">
         <v>10</v>
       </c>
-      <c r="H4" s="7">
-        <v>0</v>
-      </c>
-      <c r="I4" s="7">
+      <c r="H4" s="4">
+        <v>0</v>
+      </c>
+      <c r="I4" s="4">
         <v>3</v>
       </c>
-      <c r="J4" s="7">
+      <c r="J4" s="4">
         <v>3</v>
       </c>
-      <c r="K4" s="7">
-        <v>0</v>
-      </c>
-      <c r="L4" s="7">
+      <c r="K4" s="4">
+        <v>0</v>
+      </c>
+      <c r="L4" s="4">
         <v>1E-3</v>
       </c>
-      <c r="M4" s="7">
-        <v>0</v>
-      </c>
-      <c r="N4" s="7">
-        <v>0</v>
-      </c>
-      <c r="O4" s="7">
-        <v>1</v>
-      </c>
-      <c r="P4" s="7">
+      <c r="M4" s="4">
+        <v>0</v>
+      </c>
+      <c r="N4" s="4">
+        <v>0</v>
+      </c>
+      <c r="O4" s="4">
+        <v>1</v>
+      </c>
+      <c r="P4" s="4">
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>62</v>
       </c>
-      <c r="B5" s="7">
-        <v>0</v>
-      </c>
-      <c r="C5" s="7">
-        <v>0</v>
-      </c>
-      <c r="D5" s="7">
-        <v>0</v>
-      </c>
-      <c r="E5" s="7">
-        <v>0</v>
-      </c>
-      <c r="F5" s="7">
-        <v>1</v>
-      </c>
-      <c r="G5" s="7">
-        <v>0</v>
-      </c>
-      <c r="H5" s="7">
-        <v>0</v>
-      </c>
-      <c r="I5" s="7">
-        <v>0</v>
-      </c>
-      <c r="J5" s="7">
-        <v>0</v>
-      </c>
-      <c r="K5" s="7">
-        <v>0</v>
-      </c>
-      <c r="L5" s="7">
-        <v>0</v>
-      </c>
-      <c r="M5" s="7">
-        <v>0</v>
-      </c>
-      <c r="N5" s="7">
-        <v>0</v>
-      </c>
-      <c r="O5" s="7">
-        <v>1</v>
-      </c>
-      <c r="P5" s="7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A6" s="9" t="s">
+      <c r="B5" s="4">
+        <v>0</v>
+      </c>
+      <c r="C5" s="4">
+        <v>0</v>
+      </c>
+      <c r="D5" s="4">
+        <v>0</v>
+      </c>
+      <c r="E5" s="4">
+        <v>0</v>
+      </c>
+      <c r="F5" s="4">
+        <v>1</v>
+      </c>
+      <c r="G5" s="4">
+        <v>0</v>
+      </c>
+      <c r="H5" s="4">
+        <v>0</v>
+      </c>
+      <c r="I5" s="4">
+        <v>0</v>
+      </c>
+      <c r="J5" s="4">
+        <v>0</v>
+      </c>
+      <c r="K5" s="4">
+        <v>0</v>
+      </c>
+      <c r="L5" s="4">
+        <v>0</v>
+      </c>
+      <c r="M5" s="4">
+        <v>0</v>
+      </c>
+      <c r="N5" s="4">
+        <v>0</v>
+      </c>
+      <c r="O5" s="4">
+        <v>1</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
         <v>117</v>
       </c>
-      <c r="B6" s="7">
-        <v>1</v>
-      </c>
-      <c r="C6" s="7">
-        <v>0</v>
-      </c>
-      <c r="D6" s="7">
-        <v>0</v>
-      </c>
-      <c r="E6" s="7">
-        <v>0</v>
-      </c>
-      <c r="F6" s="7">
-        <v>0</v>
-      </c>
-      <c r="G6" s="7">
-        <v>0</v>
-      </c>
-      <c r="H6" s="7">
-        <v>0</v>
-      </c>
-      <c r="I6" s="7">
-        <v>0</v>
-      </c>
-      <c r="J6" s="7">
-        <v>0</v>
-      </c>
-      <c r="K6" s="7">
-        <v>0</v>
-      </c>
-      <c r="L6" s="7">
-        <v>0</v>
-      </c>
-      <c r="M6" s="7">
-        <v>0</v>
-      </c>
-      <c r="N6" s="7">
-        <v>0</v>
-      </c>
-      <c r="O6" s="7">
-        <v>1</v>
-      </c>
-      <c r="P6" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q6" s="3"/>
+      <c r="B6" s="4">
+        <v>1</v>
+      </c>
+      <c r="C6" s="4">
+        <v>0</v>
+      </c>
+      <c r="D6" s="4">
+        <v>0</v>
+      </c>
+      <c r="E6" s="4">
+        <v>0</v>
+      </c>
+      <c r="F6" s="4">
+        <v>0</v>
+      </c>
+      <c r="G6" s="4">
+        <v>0</v>
+      </c>
+      <c r="H6" s="4">
+        <v>0</v>
+      </c>
+      <c r="I6" s="4">
+        <v>0</v>
+      </c>
+      <c r="J6" s="4">
+        <v>0</v>
+      </c>
+      <c r="K6" s="4">
+        <v>0</v>
+      </c>
+      <c r="L6" s="4">
+        <v>0</v>
+      </c>
+      <c r="M6" s="4">
+        <v>0</v>
+      </c>
+      <c r="N6" s="4">
+        <v>0</v>
+      </c>
+      <c r="O6" s="4">
+        <v>1</v>
+      </c>
+      <c r="P6" s="4">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -14029,1084 +14068,1084 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CB20090B-02A9-43B7-8D03-9C18D42920EB}">
   <dimension ref="A1:Q221"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="16.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.88671875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="5" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.28515625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6.140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.7109375" customWidth="1"/>
+    <col min="3" max="3" width="8.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.6640625" customWidth="1"/>
     <col min="7" max="7" width="5" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="9.28515625" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="9.5703125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="11.140625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="11.42578125" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="11.42578125" customWidth="1"/>
-    <col min="16" max="16" width="9.140625" style="3"/>
+    <col min="8" max="8" width="9.33203125" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="9.5546875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11.109375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="11.44140625" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="11.44140625" customWidth="1"/>
+    <col min="16" max="16" width="9.109375" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="I1" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="J1" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="K1" s="3" t="s">
+      <c r="K1" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="L1" s="3" t="s">
+      <c r="L1" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="M1" s="3" t="s">
+      <c r="M1" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="N1" s="3" t="s">
+      <c r="N1" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="O1" s="3" t="s">
+      <c r="O1" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="P1" s="3" t="s">
+      <c r="P1" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="Q1" s="3" t="s">
+      <c r="Q1" s="2" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>63</v>
       </c>
-      <c r="B2" s="7">
-        <v>0</v>
-      </c>
-      <c r="C2" s="7">
-        <v>0</v>
-      </c>
-      <c r="D2" s="7">
-        <v>1</v>
-      </c>
-      <c r="E2" s="7">
-        <v>1</v>
-      </c>
-      <c r="F2" s="7">
-        <v>1</v>
-      </c>
-      <c r="G2" s="7">
+      <c r="B2" s="4">
+        <v>0</v>
+      </c>
+      <c r="C2" s="4">
+        <v>0</v>
+      </c>
+      <c r="D2" s="4">
+        <v>1</v>
+      </c>
+      <c r="E2" s="4">
+        <v>1</v>
+      </c>
+      <c r="F2" s="4">
+        <v>1</v>
+      </c>
+      <c r="G2" s="4">
         <v>0.9</v>
       </c>
-      <c r="H2" s="7">
+      <c r="H2" s="4">
         <v>0.4</v>
       </c>
-      <c r="I2" s="7">
-        <v>1</v>
-      </c>
-      <c r="J2" s="7">
-        <v>0</v>
-      </c>
-      <c r="K2" s="7">
-        <v>0</v>
-      </c>
-      <c r="L2" s="7">
-        <v>0</v>
-      </c>
-      <c r="M2" s="7">
-        <v>0</v>
-      </c>
-      <c r="N2" s="7">
-        <v>0</v>
-      </c>
-      <c r="O2" s="7">
-        <v>1</v>
-      </c>
-      <c r="P2" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q2" s="7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="I2" s="4">
+        <v>1</v>
+      </c>
+      <c r="J2" s="4">
+        <v>0</v>
+      </c>
+      <c r="K2" s="4">
+        <v>0</v>
+      </c>
+      <c r="L2" s="4">
+        <v>0</v>
+      </c>
+      <c r="M2" s="4">
+        <v>0</v>
+      </c>
+      <c r="N2" s="4">
+        <v>0</v>
+      </c>
+      <c r="O2" s="4">
+        <v>1</v>
+      </c>
+      <c r="P2" s="4">
+        <v>0</v>
+      </c>
+      <c r="Q2" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>124</v>
       </c>
-      <c r="B3" s="7">
-        <v>0</v>
-      </c>
-      <c r="C3" s="7">
-        <v>0</v>
-      </c>
-      <c r="D3" s="7">
-        <v>0</v>
-      </c>
-      <c r="E3" s="7">
-        <v>1</v>
-      </c>
-      <c r="F3" s="7">
-        <v>1</v>
-      </c>
-      <c r="G3" s="7">
-        <v>1</v>
-      </c>
-      <c r="H3" s="7">
-        <v>0</v>
-      </c>
-      <c r="I3" s="7">
-        <v>1</v>
-      </c>
-      <c r="J3" s="7">
-        <v>0</v>
-      </c>
-      <c r="K3" s="7">
-        <v>0</v>
-      </c>
-      <c r="L3" s="7">
-        <v>0</v>
-      </c>
-      <c r="M3" s="7">
-        <v>0</v>
-      </c>
-      <c r="N3" s="7">
-        <v>0</v>
-      </c>
-      <c r="O3" s="7">
-        <v>0</v>
-      </c>
-      <c r="P3" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q3" s="7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="B3" s="4">
+        <v>0</v>
+      </c>
+      <c r="C3" s="4">
+        <v>0</v>
+      </c>
+      <c r="D3" s="4">
+        <v>0</v>
+      </c>
+      <c r="E3" s="4">
+        <v>1</v>
+      </c>
+      <c r="F3" s="4">
+        <v>1</v>
+      </c>
+      <c r="G3" s="4">
+        <v>1</v>
+      </c>
+      <c r="H3" s="4">
+        <v>0</v>
+      </c>
+      <c r="I3" s="4">
+        <v>1</v>
+      </c>
+      <c r="J3" s="4">
+        <v>0</v>
+      </c>
+      <c r="K3" s="4">
+        <v>0</v>
+      </c>
+      <c r="L3" s="4">
+        <v>0</v>
+      </c>
+      <c r="M3" s="4">
+        <v>0</v>
+      </c>
+      <c r="N3" s="4">
+        <v>0</v>
+      </c>
+      <c r="O3" s="4">
+        <v>0</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>125</v>
       </c>
-      <c r="B4" s="7">
-        <v>0</v>
-      </c>
-      <c r="C4" s="7">
-        <v>0</v>
-      </c>
-      <c r="D4" s="7">
-        <v>0</v>
-      </c>
-      <c r="E4" s="7">
-        <v>1</v>
-      </c>
-      <c r="F4" s="7">
-        <v>1</v>
-      </c>
-      <c r="G4" s="7">
+      <c r="B4" s="4">
+        <v>0</v>
+      </c>
+      <c r="C4" s="4">
+        <v>0</v>
+      </c>
+      <c r="D4" s="4">
+        <v>0</v>
+      </c>
+      <c r="E4" s="4">
+        <v>1</v>
+      </c>
+      <c r="F4" s="4">
+        <v>1</v>
+      </c>
+      <c r="G4" s="4">
         <v>2</v>
       </c>
-      <c r="H4" s="7">
-        <v>0</v>
-      </c>
-      <c r="I4" s="7">
-        <v>1</v>
-      </c>
-      <c r="J4" s="7">
-        <v>0</v>
-      </c>
-      <c r="K4" s="7">
-        <v>0</v>
-      </c>
-      <c r="L4" s="7">
-        <v>0</v>
-      </c>
-      <c r="M4" s="7">
-        <v>0</v>
-      </c>
-      <c r="N4" s="7">
-        <v>0</v>
-      </c>
-      <c r="O4" s="7">
-        <v>0</v>
-      </c>
-      <c r="P4" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q4" s="7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="H4" s="4">
+        <v>0</v>
+      </c>
+      <c r="I4" s="4">
+        <v>1</v>
+      </c>
+      <c r="J4" s="4">
+        <v>0</v>
+      </c>
+      <c r="K4" s="4">
+        <v>0</v>
+      </c>
+      <c r="L4" s="4">
+        <v>0</v>
+      </c>
+      <c r="M4" s="4">
+        <v>0</v>
+      </c>
+      <c r="N4" s="4">
+        <v>0</v>
+      </c>
+      <c r="O4" s="4">
+        <v>0</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>109</v>
       </c>
-      <c r="B5" s="7">
-        <v>0</v>
-      </c>
-      <c r="C5" s="7">
-        <v>0</v>
-      </c>
-      <c r="D5" s="7">
-        <v>0</v>
-      </c>
-      <c r="E5" s="7">
-        <v>0</v>
-      </c>
-      <c r="F5" s="7">
-        <v>1</v>
-      </c>
-      <c r="G5" s="7">
+      <c r="B5" s="4">
+        <v>0</v>
+      </c>
+      <c r="C5" s="4">
+        <v>0</v>
+      </c>
+      <c r="D5" s="4">
+        <v>0</v>
+      </c>
+      <c r="E5" s="4">
+        <v>0</v>
+      </c>
+      <c r="F5" s="4">
+        <v>1</v>
+      </c>
+      <c r="G5" s="4">
         <v>0.99</v>
       </c>
-      <c r="H5" s="7">
-        <v>0</v>
-      </c>
-      <c r="I5" s="7">
-        <v>1</v>
-      </c>
-      <c r="J5" s="7">
-        <v>0</v>
-      </c>
-      <c r="K5" s="7">
-        <v>0</v>
-      </c>
-      <c r="L5" s="7">
-        <v>0</v>
-      </c>
-      <c r="M5" s="7">
-        <v>0</v>
-      </c>
-      <c r="N5" s="7">
-        <v>0</v>
-      </c>
-      <c r="O5" s="7">
-        <v>0</v>
-      </c>
-      <c r="P5" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q5" s="7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="H5" s="4">
+        <v>0</v>
+      </c>
+      <c r="I5" s="4">
+        <v>1</v>
+      </c>
+      <c r="J5" s="4">
+        <v>0</v>
+      </c>
+      <c r="K5" s="4">
+        <v>0</v>
+      </c>
+      <c r="L5" s="4">
+        <v>0</v>
+      </c>
+      <c r="M5" s="4">
+        <v>0</v>
+      </c>
+      <c r="N5" s="4">
+        <v>0</v>
+      </c>
+      <c r="O5" s="4">
+        <v>0</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>110</v>
       </c>
-      <c r="B6" s="7">
-        <v>0</v>
-      </c>
-      <c r="C6" s="7">
-        <v>0</v>
-      </c>
-      <c r="D6" s="7">
-        <v>0</v>
-      </c>
-      <c r="E6" s="7">
-        <v>0</v>
-      </c>
-      <c r="F6" s="7">
-        <v>1</v>
-      </c>
-      <c r="G6" s="7">
+      <c r="B6" s="4">
+        <v>0</v>
+      </c>
+      <c r="C6" s="4">
+        <v>0</v>
+      </c>
+      <c r="D6" s="4">
+        <v>0</v>
+      </c>
+      <c r="E6" s="4">
+        <v>0</v>
+      </c>
+      <c r="F6" s="4">
+        <v>1</v>
+      </c>
+      <c r="G6" s="4">
         <v>0.99</v>
       </c>
-      <c r="H6" s="7">
-        <v>0</v>
-      </c>
-      <c r="I6" s="7">
-        <v>1</v>
-      </c>
-      <c r="J6" s="7">
-        <v>0</v>
-      </c>
-      <c r="K6" s="7">
-        <v>0</v>
-      </c>
-      <c r="L6" s="7">
-        <v>0</v>
-      </c>
-      <c r="M6" s="7">
-        <v>0</v>
-      </c>
-      <c r="N6" s="7">
-        <v>0</v>
-      </c>
-      <c r="O6" s="7">
-        <v>0</v>
-      </c>
-      <c r="P6" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q6" s="7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="H6" s="4">
+        <v>0</v>
+      </c>
+      <c r="I6" s="4">
+        <v>1</v>
+      </c>
+      <c r="J6" s="4">
+        <v>0</v>
+      </c>
+      <c r="K6" s="4">
+        <v>0</v>
+      </c>
+      <c r="L6" s="4">
+        <v>0</v>
+      </c>
+      <c r="M6" s="4">
+        <v>0</v>
+      </c>
+      <c r="N6" s="4">
+        <v>0</v>
+      </c>
+      <c r="O6" s="4">
+        <v>0</v>
+      </c>
+      <c r="P6" s="4">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>108</v>
       </c>
-      <c r="B7" s="7">
-        <v>1</v>
-      </c>
-      <c r="C7" s="7">
-        <v>1</v>
-      </c>
-      <c r="D7" s="7">
-        <v>0</v>
-      </c>
-      <c r="E7" s="7">
-        <v>0</v>
-      </c>
-      <c r="F7" s="7">
-        <v>1</v>
-      </c>
-      <c r="G7" s="7">
-        <v>1</v>
-      </c>
-      <c r="H7" s="7">
-        <v>0</v>
-      </c>
-      <c r="I7" s="7">
-        <v>1</v>
-      </c>
-      <c r="J7" s="7">
-        <v>0</v>
-      </c>
-      <c r="K7" s="7">
-        <v>0</v>
-      </c>
-      <c r="L7" s="7">
-        <v>0</v>
-      </c>
-      <c r="M7" s="7">
-        <v>0</v>
-      </c>
-      <c r="N7" s="7">
-        <v>0</v>
-      </c>
-      <c r="O7" s="7">
-        <v>0</v>
-      </c>
-      <c r="P7" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q7" s="7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="B7" s="4">
+        <v>1</v>
+      </c>
+      <c r="C7" s="4">
+        <v>1</v>
+      </c>
+      <c r="D7" s="4">
+        <v>0</v>
+      </c>
+      <c r="E7" s="4">
+        <v>0</v>
+      </c>
+      <c r="F7" s="4">
+        <v>1</v>
+      </c>
+      <c r="G7" s="4">
+        <v>1</v>
+      </c>
+      <c r="H7" s="4">
+        <v>0</v>
+      </c>
+      <c r="I7" s="4">
+        <v>1</v>
+      </c>
+      <c r="J7" s="4">
+        <v>0</v>
+      </c>
+      <c r="K7" s="4">
+        <v>0</v>
+      </c>
+      <c r="L7" s="4">
+        <v>0</v>
+      </c>
+      <c r="M7" s="4">
+        <v>0</v>
+      </c>
+      <c r="N7" s="4">
+        <v>0</v>
+      </c>
+      <c r="O7" s="4">
+        <v>0</v>
+      </c>
+      <c r="P7" s="4">
+        <v>0</v>
+      </c>
+      <c r="Q7" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>111</v>
       </c>
-      <c r="B8" s="7">
-        <v>0</v>
-      </c>
-      <c r="C8" s="7">
-        <v>0</v>
-      </c>
-      <c r="D8" s="7">
-        <v>0</v>
-      </c>
-      <c r="E8" s="7">
-        <v>1</v>
-      </c>
-      <c r="F8" s="7">
-        <v>1</v>
-      </c>
-      <c r="G8" s="7">
+      <c r="B8" s="4">
+        <v>0</v>
+      </c>
+      <c r="C8" s="4">
+        <v>0</v>
+      </c>
+      <c r="D8" s="4">
+        <v>0</v>
+      </c>
+      <c r="E8" s="4">
+        <v>1</v>
+      </c>
+      <c r="F8" s="4">
+        <v>1</v>
+      </c>
+      <c r="G8" s="4">
         <v>0.96</v>
       </c>
-      <c r="H8" s="7">
-        <v>0</v>
-      </c>
-      <c r="I8" s="7">
-        <v>1</v>
-      </c>
-      <c r="J8" s="7">
-        <v>0</v>
-      </c>
-      <c r="K8" s="7">
-        <v>0</v>
-      </c>
-      <c r="L8" s="7">
-        <v>0</v>
-      </c>
-      <c r="M8" s="7">
-        <v>0</v>
-      </c>
-      <c r="N8" s="7">
-        <v>0</v>
-      </c>
-      <c r="O8" s="7">
-        <v>0</v>
-      </c>
-      <c r="P8" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q8" s="7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="P9" s="7"/>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="P10" s="7"/>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="P11" s="7"/>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="P12" s="7"/>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="P13" s="7"/>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="P14" s="7"/>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="P15" s="7"/>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="P16" s="7"/>
-    </row>
-    <row r="17" spans="16:16" x14ac:dyDescent="0.25">
-      <c r="P17" s="7"/>
-    </row>
-    <row r="18" spans="16:16" x14ac:dyDescent="0.25">
-      <c r="P18" s="7"/>
-    </row>
-    <row r="19" spans="16:16" x14ac:dyDescent="0.25">
-      <c r="P19" s="7"/>
-    </row>
-    <row r="20" spans="16:16" x14ac:dyDescent="0.25">
-      <c r="P20" s="7"/>
-    </row>
-    <row r="21" spans="16:16" x14ac:dyDescent="0.25">
-      <c r="P21" s="7"/>
-    </row>
-    <row r="22" spans="16:16" x14ac:dyDescent="0.25">
-      <c r="P22" s="7"/>
-    </row>
-    <row r="23" spans="16:16" x14ac:dyDescent="0.25">
-      <c r="P23" s="7"/>
-    </row>
-    <row r="24" spans="16:16" x14ac:dyDescent="0.25">
-      <c r="P24" s="7"/>
-    </row>
-    <row r="25" spans="16:16" x14ac:dyDescent="0.25">
-      <c r="P25" s="7"/>
-    </row>
-    <row r="26" spans="16:16" x14ac:dyDescent="0.25">
-      <c r="P26" s="7"/>
-    </row>
-    <row r="27" spans="16:16" x14ac:dyDescent="0.25">
-      <c r="P27" s="7"/>
-    </row>
-    <row r="28" spans="16:16" x14ac:dyDescent="0.25">
-      <c r="P28" s="7"/>
-    </row>
-    <row r="29" spans="16:16" x14ac:dyDescent="0.25">
-      <c r="P29" s="7"/>
-    </row>
-    <row r="30" spans="16:16" x14ac:dyDescent="0.25">
-      <c r="P30" s="7"/>
-    </row>
-    <row r="31" spans="16:16" x14ac:dyDescent="0.25">
-      <c r="P31" s="7"/>
-    </row>
-    <row r="32" spans="16:16" x14ac:dyDescent="0.25">
-      <c r="P32" s="7"/>
-    </row>
-    <row r="33" spans="16:16" x14ac:dyDescent="0.25">
-      <c r="P33" s="7"/>
-    </row>
-    <row r="34" spans="16:16" x14ac:dyDescent="0.25">
-      <c r="P34" s="7"/>
-    </row>
-    <row r="35" spans="16:16" x14ac:dyDescent="0.25">
-      <c r="P35" s="7"/>
-    </row>
-    <row r="36" spans="16:16" x14ac:dyDescent="0.25">
-      <c r="P36" s="7"/>
-    </row>
-    <row r="37" spans="16:16" x14ac:dyDescent="0.25">
-      <c r="P37" s="7"/>
-    </row>
-    <row r="38" spans="16:16" x14ac:dyDescent="0.25">
-      <c r="P38" s="7"/>
-    </row>
-    <row r="39" spans="16:16" x14ac:dyDescent="0.25">
-      <c r="P39" s="7"/>
-    </row>
-    <row r="40" spans="16:16" x14ac:dyDescent="0.25">
-      <c r="P40" s="7"/>
-    </row>
-    <row r="41" spans="16:16" x14ac:dyDescent="0.25">
-      <c r="P41" s="7"/>
-    </row>
-    <row r="42" spans="16:16" x14ac:dyDescent="0.25">
-      <c r="P42" s="7"/>
-    </row>
-    <row r="43" spans="16:16" x14ac:dyDescent="0.25">
-      <c r="P43" s="7"/>
-    </row>
-    <row r="44" spans="16:16" x14ac:dyDescent="0.25">
-      <c r="P44" s="7"/>
-    </row>
-    <row r="45" spans="16:16" x14ac:dyDescent="0.25">
-      <c r="P45" s="7"/>
-    </row>
-    <row r="46" spans="16:16" x14ac:dyDescent="0.25">
-      <c r="P46" s="7"/>
-    </row>
-    <row r="47" spans="16:16" x14ac:dyDescent="0.25">
-      <c r="P47" s="7"/>
-    </row>
-    <row r="48" spans="16:16" x14ac:dyDescent="0.25">
-      <c r="P48" s="7"/>
-    </row>
-    <row r="49" spans="16:16" x14ac:dyDescent="0.25">
-      <c r="P49" s="7"/>
-    </row>
-    <row r="50" spans="16:16" x14ac:dyDescent="0.25">
-      <c r="P50" s="7"/>
-    </row>
-    <row r="51" spans="16:16" x14ac:dyDescent="0.25">
-      <c r="P51" s="7"/>
-    </row>
-    <row r="52" spans="16:16" x14ac:dyDescent="0.25">
-      <c r="P52" s="7"/>
-    </row>
-    <row r="53" spans="16:16" x14ac:dyDescent="0.25">
-      <c r="P53" s="7"/>
-    </row>
-    <row r="54" spans="16:16" x14ac:dyDescent="0.25">
-      <c r="P54" s="7"/>
-    </row>
-    <row r="55" spans="16:16" x14ac:dyDescent="0.25">
-      <c r="P55" s="7"/>
-    </row>
-    <row r="56" spans="16:16" x14ac:dyDescent="0.25">
-      <c r="P56" s="7"/>
-    </row>
-    <row r="57" spans="16:16" x14ac:dyDescent="0.25">
-      <c r="P57" s="7"/>
-    </row>
-    <row r="58" spans="16:16" x14ac:dyDescent="0.25">
-      <c r="P58" s="7"/>
-    </row>
-    <row r="59" spans="16:16" x14ac:dyDescent="0.25">
-      <c r="P59" s="7"/>
-    </row>
-    <row r="60" spans="16:16" x14ac:dyDescent="0.25">
-      <c r="P60" s="7"/>
-    </row>
-    <row r="61" spans="16:16" x14ac:dyDescent="0.25">
-      <c r="P61" s="7"/>
-    </row>
-    <row r="62" spans="16:16" x14ac:dyDescent="0.25">
-      <c r="P62" s="7"/>
-    </row>
-    <row r="63" spans="16:16" x14ac:dyDescent="0.25">
-      <c r="P63" s="7"/>
-    </row>
-    <row r="64" spans="16:16" x14ac:dyDescent="0.25">
-      <c r="P64" s="7"/>
-    </row>
-    <row r="65" spans="16:16" x14ac:dyDescent="0.25">
-      <c r="P65" s="7"/>
-    </row>
-    <row r="66" spans="16:16" x14ac:dyDescent="0.25">
-      <c r="P66" s="7"/>
-    </row>
-    <row r="67" spans="16:16" x14ac:dyDescent="0.25">
-      <c r="P67" s="7"/>
-    </row>
-    <row r="68" spans="16:16" x14ac:dyDescent="0.25">
-      <c r="P68" s="7"/>
-    </row>
-    <row r="69" spans="16:16" x14ac:dyDescent="0.25">
-      <c r="P69" s="7"/>
-    </row>
-    <row r="70" spans="16:16" x14ac:dyDescent="0.25">
-      <c r="P70" s="7"/>
-    </row>
-    <row r="71" spans="16:16" x14ac:dyDescent="0.25">
-      <c r="P71" s="7"/>
-    </row>
-    <row r="72" spans="16:16" x14ac:dyDescent="0.25">
-      <c r="P72" s="7"/>
-    </row>
-    <row r="73" spans="16:16" x14ac:dyDescent="0.25">
-      <c r="P73" s="7"/>
-    </row>
-    <row r="74" spans="16:16" x14ac:dyDescent="0.25">
-      <c r="P74" s="7"/>
-    </row>
-    <row r="75" spans="16:16" x14ac:dyDescent="0.25">
-      <c r="P75" s="7"/>
-    </row>
-    <row r="76" spans="16:16" x14ac:dyDescent="0.25">
-      <c r="P76" s="7"/>
-    </row>
-    <row r="77" spans="16:16" x14ac:dyDescent="0.25">
-      <c r="P77" s="7"/>
-    </row>
-    <row r="78" spans="16:16" x14ac:dyDescent="0.25">
-      <c r="P78" s="7"/>
-    </row>
-    <row r="79" spans="16:16" x14ac:dyDescent="0.25">
-      <c r="P79" s="7"/>
-    </row>
-    <row r="80" spans="16:16" x14ac:dyDescent="0.25">
-      <c r="P80" s="7"/>
-    </row>
-    <row r="81" spans="16:16" x14ac:dyDescent="0.25">
-      <c r="P81" s="7"/>
-    </row>
-    <row r="82" spans="16:16" x14ac:dyDescent="0.25">
-      <c r="P82" s="7"/>
-    </row>
-    <row r="83" spans="16:16" x14ac:dyDescent="0.25">
-      <c r="P83" s="7"/>
-    </row>
-    <row r="84" spans="16:16" x14ac:dyDescent="0.25">
-      <c r="P84" s="7"/>
-    </row>
-    <row r="85" spans="16:16" x14ac:dyDescent="0.25">
-      <c r="P85" s="7"/>
-    </row>
-    <row r="86" spans="16:16" x14ac:dyDescent="0.25">
-      <c r="P86" s="7"/>
-    </row>
-    <row r="87" spans="16:16" x14ac:dyDescent="0.25">
-      <c r="P87" s="7"/>
-    </row>
-    <row r="88" spans="16:16" x14ac:dyDescent="0.25">
-      <c r="P88" s="7"/>
-    </row>
-    <row r="89" spans="16:16" x14ac:dyDescent="0.25">
-      <c r="P89" s="7"/>
-    </row>
-    <row r="90" spans="16:16" x14ac:dyDescent="0.25">
-      <c r="P90" s="7"/>
-    </row>
-    <row r="91" spans="16:16" x14ac:dyDescent="0.25">
-      <c r="P91" s="7"/>
-    </row>
-    <row r="92" spans="16:16" x14ac:dyDescent="0.25">
-      <c r="P92" s="7"/>
-    </row>
-    <row r="93" spans="16:16" x14ac:dyDescent="0.25">
-      <c r="P93" s="7"/>
-    </row>
-    <row r="94" spans="16:16" x14ac:dyDescent="0.25">
-      <c r="P94" s="7"/>
-    </row>
-    <row r="95" spans="16:16" x14ac:dyDescent="0.25">
-      <c r="P95" s="7"/>
-    </row>
-    <row r="96" spans="16:16" x14ac:dyDescent="0.25">
-      <c r="P96" s="7"/>
-    </row>
-    <row r="97" spans="16:16" x14ac:dyDescent="0.25">
-      <c r="P97" s="7"/>
-    </row>
-    <row r="98" spans="16:16" x14ac:dyDescent="0.25">
-      <c r="P98" s="7"/>
-    </row>
-    <row r="99" spans="16:16" x14ac:dyDescent="0.25">
-      <c r="P99" s="7"/>
-    </row>
-    <row r="100" spans="16:16" x14ac:dyDescent="0.25">
-      <c r="P100" s="7"/>
-    </row>
-    <row r="101" spans="16:16" x14ac:dyDescent="0.25">
-      <c r="P101" s="7"/>
-    </row>
-    <row r="102" spans="16:16" x14ac:dyDescent="0.25">
-      <c r="P102" s="7"/>
-    </row>
-    <row r="103" spans="16:16" x14ac:dyDescent="0.25">
-      <c r="P103" s="7"/>
-    </row>
-    <row r="104" spans="16:16" x14ac:dyDescent="0.25">
-      <c r="P104" s="7"/>
-    </row>
-    <row r="105" spans="16:16" x14ac:dyDescent="0.25">
-      <c r="P105" s="7"/>
-    </row>
-    <row r="106" spans="16:16" x14ac:dyDescent="0.25">
-      <c r="P106" s="7"/>
-    </row>
-    <row r="107" spans="16:16" x14ac:dyDescent="0.25">
-      <c r="P107" s="7"/>
-    </row>
-    <row r="108" spans="16:16" x14ac:dyDescent="0.25">
-      <c r="P108" s="7"/>
-    </row>
-    <row r="109" spans="16:16" x14ac:dyDescent="0.25">
-      <c r="P109" s="7"/>
-    </row>
-    <row r="110" spans="16:16" x14ac:dyDescent="0.25">
-      <c r="P110" s="7"/>
-    </row>
-    <row r="111" spans="16:16" x14ac:dyDescent="0.25">
-      <c r="P111" s="7"/>
-    </row>
-    <row r="112" spans="16:16" x14ac:dyDescent="0.25">
-      <c r="P112" s="7"/>
-    </row>
-    <row r="113" spans="16:16" x14ac:dyDescent="0.25">
-      <c r="P113" s="7"/>
-    </row>
-    <row r="114" spans="16:16" x14ac:dyDescent="0.25">
-      <c r="P114" s="7"/>
-    </row>
-    <row r="115" spans="16:16" x14ac:dyDescent="0.25">
-      <c r="P115" s="7"/>
-    </row>
-    <row r="116" spans="16:16" x14ac:dyDescent="0.25">
-      <c r="P116" s="7"/>
-    </row>
-    <row r="117" spans="16:16" x14ac:dyDescent="0.25">
-      <c r="P117" s="7"/>
-    </row>
-    <row r="118" spans="16:16" x14ac:dyDescent="0.25">
-      <c r="P118" s="7"/>
-    </row>
-    <row r="119" spans="16:16" x14ac:dyDescent="0.25">
-      <c r="P119" s="7"/>
-    </row>
-    <row r="120" spans="16:16" x14ac:dyDescent="0.25">
-      <c r="P120" s="7"/>
-    </row>
-    <row r="121" spans="16:16" x14ac:dyDescent="0.25">
-      <c r="P121" s="7"/>
-    </row>
-    <row r="122" spans="16:16" x14ac:dyDescent="0.25">
-      <c r="P122" s="7"/>
-    </row>
-    <row r="123" spans="16:16" x14ac:dyDescent="0.25">
-      <c r="P123" s="7"/>
-    </row>
-    <row r="124" spans="16:16" x14ac:dyDescent="0.25">
-      <c r="P124" s="7"/>
-    </row>
-    <row r="125" spans="16:16" x14ac:dyDescent="0.25">
-      <c r="P125" s="7"/>
-    </row>
-    <row r="126" spans="16:16" x14ac:dyDescent="0.25">
-      <c r="P126" s="7"/>
-    </row>
-    <row r="127" spans="16:16" x14ac:dyDescent="0.25">
-      <c r="P127" s="7"/>
-    </row>
-    <row r="128" spans="16:16" x14ac:dyDescent="0.25">
-      <c r="P128" s="7"/>
-    </row>
-    <row r="129" spans="16:16" x14ac:dyDescent="0.25">
-      <c r="P129" s="7"/>
-    </row>
-    <row r="130" spans="16:16" x14ac:dyDescent="0.25">
-      <c r="P130" s="7"/>
-    </row>
-    <row r="131" spans="16:16" x14ac:dyDescent="0.25">
-      <c r="P131" s="7"/>
-    </row>
-    <row r="132" spans="16:16" x14ac:dyDescent="0.25">
-      <c r="P132" s="7"/>
-    </row>
-    <row r="133" spans="16:16" x14ac:dyDescent="0.25">
-      <c r="P133" s="7"/>
-    </row>
-    <row r="134" spans="16:16" x14ac:dyDescent="0.25">
-      <c r="P134" s="7"/>
-    </row>
-    <row r="135" spans="16:16" x14ac:dyDescent="0.25">
-      <c r="P135" s="7"/>
-    </row>
-    <row r="136" spans="16:16" x14ac:dyDescent="0.25">
-      <c r="P136" s="7"/>
-    </row>
-    <row r="137" spans="16:16" x14ac:dyDescent="0.25">
-      <c r="P137" s="7"/>
-    </row>
-    <row r="138" spans="16:16" x14ac:dyDescent="0.25">
-      <c r="P138" s="7"/>
-    </row>
-    <row r="139" spans="16:16" x14ac:dyDescent="0.25">
-      <c r="P139" s="7"/>
-    </row>
-    <row r="140" spans="16:16" x14ac:dyDescent="0.25">
-      <c r="P140" s="7"/>
-    </row>
-    <row r="141" spans="16:16" x14ac:dyDescent="0.25">
-      <c r="P141" s="7"/>
-    </row>
-    <row r="142" spans="16:16" x14ac:dyDescent="0.25">
-      <c r="P142" s="7"/>
-    </row>
-    <row r="143" spans="16:16" x14ac:dyDescent="0.25">
-      <c r="P143" s="7"/>
-    </row>
-    <row r="144" spans="16:16" x14ac:dyDescent="0.25">
-      <c r="P144" s="7"/>
-    </row>
-    <row r="145" spans="16:16" x14ac:dyDescent="0.25">
-      <c r="P145" s="7"/>
-    </row>
-    <row r="146" spans="16:16" x14ac:dyDescent="0.25">
-      <c r="P146" s="7"/>
-    </row>
-    <row r="147" spans="16:16" x14ac:dyDescent="0.25">
-      <c r="P147" s="7"/>
-    </row>
-    <row r="148" spans="16:16" x14ac:dyDescent="0.25">
-      <c r="P148" s="7"/>
-    </row>
-    <row r="149" spans="16:16" x14ac:dyDescent="0.25">
-      <c r="P149" s="7"/>
-    </row>
-    <row r="150" spans="16:16" x14ac:dyDescent="0.25">
-      <c r="P150" s="7"/>
-    </row>
-    <row r="151" spans="16:16" x14ac:dyDescent="0.25">
-      <c r="P151" s="7"/>
-    </row>
-    <row r="152" spans="16:16" x14ac:dyDescent="0.25">
-      <c r="P152" s="7"/>
-    </row>
-    <row r="153" spans="16:16" x14ac:dyDescent="0.25">
-      <c r="P153" s="7"/>
-    </row>
-    <row r="154" spans="16:16" x14ac:dyDescent="0.25">
-      <c r="P154" s="7"/>
-    </row>
-    <row r="155" spans="16:16" x14ac:dyDescent="0.25">
-      <c r="P155" s="7"/>
-    </row>
-    <row r="156" spans="16:16" x14ac:dyDescent="0.25">
-      <c r="P156" s="7"/>
-    </row>
-    <row r="157" spans="16:16" x14ac:dyDescent="0.25">
-      <c r="P157" s="7"/>
-    </row>
-    <row r="158" spans="16:16" x14ac:dyDescent="0.25">
-      <c r="P158" s="7"/>
-    </row>
-    <row r="159" spans="16:16" x14ac:dyDescent="0.25">
-      <c r="P159" s="7"/>
-    </row>
-    <row r="160" spans="16:16" x14ac:dyDescent="0.25">
-      <c r="P160" s="7"/>
-    </row>
-    <row r="161" spans="16:16" x14ac:dyDescent="0.25">
-      <c r="P161" s="7"/>
-    </row>
-    <row r="162" spans="16:16" x14ac:dyDescent="0.25">
-      <c r="P162" s="7"/>
-    </row>
-    <row r="163" spans="16:16" x14ac:dyDescent="0.25">
-      <c r="P163" s="7"/>
-    </row>
-    <row r="164" spans="16:16" x14ac:dyDescent="0.25">
-      <c r="P164" s="7"/>
-    </row>
-    <row r="165" spans="16:16" x14ac:dyDescent="0.25">
-      <c r="P165" s="7"/>
-    </row>
-    <row r="166" spans="16:16" x14ac:dyDescent="0.25">
-      <c r="P166" s="7"/>
-    </row>
-    <row r="167" spans="16:16" x14ac:dyDescent="0.25">
-      <c r="P167" s="7"/>
-    </row>
-    <row r="168" spans="16:16" x14ac:dyDescent="0.25">
-      <c r="P168" s="7"/>
-    </row>
-    <row r="169" spans="16:16" x14ac:dyDescent="0.25">
-      <c r="P169" s="7"/>
-    </row>
-    <row r="170" spans="16:16" x14ac:dyDescent="0.25">
-      <c r="P170" s="7"/>
-    </row>
-    <row r="171" spans="16:16" x14ac:dyDescent="0.25">
-      <c r="P171" s="7"/>
-    </row>
-    <row r="172" spans="16:16" x14ac:dyDescent="0.25">
-      <c r="P172" s="7"/>
-    </row>
-    <row r="173" spans="16:16" x14ac:dyDescent="0.25">
-      <c r="P173" s="7"/>
-    </row>
-    <row r="174" spans="16:16" x14ac:dyDescent="0.25">
-      <c r="P174" s="7"/>
-    </row>
-    <row r="175" spans="16:16" x14ac:dyDescent="0.25">
-      <c r="P175" s="7"/>
-    </row>
-    <row r="176" spans="16:16" x14ac:dyDescent="0.25">
-      <c r="P176" s="7"/>
-    </row>
-    <row r="177" spans="16:16" x14ac:dyDescent="0.25">
-      <c r="P177" s="7"/>
-    </row>
-    <row r="178" spans="16:16" x14ac:dyDescent="0.25">
-      <c r="P178" s="7"/>
-    </row>
-    <row r="179" spans="16:16" x14ac:dyDescent="0.25">
-      <c r="P179" s="7"/>
-    </row>
-    <row r="180" spans="16:16" x14ac:dyDescent="0.25">
-      <c r="P180" s="7"/>
-    </row>
-    <row r="181" spans="16:16" x14ac:dyDescent="0.25">
-      <c r="P181" s="7"/>
-    </row>
-    <row r="182" spans="16:16" x14ac:dyDescent="0.25">
-      <c r="P182" s="7"/>
-    </row>
-    <row r="183" spans="16:16" x14ac:dyDescent="0.25">
-      <c r="P183" s="7"/>
-    </row>
-    <row r="184" spans="16:16" x14ac:dyDescent="0.25">
-      <c r="P184" s="7"/>
-    </row>
-    <row r="185" spans="16:16" x14ac:dyDescent="0.25">
-      <c r="P185" s="7"/>
-    </row>
-    <row r="186" spans="16:16" x14ac:dyDescent="0.25">
-      <c r="P186" s="7"/>
-    </row>
-    <row r="187" spans="16:16" x14ac:dyDescent="0.25">
-      <c r="P187" s="7"/>
-    </row>
-    <row r="188" spans="16:16" x14ac:dyDescent="0.25">
-      <c r="P188" s="7"/>
-    </row>
-    <row r="189" spans="16:16" x14ac:dyDescent="0.25">
-      <c r="P189" s="7"/>
-    </row>
-    <row r="190" spans="16:16" x14ac:dyDescent="0.25">
-      <c r="P190" s="7"/>
-    </row>
-    <row r="191" spans="16:16" x14ac:dyDescent="0.25">
-      <c r="P191" s="7"/>
-    </row>
-    <row r="192" spans="16:16" x14ac:dyDescent="0.25">
-      <c r="P192" s="7"/>
-    </row>
-    <row r="193" spans="16:16" x14ac:dyDescent="0.25">
-      <c r="P193" s="7"/>
-    </row>
-    <row r="194" spans="16:16" x14ac:dyDescent="0.25">
-      <c r="P194" s="7"/>
-    </row>
-    <row r="195" spans="16:16" x14ac:dyDescent="0.25">
-      <c r="P195" s="7"/>
-    </row>
-    <row r="196" spans="16:16" x14ac:dyDescent="0.25">
-      <c r="P196" s="7"/>
-    </row>
-    <row r="197" spans="16:16" x14ac:dyDescent="0.25">
-      <c r="P197" s="7"/>
-    </row>
-    <row r="198" spans="16:16" x14ac:dyDescent="0.25">
-      <c r="P198" s="7"/>
-    </row>
-    <row r="199" spans="16:16" x14ac:dyDescent="0.25">
-      <c r="P199" s="7"/>
-    </row>
-    <row r="200" spans="16:16" x14ac:dyDescent="0.25">
-      <c r="P200" s="7"/>
-    </row>
-    <row r="201" spans="16:16" x14ac:dyDescent="0.25">
-      <c r="P201" s="7"/>
-    </row>
-    <row r="202" spans="16:16" x14ac:dyDescent="0.25">
-      <c r="P202" s="7"/>
-    </row>
-    <row r="203" spans="16:16" x14ac:dyDescent="0.25">
-      <c r="P203" s="7"/>
-    </row>
-    <row r="204" spans="16:16" x14ac:dyDescent="0.25">
-      <c r="P204" s="7"/>
-    </row>
-    <row r="205" spans="16:16" x14ac:dyDescent="0.25">
-      <c r="P205" s="7"/>
-    </row>
-    <row r="206" spans="16:16" x14ac:dyDescent="0.25">
-      <c r="P206" s="7"/>
-    </row>
-    <row r="207" spans="16:16" x14ac:dyDescent="0.25">
-      <c r="P207" s="7"/>
-    </row>
-    <row r="208" spans="16:16" x14ac:dyDescent="0.25">
-      <c r="P208" s="7"/>
-    </row>
-    <row r="209" spans="16:16" x14ac:dyDescent="0.25">
-      <c r="P209" s="7"/>
-    </row>
-    <row r="210" spans="16:16" x14ac:dyDescent="0.25">
-      <c r="P210" s="7"/>
-    </row>
-    <row r="211" spans="16:16" x14ac:dyDescent="0.25">
-      <c r="P211" s="7"/>
-    </row>
-    <row r="212" spans="16:16" x14ac:dyDescent="0.25">
-      <c r="P212" s="7"/>
-    </row>
-    <row r="213" spans="16:16" x14ac:dyDescent="0.25">
-      <c r="P213" s="7"/>
-    </row>
-    <row r="214" spans="16:16" x14ac:dyDescent="0.25">
-      <c r="P214" s="7"/>
-    </row>
-    <row r="215" spans="16:16" x14ac:dyDescent="0.25">
-      <c r="P215" s="7"/>
-    </row>
-    <row r="216" spans="16:16" x14ac:dyDescent="0.25">
-      <c r="P216" s="7"/>
-    </row>
-    <row r="217" spans="16:16" x14ac:dyDescent="0.25">
-      <c r="P217" s="7"/>
-    </row>
-    <row r="218" spans="16:16" x14ac:dyDescent="0.25">
-      <c r="P218" s="7"/>
-    </row>
-    <row r="219" spans="16:16" x14ac:dyDescent="0.25">
-      <c r="P219" s="7"/>
-    </row>
-    <row r="220" spans="16:16" x14ac:dyDescent="0.25">
-      <c r="P220" s="7"/>
-    </row>
-    <row r="221" spans="16:16" x14ac:dyDescent="0.25">
-      <c r="P221" s="7"/>
+      <c r="H8" s="4">
+        <v>0</v>
+      </c>
+      <c r="I8" s="4">
+        <v>1</v>
+      </c>
+      <c r="J8" s="4">
+        <v>0</v>
+      </c>
+      <c r="K8" s="4">
+        <v>0</v>
+      </c>
+      <c r="L8" s="4">
+        <v>0</v>
+      </c>
+      <c r="M8" s="4">
+        <v>0</v>
+      </c>
+      <c r="N8" s="4">
+        <v>0</v>
+      </c>
+      <c r="O8" s="4">
+        <v>0</v>
+      </c>
+      <c r="P8" s="4">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="P9" s="4"/>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="P10" s="4"/>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="P11" s="4"/>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="P12" s="4"/>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="P13" s="4"/>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="P14" s="4"/>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="P15" s="4"/>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="P16" s="4"/>
+    </row>
+    <row r="17" spans="16:16" x14ac:dyDescent="0.3">
+      <c r="P17" s="4"/>
+    </row>
+    <row r="18" spans="16:16" x14ac:dyDescent="0.3">
+      <c r="P18" s="4"/>
+    </row>
+    <row r="19" spans="16:16" x14ac:dyDescent="0.3">
+      <c r="P19" s="4"/>
+    </row>
+    <row r="20" spans="16:16" x14ac:dyDescent="0.3">
+      <c r="P20" s="4"/>
+    </row>
+    <row r="21" spans="16:16" x14ac:dyDescent="0.3">
+      <c r="P21" s="4"/>
+    </row>
+    <row r="22" spans="16:16" x14ac:dyDescent="0.3">
+      <c r="P22" s="4"/>
+    </row>
+    <row r="23" spans="16:16" x14ac:dyDescent="0.3">
+      <c r="P23" s="4"/>
+    </row>
+    <row r="24" spans="16:16" x14ac:dyDescent="0.3">
+      <c r="P24" s="4"/>
+    </row>
+    <row r="25" spans="16:16" x14ac:dyDescent="0.3">
+      <c r="P25" s="4"/>
+    </row>
+    <row r="26" spans="16:16" x14ac:dyDescent="0.3">
+      <c r="P26" s="4"/>
+    </row>
+    <row r="27" spans="16:16" x14ac:dyDescent="0.3">
+      <c r="P27" s="4"/>
+    </row>
+    <row r="28" spans="16:16" x14ac:dyDescent="0.3">
+      <c r="P28" s="4"/>
+    </row>
+    <row r="29" spans="16:16" x14ac:dyDescent="0.3">
+      <c r="P29" s="4"/>
+    </row>
+    <row r="30" spans="16:16" x14ac:dyDescent="0.3">
+      <c r="P30" s="4"/>
+    </row>
+    <row r="31" spans="16:16" x14ac:dyDescent="0.3">
+      <c r="P31" s="4"/>
+    </row>
+    <row r="32" spans="16:16" x14ac:dyDescent="0.3">
+      <c r="P32" s="4"/>
+    </row>
+    <row r="33" spans="16:16" x14ac:dyDescent="0.3">
+      <c r="P33" s="4"/>
+    </row>
+    <row r="34" spans="16:16" x14ac:dyDescent="0.3">
+      <c r="P34" s="4"/>
+    </row>
+    <row r="35" spans="16:16" x14ac:dyDescent="0.3">
+      <c r="P35" s="4"/>
+    </row>
+    <row r="36" spans="16:16" x14ac:dyDescent="0.3">
+      <c r="P36" s="4"/>
+    </row>
+    <row r="37" spans="16:16" x14ac:dyDescent="0.3">
+      <c r="P37" s="4"/>
+    </row>
+    <row r="38" spans="16:16" x14ac:dyDescent="0.3">
+      <c r="P38" s="4"/>
+    </row>
+    <row r="39" spans="16:16" x14ac:dyDescent="0.3">
+      <c r="P39" s="4"/>
+    </row>
+    <row r="40" spans="16:16" x14ac:dyDescent="0.3">
+      <c r="P40" s="4"/>
+    </row>
+    <row r="41" spans="16:16" x14ac:dyDescent="0.3">
+      <c r="P41" s="4"/>
+    </row>
+    <row r="42" spans="16:16" x14ac:dyDescent="0.3">
+      <c r="P42" s="4"/>
+    </row>
+    <row r="43" spans="16:16" x14ac:dyDescent="0.3">
+      <c r="P43" s="4"/>
+    </row>
+    <row r="44" spans="16:16" x14ac:dyDescent="0.3">
+      <c r="P44" s="4"/>
+    </row>
+    <row r="45" spans="16:16" x14ac:dyDescent="0.3">
+      <c r="P45" s="4"/>
+    </row>
+    <row r="46" spans="16:16" x14ac:dyDescent="0.3">
+      <c r="P46" s="4"/>
+    </row>
+    <row r="47" spans="16:16" x14ac:dyDescent="0.3">
+      <c r="P47" s="4"/>
+    </row>
+    <row r="48" spans="16:16" x14ac:dyDescent="0.3">
+      <c r="P48" s="4"/>
+    </row>
+    <row r="49" spans="16:16" x14ac:dyDescent="0.3">
+      <c r="P49" s="4"/>
+    </row>
+    <row r="50" spans="16:16" x14ac:dyDescent="0.3">
+      <c r="P50" s="4"/>
+    </row>
+    <row r="51" spans="16:16" x14ac:dyDescent="0.3">
+      <c r="P51" s="4"/>
+    </row>
+    <row r="52" spans="16:16" x14ac:dyDescent="0.3">
+      <c r="P52" s="4"/>
+    </row>
+    <row r="53" spans="16:16" x14ac:dyDescent="0.3">
+      <c r="P53" s="4"/>
+    </row>
+    <row r="54" spans="16:16" x14ac:dyDescent="0.3">
+      <c r="P54" s="4"/>
+    </row>
+    <row r="55" spans="16:16" x14ac:dyDescent="0.3">
+      <c r="P55" s="4"/>
+    </row>
+    <row r="56" spans="16:16" x14ac:dyDescent="0.3">
+      <c r="P56" s="4"/>
+    </row>
+    <row r="57" spans="16:16" x14ac:dyDescent="0.3">
+      <c r="P57" s="4"/>
+    </row>
+    <row r="58" spans="16:16" x14ac:dyDescent="0.3">
+      <c r="P58" s="4"/>
+    </row>
+    <row r="59" spans="16:16" x14ac:dyDescent="0.3">
+      <c r="P59" s="4"/>
+    </row>
+    <row r="60" spans="16:16" x14ac:dyDescent="0.3">
+      <c r="P60" s="4"/>
+    </row>
+    <row r="61" spans="16:16" x14ac:dyDescent="0.3">
+      <c r="P61" s="4"/>
+    </row>
+    <row r="62" spans="16:16" x14ac:dyDescent="0.3">
+      <c r="P62" s="4"/>
+    </row>
+    <row r="63" spans="16:16" x14ac:dyDescent="0.3">
+      <c r="P63" s="4"/>
+    </row>
+    <row r="64" spans="16:16" x14ac:dyDescent="0.3">
+      <c r="P64" s="4"/>
+    </row>
+    <row r="65" spans="16:16" x14ac:dyDescent="0.3">
+      <c r="P65" s="4"/>
+    </row>
+    <row r="66" spans="16:16" x14ac:dyDescent="0.3">
+      <c r="P66" s="4"/>
+    </row>
+    <row r="67" spans="16:16" x14ac:dyDescent="0.3">
+      <c r="P67" s="4"/>
+    </row>
+    <row r="68" spans="16:16" x14ac:dyDescent="0.3">
+      <c r="P68" s="4"/>
+    </row>
+    <row r="69" spans="16:16" x14ac:dyDescent="0.3">
+      <c r="P69" s="4"/>
+    </row>
+    <row r="70" spans="16:16" x14ac:dyDescent="0.3">
+      <c r="P70" s="4"/>
+    </row>
+    <row r="71" spans="16:16" x14ac:dyDescent="0.3">
+      <c r="P71" s="4"/>
+    </row>
+    <row r="72" spans="16:16" x14ac:dyDescent="0.3">
+      <c r="P72" s="4"/>
+    </row>
+    <row r="73" spans="16:16" x14ac:dyDescent="0.3">
+      <c r="P73" s="4"/>
+    </row>
+    <row r="74" spans="16:16" x14ac:dyDescent="0.3">
+      <c r="P74" s="4"/>
+    </row>
+    <row r="75" spans="16:16" x14ac:dyDescent="0.3">
+      <c r="P75" s="4"/>
+    </row>
+    <row r="76" spans="16:16" x14ac:dyDescent="0.3">
+      <c r="P76" s="4"/>
+    </row>
+    <row r="77" spans="16:16" x14ac:dyDescent="0.3">
+      <c r="P77" s="4"/>
+    </row>
+    <row r="78" spans="16:16" x14ac:dyDescent="0.3">
+      <c r="P78" s="4"/>
+    </row>
+    <row r="79" spans="16:16" x14ac:dyDescent="0.3">
+      <c r="P79" s="4"/>
+    </row>
+    <row r="80" spans="16:16" x14ac:dyDescent="0.3">
+      <c r="P80" s="4"/>
+    </row>
+    <row r="81" spans="16:16" x14ac:dyDescent="0.3">
+      <c r="P81" s="4"/>
+    </row>
+    <row r="82" spans="16:16" x14ac:dyDescent="0.3">
+      <c r="P82" s="4"/>
+    </row>
+    <row r="83" spans="16:16" x14ac:dyDescent="0.3">
+      <c r="P83" s="4"/>
+    </row>
+    <row r="84" spans="16:16" x14ac:dyDescent="0.3">
+      <c r="P84" s="4"/>
+    </row>
+    <row r="85" spans="16:16" x14ac:dyDescent="0.3">
+      <c r="P85" s="4"/>
+    </row>
+    <row r="86" spans="16:16" x14ac:dyDescent="0.3">
+      <c r="P86" s="4"/>
+    </row>
+    <row r="87" spans="16:16" x14ac:dyDescent="0.3">
+      <c r="P87" s="4"/>
+    </row>
+    <row r="88" spans="16:16" x14ac:dyDescent="0.3">
+      <c r="P88" s="4"/>
+    </row>
+    <row r="89" spans="16:16" x14ac:dyDescent="0.3">
+      <c r="P89" s="4"/>
+    </row>
+    <row r="90" spans="16:16" x14ac:dyDescent="0.3">
+      <c r="P90" s="4"/>
+    </row>
+    <row r="91" spans="16:16" x14ac:dyDescent="0.3">
+      <c r="P91" s="4"/>
+    </row>
+    <row r="92" spans="16:16" x14ac:dyDescent="0.3">
+      <c r="P92" s="4"/>
+    </row>
+    <row r="93" spans="16:16" x14ac:dyDescent="0.3">
+      <c r="P93" s="4"/>
+    </row>
+    <row r="94" spans="16:16" x14ac:dyDescent="0.3">
+      <c r="P94" s="4"/>
+    </row>
+    <row r="95" spans="16:16" x14ac:dyDescent="0.3">
+      <c r="P95" s="4"/>
+    </row>
+    <row r="96" spans="16:16" x14ac:dyDescent="0.3">
+      <c r="P96" s="4"/>
+    </row>
+    <row r="97" spans="16:16" x14ac:dyDescent="0.3">
+      <c r="P97" s="4"/>
+    </row>
+    <row r="98" spans="16:16" x14ac:dyDescent="0.3">
+      <c r="P98" s="4"/>
+    </row>
+    <row r="99" spans="16:16" x14ac:dyDescent="0.3">
+      <c r="P99" s="4"/>
+    </row>
+    <row r="100" spans="16:16" x14ac:dyDescent="0.3">
+      <c r="P100" s="4"/>
+    </row>
+    <row r="101" spans="16:16" x14ac:dyDescent="0.3">
+      <c r="P101" s="4"/>
+    </row>
+    <row r="102" spans="16:16" x14ac:dyDescent="0.3">
+      <c r="P102" s="4"/>
+    </row>
+    <row r="103" spans="16:16" x14ac:dyDescent="0.3">
+      <c r="P103" s="4"/>
+    </row>
+    <row r="104" spans="16:16" x14ac:dyDescent="0.3">
+      <c r="P104" s="4"/>
+    </row>
+    <row r="105" spans="16:16" x14ac:dyDescent="0.3">
+      <c r="P105" s="4"/>
+    </row>
+    <row r="106" spans="16:16" x14ac:dyDescent="0.3">
+      <c r="P106" s="4"/>
+    </row>
+    <row r="107" spans="16:16" x14ac:dyDescent="0.3">
+      <c r="P107" s="4"/>
+    </row>
+    <row r="108" spans="16:16" x14ac:dyDescent="0.3">
+      <c r="P108" s="4"/>
+    </row>
+    <row r="109" spans="16:16" x14ac:dyDescent="0.3">
+      <c r="P109" s="4"/>
+    </row>
+    <row r="110" spans="16:16" x14ac:dyDescent="0.3">
+      <c r="P110" s="4"/>
+    </row>
+    <row r="111" spans="16:16" x14ac:dyDescent="0.3">
+      <c r="P111" s="4"/>
+    </row>
+    <row r="112" spans="16:16" x14ac:dyDescent="0.3">
+      <c r="P112" s="4"/>
+    </row>
+    <row r="113" spans="16:16" x14ac:dyDescent="0.3">
+      <c r="P113" s="4"/>
+    </row>
+    <row r="114" spans="16:16" x14ac:dyDescent="0.3">
+      <c r="P114" s="4"/>
+    </row>
+    <row r="115" spans="16:16" x14ac:dyDescent="0.3">
+      <c r="P115" s="4"/>
+    </row>
+    <row r="116" spans="16:16" x14ac:dyDescent="0.3">
+      <c r="P116" s="4"/>
+    </row>
+    <row r="117" spans="16:16" x14ac:dyDescent="0.3">
+      <c r="P117" s="4"/>
+    </row>
+    <row r="118" spans="16:16" x14ac:dyDescent="0.3">
+      <c r="P118" s="4"/>
+    </row>
+    <row r="119" spans="16:16" x14ac:dyDescent="0.3">
+      <c r="P119" s="4"/>
+    </row>
+    <row r="120" spans="16:16" x14ac:dyDescent="0.3">
+      <c r="P120" s="4"/>
+    </row>
+    <row r="121" spans="16:16" x14ac:dyDescent="0.3">
+      <c r="P121" s="4"/>
+    </row>
+    <row r="122" spans="16:16" x14ac:dyDescent="0.3">
+      <c r="P122" s="4"/>
+    </row>
+    <row r="123" spans="16:16" x14ac:dyDescent="0.3">
+      <c r="P123" s="4"/>
+    </row>
+    <row r="124" spans="16:16" x14ac:dyDescent="0.3">
+      <c r="P124" s="4"/>
+    </row>
+    <row r="125" spans="16:16" x14ac:dyDescent="0.3">
+      <c r="P125" s="4"/>
+    </row>
+    <row r="126" spans="16:16" x14ac:dyDescent="0.3">
+      <c r="P126" s="4"/>
+    </row>
+    <row r="127" spans="16:16" x14ac:dyDescent="0.3">
+      <c r="P127" s="4"/>
+    </row>
+    <row r="128" spans="16:16" x14ac:dyDescent="0.3">
+      <c r="P128" s="4"/>
+    </row>
+    <row r="129" spans="16:16" x14ac:dyDescent="0.3">
+      <c r="P129" s="4"/>
+    </row>
+    <row r="130" spans="16:16" x14ac:dyDescent="0.3">
+      <c r="P130" s="4"/>
+    </row>
+    <row r="131" spans="16:16" x14ac:dyDescent="0.3">
+      <c r="P131" s="4"/>
+    </row>
+    <row r="132" spans="16:16" x14ac:dyDescent="0.3">
+      <c r="P132" s="4"/>
+    </row>
+    <row r="133" spans="16:16" x14ac:dyDescent="0.3">
+      <c r="P133" s="4"/>
+    </row>
+    <row r="134" spans="16:16" x14ac:dyDescent="0.3">
+      <c r="P134" s="4"/>
+    </row>
+    <row r="135" spans="16:16" x14ac:dyDescent="0.3">
+      <c r="P135" s="4"/>
+    </row>
+    <row r="136" spans="16:16" x14ac:dyDescent="0.3">
+      <c r="P136" s="4"/>
+    </row>
+    <row r="137" spans="16:16" x14ac:dyDescent="0.3">
+      <c r="P137" s="4"/>
+    </row>
+    <row r="138" spans="16:16" x14ac:dyDescent="0.3">
+      <c r="P138" s="4"/>
+    </row>
+    <row r="139" spans="16:16" x14ac:dyDescent="0.3">
+      <c r="P139" s="4"/>
+    </row>
+    <row r="140" spans="16:16" x14ac:dyDescent="0.3">
+      <c r="P140" s="4"/>
+    </row>
+    <row r="141" spans="16:16" x14ac:dyDescent="0.3">
+      <c r="P141" s="4"/>
+    </row>
+    <row r="142" spans="16:16" x14ac:dyDescent="0.3">
+      <c r="P142" s="4"/>
+    </row>
+    <row r="143" spans="16:16" x14ac:dyDescent="0.3">
+      <c r="P143" s="4"/>
+    </row>
+    <row r="144" spans="16:16" x14ac:dyDescent="0.3">
+      <c r="P144" s="4"/>
+    </row>
+    <row r="145" spans="16:16" x14ac:dyDescent="0.3">
+      <c r="P145" s="4"/>
+    </row>
+    <row r="146" spans="16:16" x14ac:dyDescent="0.3">
+      <c r="P146" s="4"/>
+    </row>
+    <row r="147" spans="16:16" x14ac:dyDescent="0.3">
+      <c r="P147" s="4"/>
+    </row>
+    <row r="148" spans="16:16" x14ac:dyDescent="0.3">
+      <c r="P148" s="4"/>
+    </row>
+    <row r="149" spans="16:16" x14ac:dyDescent="0.3">
+      <c r="P149" s="4"/>
+    </row>
+    <row r="150" spans="16:16" x14ac:dyDescent="0.3">
+      <c r="P150" s="4"/>
+    </row>
+    <row r="151" spans="16:16" x14ac:dyDescent="0.3">
+      <c r="P151" s="4"/>
+    </row>
+    <row r="152" spans="16:16" x14ac:dyDescent="0.3">
+      <c r="P152" s="4"/>
+    </row>
+    <row r="153" spans="16:16" x14ac:dyDescent="0.3">
+      <c r="P153" s="4"/>
+    </row>
+    <row r="154" spans="16:16" x14ac:dyDescent="0.3">
+      <c r="P154" s="4"/>
+    </row>
+    <row r="155" spans="16:16" x14ac:dyDescent="0.3">
+      <c r="P155" s="4"/>
+    </row>
+    <row r="156" spans="16:16" x14ac:dyDescent="0.3">
+      <c r="P156" s="4"/>
+    </row>
+    <row r="157" spans="16:16" x14ac:dyDescent="0.3">
+      <c r="P157" s="4"/>
+    </row>
+    <row r="158" spans="16:16" x14ac:dyDescent="0.3">
+      <c r="P158" s="4"/>
+    </row>
+    <row r="159" spans="16:16" x14ac:dyDescent="0.3">
+      <c r="P159" s="4"/>
+    </row>
+    <row r="160" spans="16:16" x14ac:dyDescent="0.3">
+      <c r="P160" s="4"/>
+    </row>
+    <row r="161" spans="16:16" x14ac:dyDescent="0.3">
+      <c r="P161" s="4"/>
+    </row>
+    <row r="162" spans="16:16" x14ac:dyDescent="0.3">
+      <c r="P162" s="4"/>
+    </row>
+    <row r="163" spans="16:16" x14ac:dyDescent="0.3">
+      <c r="P163" s="4"/>
+    </row>
+    <row r="164" spans="16:16" x14ac:dyDescent="0.3">
+      <c r="P164" s="4"/>
+    </row>
+    <row r="165" spans="16:16" x14ac:dyDescent="0.3">
+      <c r="P165" s="4"/>
+    </row>
+    <row r="166" spans="16:16" x14ac:dyDescent="0.3">
+      <c r="P166" s="4"/>
+    </row>
+    <row r="167" spans="16:16" x14ac:dyDescent="0.3">
+      <c r="P167" s="4"/>
+    </row>
+    <row r="168" spans="16:16" x14ac:dyDescent="0.3">
+      <c r="P168" s="4"/>
+    </row>
+    <row r="169" spans="16:16" x14ac:dyDescent="0.3">
+      <c r="P169" s="4"/>
+    </row>
+    <row r="170" spans="16:16" x14ac:dyDescent="0.3">
+      <c r="P170" s="4"/>
+    </row>
+    <row r="171" spans="16:16" x14ac:dyDescent="0.3">
+      <c r="P171" s="4"/>
+    </row>
+    <row r="172" spans="16:16" x14ac:dyDescent="0.3">
+      <c r="P172" s="4"/>
+    </row>
+    <row r="173" spans="16:16" x14ac:dyDescent="0.3">
+      <c r="P173" s="4"/>
+    </row>
+    <row r="174" spans="16:16" x14ac:dyDescent="0.3">
+      <c r="P174" s="4"/>
+    </row>
+    <row r="175" spans="16:16" x14ac:dyDescent="0.3">
+      <c r="P175" s="4"/>
+    </row>
+    <row r="176" spans="16:16" x14ac:dyDescent="0.3">
+      <c r="P176" s="4"/>
+    </row>
+    <row r="177" spans="16:16" x14ac:dyDescent="0.3">
+      <c r="P177" s="4"/>
+    </row>
+    <row r="178" spans="16:16" x14ac:dyDescent="0.3">
+      <c r="P178" s="4"/>
+    </row>
+    <row r="179" spans="16:16" x14ac:dyDescent="0.3">
+      <c r="P179" s="4"/>
+    </row>
+    <row r="180" spans="16:16" x14ac:dyDescent="0.3">
+      <c r="P180" s="4"/>
+    </row>
+    <row r="181" spans="16:16" x14ac:dyDescent="0.3">
+      <c r="P181" s="4"/>
+    </row>
+    <row r="182" spans="16:16" x14ac:dyDescent="0.3">
+      <c r="P182" s="4"/>
+    </row>
+    <row r="183" spans="16:16" x14ac:dyDescent="0.3">
+      <c r="P183" s="4"/>
+    </row>
+    <row r="184" spans="16:16" x14ac:dyDescent="0.3">
+      <c r="P184" s="4"/>
+    </row>
+    <row r="185" spans="16:16" x14ac:dyDescent="0.3">
+      <c r="P185" s="4"/>
+    </row>
+    <row r="186" spans="16:16" x14ac:dyDescent="0.3">
+      <c r="P186" s="4"/>
+    </row>
+    <row r="187" spans="16:16" x14ac:dyDescent="0.3">
+      <c r="P187" s="4"/>
+    </row>
+    <row r="188" spans="16:16" x14ac:dyDescent="0.3">
+      <c r="P188" s="4"/>
+    </row>
+    <row r="189" spans="16:16" x14ac:dyDescent="0.3">
+      <c r="P189" s="4"/>
+    </row>
+    <row r="190" spans="16:16" x14ac:dyDescent="0.3">
+      <c r="P190" s="4"/>
+    </row>
+    <row r="191" spans="16:16" x14ac:dyDescent="0.3">
+      <c r="P191" s="4"/>
+    </row>
+    <row r="192" spans="16:16" x14ac:dyDescent="0.3">
+      <c r="P192" s="4"/>
+    </row>
+    <row r="193" spans="16:16" x14ac:dyDescent="0.3">
+      <c r="P193" s="4"/>
+    </row>
+    <row r="194" spans="16:16" x14ac:dyDescent="0.3">
+      <c r="P194" s="4"/>
+    </row>
+    <row r="195" spans="16:16" x14ac:dyDescent="0.3">
+      <c r="P195" s="4"/>
+    </row>
+    <row r="196" spans="16:16" x14ac:dyDescent="0.3">
+      <c r="P196" s="4"/>
+    </row>
+    <row r="197" spans="16:16" x14ac:dyDescent="0.3">
+      <c r="P197" s="4"/>
+    </row>
+    <row r="198" spans="16:16" x14ac:dyDescent="0.3">
+      <c r="P198" s="4"/>
+    </row>
+    <row r="199" spans="16:16" x14ac:dyDescent="0.3">
+      <c r="P199" s="4"/>
+    </row>
+    <row r="200" spans="16:16" x14ac:dyDescent="0.3">
+      <c r="P200" s="4"/>
+    </row>
+    <row r="201" spans="16:16" x14ac:dyDescent="0.3">
+      <c r="P201" s="4"/>
+    </row>
+    <row r="202" spans="16:16" x14ac:dyDescent="0.3">
+      <c r="P202" s="4"/>
+    </row>
+    <row r="203" spans="16:16" x14ac:dyDescent="0.3">
+      <c r="P203" s="4"/>
+    </row>
+    <row r="204" spans="16:16" x14ac:dyDescent="0.3">
+      <c r="P204" s="4"/>
+    </row>
+    <row r="205" spans="16:16" x14ac:dyDescent="0.3">
+      <c r="P205" s="4"/>
+    </row>
+    <row r="206" spans="16:16" x14ac:dyDescent="0.3">
+      <c r="P206" s="4"/>
+    </row>
+    <row r="207" spans="16:16" x14ac:dyDescent="0.3">
+      <c r="P207" s="4"/>
+    </row>
+    <row r="208" spans="16:16" x14ac:dyDescent="0.3">
+      <c r="P208" s="4"/>
+    </row>
+    <row r="209" spans="16:16" x14ac:dyDescent="0.3">
+      <c r="P209" s="4"/>
+    </row>
+    <row r="210" spans="16:16" x14ac:dyDescent="0.3">
+      <c r="P210" s="4"/>
+    </row>
+    <row r="211" spans="16:16" x14ac:dyDescent="0.3">
+      <c r="P211" s="4"/>
+    </row>
+    <row r="212" spans="16:16" x14ac:dyDescent="0.3">
+      <c r="P212" s="4"/>
+    </row>
+    <row r="213" spans="16:16" x14ac:dyDescent="0.3">
+      <c r="P213" s="4"/>
+    </row>
+    <row r="214" spans="16:16" x14ac:dyDescent="0.3">
+      <c r="P214" s="4"/>
+    </row>
+    <row r="215" spans="16:16" x14ac:dyDescent="0.3">
+      <c r="P215" s="4"/>
+    </row>
+    <row r="216" spans="16:16" x14ac:dyDescent="0.3">
+      <c r="P216" s="4"/>
+    </row>
+    <row r="217" spans="16:16" x14ac:dyDescent="0.3">
+      <c r="P217" s="4"/>
+    </row>
+    <row r="218" spans="16:16" x14ac:dyDescent="0.3">
+      <c r="P218" s="4"/>
+    </row>
+    <row r="219" spans="16:16" x14ac:dyDescent="0.3">
+      <c r="P219" s="4"/>
+    </row>
+    <row r="220" spans="16:16" x14ac:dyDescent="0.3">
+      <c r="P220" s="4"/>
+    </row>
+    <row r="221" spans="16:16" x14ac:dyDescent="0.3">
+      <c r="P221" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -15116,23 +15155,23 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5539A729-4FB7-440D-A765-676495DE3453}">
   <dimension ref="A1:C8"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="17.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" s="2" t="s">
         <v>148</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="2" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -15143,7 +15182,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>11</v>
       </c>
@@ -15154,7 +15193,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>11</v>
       </c>
@@ -15165,7 +15204,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>11</v>
       </c>
@@ -15176,7 +15215,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>11</v>
       </c>
@@ -15187,7 +15226,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>11</v>
       </c>
@@ -15198,7 +15237,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>11</v>
       </c>
@@ -15217,48 +15256,48 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AAB1106B-D567-41FC-8E91-2B4CC5EC9B59}">
   <dimension ref="A1:K1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B1" s="3">
-        <v>1</v>
-      </c>
-      <c r="C1" s="3">
+      <c r="B1" s="2">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2">
         <f>B1+1</f>
         <v>2</v>
       </c>
-      <c r="D1" s="3">
+      <c r="D1" s="2">
         <f t="shared" ref="D1:K1" si="0">C1+1</f>
         <v>3</v>
       </c>
-      <c r="E1" s="3">
+      <c r="E1" s="2">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="F1" s="3">
+      <c r="F1" s="2">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="G1" s="3">
+      <c r="G1" s="2">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="H1" s="3">
+      <c r="H1" s="2">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
-      <c r="I1" s="3">
+      <c r="I1" s="2">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="J1" s="3">
+      <c r="J1" s="2">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
-      <c r="K1" s="3">
+      <c r="K1" s="2">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
@@ -15271,528 +15310,527 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8A86A8A7-FD76-4891-A53C-CBB095359118}">
   <dimension ref="A1:J16"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="16.85546875" style="5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.42578125" style="5" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="5.5703125" style="5" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="16.42578125" style="5" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="8.140625" style="5" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.140625" style="5" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="8.85546875" style="5" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.5703125" style="5" bestFit="1" customWidth="1"/>
-    <col min="9" max="16384" width="9.140625" style="5"/>
+    <col min="1" max="1" width="16.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.44140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8.88671875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="4" t="s">
+    <row r="1" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="B1" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="C1" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="D1" s="4" t="s">
+      <c r="C1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="E1" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="F1" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="G1" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="H1" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="I1" s="4" t="s">
+      <c r="I1" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="J1" s="4" t="s">
+      <c r="J1" s="2" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A2" s="5" t="s">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
         <v>63</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="B2" t="s">
         <v>21</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="C2" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="5">
-        <v>1</v>
-      </c>
-      <c r="E2" s="5">
+      <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="E2">
         <v>10</v>
       </c>
-      <c r="F2" s="5">
+      <c r="F2">
         <v>22</v>
       </c>
-      <c r="G2" s="5">
+      <c r="G2">
         <v>3</v>
       </c>
-      <c r="H2" s="5">
+      <c r="H2">
         <v>3</v>
       </c>
-      <c r="I2" s="5">
+      <c r="I2">
         <v>0.7</v>
       </c>
-      <c r="J2" s="5">
+      <c r="J2">
         <v>0.7</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A3" s="5" t="s">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
         <v>63</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B3" t="s">
         <v>23</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="C3" t="s">
         <v>8</v>
       </c>
-      <c r="D3" s="5">
-        <v>1</v>
-      </c>
-      <c r="E3" s="5">
+      <c r="D3">
+        <v>1</v>
+      </c>
+      <c r="E3">
         <v>3</v>
       </c>
-      <c r="F3" s="5">
-        <v>0</v>
-      </c>
-      <c r="G3" s="5">
+      <c r="F3">
+        <v>0</v>
+      </c>
+      <c r="G3">
         <v>3</v>
       </c>
-      <c r="H3" s="5">
+      <c r="H3">
         <v>3</v>
       </c>
-      <c r="I3" s="5">
+      <c r="I3">
         <v>0.7</v>
       </c>
-      <c r="J3" s="5">
+      <c r="J3">
         <v>0.7</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A4" s="5" t="s">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
         <v>63</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="B4" t="s">
         <v>23</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="C4" t="s">
         <v>62</v>
       </c>
-      <c r="D4" s="5">
-        <v>1</v>
-      </c>
-      <c r="E4" s="5">
+      <c r="D4">
+        <v>1</v>
+      </c>
+      <c r="E4">
         <v>6</v>
       </c>
-      <c r="F4" s="5">
-        <v>0</v>
-      </c>
-      <c r="G4" s="5">
+      <c r="F4">
+        <v>0</v>
+      </c>
+      <c r="G4">
         <v>3</v>
       </c>
-      <c r="H4" s="5">
+      <c r="H4">
         <v>3</v>
       </c>
-      <c r="I4" s="5">
+      <c r="I4">
         <v>0.7</v>
       </c>
-      <c r="J4" s="5">
+      <c r="J4">
         <v>0.7</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>124</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="B5" t="s">
         <v>21</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="C5" t="s">
         <v>8</v>
       </c>
-      <c r="D5" s="5">
-        <v>1</v>
-      </c>
-      <c r="E5" s="5">
+      <c r="D5">
+        <v>1</v>
+      </c>
+      <c r="E5">
         <v>3</v>
       </c>
-      <c r="F5" s="5">
+      <c r="F5">
         <v>15</v>
       </c>
-      <c r="G5" s="5">
+      <c r="G5">
         <v>5</v>
       </c>
-      <c r="H5" s="5">
+      <c r="H5">
         <v>5</v>
       </c>
-      <c r="I5" s="5">
+      <c r="I5">
         <v>0.7</v>
       </c>
-      <c r="J5" s="5">
+      <c r="J5">
         <v>0.7</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>124</v>
       </c>
-      <c r="B6" s="5" t="s">
+      <c r="B6" t="s">
         <v>21</v>
       </c>
-      <c r="C6" s="5" t="s">
+      <c r="C6" t="s">
         <v>117</v>
       </c>
-      <c r="D6" s="5">
-        <v>1</v>
-      </c>
-      <c r="E6" s="5">
+      <c r="D6">
+        <v>1</v>
+      </c>
+      <c r="E6">
         <v>10</v>
       </c>
-      <c r="F6" s="5">
-        <v>0</v>
-      </c>
-      <c r="G6" s="5">
+      <c r="F6">
+        <v>0</v>
+      </c>
+      <c r="G6">
         <v>5</v>
       </c>
-      <c r="H6" s="5">
+      <c r="H6">
         <v>5</v>
       </c>
-      <c r="I6" s="5">
+      <c r="I6">
         <v>0.7</v>
       </c>
-      <c r="J6" s="5">
+      <c r="J6">
         <v>0.7</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>124</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="B7" t="s">
         <v>23</v>
       </c>
-      <c r="C7" s="5" t="s">
+      <c r="C7" t="s">
         <v>62</v>
       </c>
-      <c r="D7" s="5">
-        <v>1</v>
-      </c>
-      <c r="E7" s="5">
+      <c r="D7">
+        <v>1</v>
+      </c>
+      <c r="E7">
         <v>9</v>
       </c>
-      <c r="F7" s="5">
-        <v>0</v>
-      </c>
-      <c r="G7" s="5">
+      <c r="F7">
+        <v>0</v>
+      </c>
+      <c r="G7">
         <v>5</v>
       </c>
-      <c r="H7" s="5">
+      <c r="H7">
         <v>5</v>
       </c>
-      <c r="I7" s="5">
+      <c r="I7">
         <v>0.7</v>
       </c>
-      <c r="J7" s="5">
+      <c r="J7">
         <v>0.7</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>125</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="B8" t="s">
         <v>21</v>
       </c>
-      <c r="C8" s="5" t="s">
+      <c r="C8" t="s">
         <v>8</v>
       </c>
-      <c r="D8" s="5">
-        <v>1</v>
-      </c>
-      <c r="E8" s="5">
+      <c r="D8">
+        <v>1</v>
+      </c>
+      <c r="E8">
         <v>3</v>
       </c>
-      <c r="F8" s="5">
+      <c r="F8">
         <v>15</v>
       </c>
-      <c r="G8" s="5">
+      <c r="G8">
         <v>5</v>
       </c>
-      <c r="H8" s="5">
+      <c r="H8">
         <v>5</v>
       </c>
-      <c r="I8" s="5">
+      <c r="I8">
         <v>0.7</v>
       </c>
-      <c r="J8" s="5">
+      <c r="J8">
         <v>0.7</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>125</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="B9" t="s">
         <v>23</v>
       </c>
-      <c r="C9" s="5" t="s">
+      <c r="C9" t="s">
         <v>62</v>
       </c>
-      <c r="D9" s="5">
-        <v>1</v>
-      </c>
-      <c r="E9" s="5">
+      <c r="D9">
+        <v>1</v>
+      </c>
+      <c r="E9">
         <v>9</v>
       </c>
-      <c r="F9" s="5">
-        <v>0</v>
-      </c>
-      <c r="G9" s="5">
+      <c r="F9">
+        <v>0</v>
+      </c>
+      <c r="G9">
         <v>5</v>
       </c>
-      <c r="H9" s="5">
+      <c r="H9">
         <v>5</v>
       </c>
-      <c r="I9" s="5">
+      <c r="I9">
         <v>0.7</v>
       </c>
-      <c r="J9" s="5">
+      <c r="J9">
         <v>0.7</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>109</v>
       </c>
-      <c r="B10" s="5" t="s">
+      <c r="B10" t="s">
         <v>21</v>
       </c>
-      <c r="C10" s="5" t="s">
+      <c r="C10" t="s">
         <v>62</v>
       </c>
-      <c r="D10" s="5">
-        <v>1</v>
-      </c>
-      <c r="E10" s="5">
+      <c r="D10">
+        <v>1</v>
+      </c>
+      <c r="E10">
         <v>3</v>
       </c>
-      <c r="F10" s="5">
-        <v>0</v>
-      </c>
-      <c r="G10" s="5">
-        <v>1</v>
-      </c>
-      <c r="H10" s="5">
-        <v>1</v>
-      </c>
-      <c r="I10" s="5">
+      <c r="F10">
+        <v>0</v>
+      </c>
+      <c r="G10">
+        <v>1</v>
+      </c>
+      <c r="H10">
+        <v>1</v>
+      </c>
+      <c r="I10">
         <v>0.7</v>
       </c>
-      <c r="J10" s="5">
+      <c r="J10">
         <v>0.7</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>109</v>
       </c>
-      <c r="B11" s="5" t="s">
+      <c r="B11" t="s">
         <v>23</v>
       </c>
-      <c r="C11" s="5" t="s">
+      <c r="C11" t="s">
         <v>107</v>
       </c>
-      <c r="D11" s="5">
-        <v>1</v>
-      </c>
-      <c r="E11" s="5">
+      <c r="D11">
+        <v>1</v>
+      </c>
+      <c r="E11">
         <v>3</v>
       </c>
-      <c r="F11" s="5">
-        <v>0</v>
-      </c>
-      <c r="G11" s="5">
-        <v>1</v>
-      </c>
-      <c r="H11" s="5">
-        <v>1</v>
-      </c>
-      <c r="I11" s="5">
+      <c r="F11">
+        <v>0</v>
+      </c>
+      <c r="G11">
+        <v>1</v>
+      </c>
+      <c r="H11">
+        <v>1</v>
+      </c>
+      <c r="I11">
         <v>0.7</v>
       </c>
-      <c r="J11" s="5">
+      <c r="J11">
         <v>0.7</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>110</v>
       </c>
-      <c r="B12" s="5" t="s">
+      <c r="B12" t="s">
         <v>21</v>
       </c>
-      <c r="C12" s="5" t="s">
+      <c r="C12" t="s">
         <v>107</v>
       </c>
-      <c r="D12" s="5">
-        <v>1</v>
-      </c>
-      <c r="E12" s="5">
+      <c r="D12">
+        <v>1</v>
+      </c>
+      <c r="E12">
         <v>3</v>
       </c>
-      <c r="F12" s="5">
-        <v>0</v>
-      </c>
-      <c r="G12" s="5">
-        <v>1</v>
-      </c>
-      <c r="H12" s="5">
-        <v>1</v>
-      </c>
-      <c r="I12" s="5">
+      <c r="F12">
+        <v>0</v>
+      </c>
+      <c r="G12">
+        <v>1</v>
+      </c>
+      <c r="H12">
+        <v>1</v>
+      </c>
+      <c r="I12">
         <v>0.7</v>
       </c>
-      <c r="J12" s="5">
+      <c r="J12">
         <v>0.7</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>110</v>
       </c>
-      <c r="B13" s="5" t="s">
+      <c r="B13" t="s">
         <v>23</v>
       </c>
-      <c r="C13" s="5" t="s">
+      <c r="C13" t="s">
         <v>62</v>
       </c>
-      <c r="D13" s="5">
-        <v>1</v>
-      </c>
-      <c r="E13" s="5">
+      <c r="D13">
+        <v>1</v>
+      </c>
+      <c r="E13">
         <v>3</v>
       </c>
-      <c r="F13" s="5">
-        <v>0</v>
-      </c>
-      <c r="G13" s="5">
-        <v>1</v>
-      </c>
-      <c r="H13" s="5">
-        <v>1</v>
-      </c>
-      <c r="I13" s="5">
+      <c r="F13">
+        <v>0</v>
+      </c>
+      <c r="G13">
+        <v>1</v>
+      </c>
+      <c r="H13">
+        <v>1</v>
+      </c>
+      <c r="I13">
         <v>0.7</v>
       </c>
-      <c r="J13" s="5">
+      <c r="J13">
         <v>0.7</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A14" s="5" t="s">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
         <v>108</v>
       </c>
-      <c r="B14" s="5" t="s">
+      <c r="B14" t="s">
         <v>23</v>
       </c>
-      <c r="C14" s="5" t="s">
+      <c r="C14" t="s">
         <v>62</v>
       </c>
-      <c r="D14" s="5">
-        <v>1</v>
-      </c>
-      <c r="E14" s="5">
+      <c r="D14">
+        <v>1</v>
+      </c>
+      <c r="E14">
         <v>3</v>
       </c>
-      <c r="F14" s="5">
-        <v>0</v>
-      </c>
-      <c r="G14" s="5">
-        <v>1</v>
-      </c>
-      <c r="H14" s="5">
-        <v>1</v>
-      </c>
-      <c r="I14" s="5">
+      <c r="F14">
+        <v>0</v>
+      </c>
+      <c r="G14">
+        <v>1</v>
+      </c>
+      <c r="H14">
+        <v>1</v>
+      </c>
+      <c r="I14">
         <v>0.7</v>
       </c>
-      <c r="J14" s="5">
+      <c r="J14">
         <v>0.7</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A15" s="5" t="s">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
         <v>111</v>
       </c>
-      <c r="B15" s="5" t="s">
+      <c r="B15" t="s">
         <v>21</v>
       </c>
-      <c r="C15" s="5" t="s">
+      <c r="C15" t="s">
         <v>8</v>
       </c>
-      <c r="D15" s="5">
-        <v>1</v>
-      </c>
-      <c r="E15" s="5">
+      <c r="D15">
+        <v>1</v>
+      </c>
+      <c r="E15">
         <v>5</v>
       </c>
-      <c r="F15" s="5">
+      <c r="F15">
         <v>15</v>
       </c>
-      <c r="G15" s="5">
+      <c r="G15">
         <v>10</v>
       </c>
-      <c r="H15" s="5">
+      <c r="H15">
         <v>10</v>
       </c>
-      <c r="I15" s="5">
+      <c r="I15">
         <v>0.7</v>
       </c>
-      <c r="J15" s="5">
+      <c r="J15">
         <v>0.7</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A16" s="5" t="s">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
         <v>111</v>
       </c>
-      <c r="B16" s="5" t="s">
+      <c r="B16" t="s">
         <v>23</v>
       </c>
-      <c r="C16" s="5" t="s">
+      <c r="C16" t="s">
         <v>62</v>
       </c>
-      <c r="D16" s="5">
-        <v>1</v>
-      </c>
-      <c r="E16" s="5">
+      <c r="D16">
+        <v>1</v>
+      </c>
+      <c r="E16">
         <v>5</v>
       </c>
-      <c r="F16" s="5">
-        <v>0</v>
-      </c>
-      <c r="G16" s="5">
+      <c r="F16">
+        <v>0</v>
+      </c>
+      <c r="G16">
         <v>10</v>
       </c>
-      <c r="H16" s="5">
+      <c r="H16">
         <v>10</v>
       </c>
-      <c r="I16" s="5">
+      <c r="I16">
         <v>0.7</v>
       </c>
-      <c r="J16" s="5">
+      <c r="J16">
         <v>0.7</v>
       </c>
     </row>
@@ -15806,156 +15844,156 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B7AEF404-3743-47D7-AC45-7AE3A9FB796E}">
   <dimension ref="A1:A25"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="19.28515625" style="8" customWidth="1"/>
+    <col min="1" max="1" width="19.33203125" style="5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1" s="2" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A2" s="8">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A2" s="5">
         <f>IF(timeseries!A2&lt;&gt;"",timeseries!A2,"")</f>
         <v>45398</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A3" s="8">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A3" s="5">
         <f>IF(timeseries!A3&lt;&gt;"",timeseries!A3,"")</f>
         <v>45398.041666666664</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A4" s="8">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A4" s="5">
         <f>IF(timeseries!A4&lt;&gt;"",timeseries!A4,"")</f>
         <v>45398.083333333336</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A5" s="8">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A5" s="5">
         <f>IF(timeseries!A5&lt;&gt;"",timeseries!A5,"")</f>
         <v>45398.125</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A6" s="8">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6" s="5">
         <f>IF(timeseries!A6&lt;&gt;"",timeseries!A6,"")</f>
         <v>45398.166666666664</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A7" s="8">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A7" s="5">
         <f>IF(timeseries!A7&lt;&gt;"",timeseries!A7,"")</f>
         <v>45398.208333333336</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A8" s="8">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A8" s="5">
         <f>IF(timeseries!A8&lt;&gt;"",timeseries!A8,"")</f>
         <v>45398.25</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A9" s="8">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A9" s="5">
         <f>IF(timeseries!A9&lt;&gt;"",timeseries!A9,"")</f>
         <v>45398.291666666664</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A10" s="8">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A10" s="5">
         <f>IF(timeseries!A10&lt;&gt;"",timeseries!A10,"")</f>
         <v>45398.333333333336</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A11" s="8">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A11" s="5">
         <f>IF(timeseries!A11&lt;&gt;"",timeseries!A11,"")</f>
         <v>45398.375</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A12" s="8">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A12" s="5">
         <f>IF(timeseries!A12&lt;&gt;"",timeseries!A12,"")</f>
         <v>45398.416666666664</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A13" s="8">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A13" s="5">
         <f>IF(timeseries!A13&lt;&gt;"",timeseries!A13,"")</f>
         <v>45398.458333333336</v>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A14" s="8">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A14" s="5">
         <f>IF(timeseries!A14&lt;&gt;"",timeseries!A14,"")</f>
         <v>45398.5</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A15" s="8">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A15" s="5">
         <f>IF(timeseries!A15&lt;&gt;"",timeseries!A15,"")</f>
         <v>45398.541666666664</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A16" s="8">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A16" s="5">
         <f>IF(timeseries!A16&lt;&gt;"",timeseries!A16,"")</f>
         <v>45398.583333333336</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A17" s="8">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A17" s="5">
         <f>IF(timeseries!A17&lt;&gt;"",timeseries!A17,"")</f>
         <v>45398.625</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A18" s="8">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A18" s="5">
         <f>IF(timeseries!A18&lt;&gt;"",timeseries!A18,"")</f>
         <v>45398.666666666664</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A19" s="8">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A19" s="5">
         <f>IF(timeseries!A19&lt;&gt;"",timeseries!A19,"")</f>
         <v>45398.708333333336</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A20" s="8">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A20" s="5">
         <f>IF(timeseries!A20&lt;&gt;"",timeseries!A20,"")</f>
         <v>45398.75</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A21" s="8">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A21" s="5">
         <f>IF(timeseries!A21&lt;&gt;"",timeseries!A21,"")</f>
         <v>45398.791666666664</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A22" s="8">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A22" s="5">
         <f>IF(timeseries!A22&lt;&gt;"",timeseries!A22,"")</f>
         <v>45398.833333333336</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A23" s="8">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A23" s="5">
         <f>IF(timeseries!A23&lt;&gt;"",timeseries!A23,"")</f>
         <v>45398.875</v>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A24" s="8">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A24" s="5">
         <f>IF(timeseries!A24&lt;&gt;"",timeseries!A24,"")</f>
         <v>45398.916666666664</v>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A25" s="8">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A25" s="5">
         <f>IF(timeseries!A25&lt;&gt;"",timeseries!A25,"")</f>
         <v>45398.958333333336</v>
       </c>
@@ -15968,27 +16006,27 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C7B98CF0-A261-4D3A-B414-AE3BDF1136D0}">
   <dimension ref="A1:E1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="6.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.28515625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="2" width="6.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="2" t="s">
         <v>94</v>
       </c>
     </row>

--- a/input_data/two_stage_dh_model.xlsx
+++ b/input_data/two_stage_dh_model.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dsdennis\HOPE\Predicer\input_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5709A8F4-2E0D-42D8-8C3F-A0C399672118}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2527E528-7023-4CC7-8B9A-806805C5967A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="796" firstSheet="4" activeTab="14" xr2:uid="{788BFBD1-D930-4535-8A91-D85C56924796}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="796" activeTab="14" xr2:uid="{788BFBD1-D930-4535-8A91-D85C56924796}"/>
   </bookViews>
   <sheets>
     <sheet name="timeseries" sheetId="18" r:id="rId1"/>
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="247" uniqueCount="156">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="248" uniqueCount="157">
   <si>
     <t>node</t>
   </si>
@@ -529,6 +529,9 @@
   </si>
   <si>
     <t>inflow</t>
+  </si>
+  <si>
+    <t>deviation_penalty</t>
   </si>
 </sst>
 </file>
@@ -8339,13 +8342,14 @@
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0B25A1A0-0B9E-4920-9C7F-E13769DD6437}">
-  <dimension ref="A1:F1"/>
+  <dimension ref="A1:G1"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.44140625" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="9.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>151</v>
       </c>
@@ -8363,6 +8367,9 @@
       </c>
       <c r="F1" t="s">
         <v>155</v>
+      </c>
+      <c r="G1" t="s">
+        <v>156</v>
       </c>
     </row>
   </sheetData>
